--- a/grupos/1FM - Estadisticos 20231.xlsx
+++ b/grupos/1FM - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="140">
   <si>
     <t>Materia</t>
   </si>
@@ -3621,13 +3621,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S33"/>
+  <dimension ref="A1:V33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:22">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>43</v>
@@ -3637,120 +3637,132 @@
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="1"/>
+      <c r="I1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
       <c r="S1" s="1"/>
-    </row>
-    <row r="2" spans="1:19">
+      <c r="T1" s="1"/>
+      <c r="U1" s="1"/>
+      <c r="V1" s="1"/>
+    </row>
+    <row r="2" spans="1:22">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="G2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="L2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M2" s="1" t="s">
+      <c r="N2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="P2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="R2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="S2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="T2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="R2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="S2" s="1" t="s">
+      <c r="U2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="V2" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:19">
+    <row r="3" spans="1:22">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:19">
+    <row r="4" spans="1:22">
       <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B4">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C4">
+        <v>100</v>
+      </c>
+      <c r="D4">
         <v>95</v>
       </c>
-      <c r="D4">
-        <v>100</v>
-      </c>
       <c r="E4">
+        <v>100</v>
+      </c>
+      <c r="F4">
         <v>90</v>
       </c>
-      <c r="F4">
-        <v>100</v>
-      </c>
       <c r="G4">
+        <v>100</v>
+      </c>
+      <c r="H4">
         <v>90</v>
       </c>
-      <c r="H4">
-        <v>100</v>
-      </c>
       <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>100</v>
+      </c>
+      <c r="K4">
         <v>95</v>
-      </c>
-      <c r="J4">
-        <v>100</v>
-      </c>
-      <c r="K4">
-        <v>90</v>
       </c>
       <c r="L4">
         <v>100</v>
@@ -3762,27 +3774,36 @@
         <v>100</v>
       </c>
       <c r="O4">
+        <v>90</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>100</v>
+      </c>
+      <c r="R4">
         <v>95</v>
       </c>
-      <c r="P4">
-        <v>100</v>
-      </c>
-      <c r="Q4">
+      <c r="S4">
+        <v>100</v>
+      </c>
+      <c r="T4">
         <v>90</v>
       </c>
-      <c r="R4">
-        <v>100</v>
-      </c>
-      <c r="S4">
+      <c r="U4">
+        <v>100</v>
+      </c>
+      <c r="V4">
         <v>90</v>
       </c>
     </row>
-    <row r="5" spans="1:19">
+    <row r="5" spans="1:22">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B5">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C5">
         <v>100</v>
@@ -3794,16 +3815,16 @@
         <v>100</v>
       </c>
       <c r="F5">
+        <v>100</v>
+      </c>
+      <c r="G5">
         <v>93.8</v>
       </c>
-      <c r="G5">
-        <v>100</v>
-      </c>
       <c r="H5">
         <v>100</v>
       </c>
       <c r="I5">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J5">
         <v>100</v>
@@ -3812,43 +3833,52 @@
         <v>100</v>
       </c>
       <c r="L5">
+        <v>100</v>
+      </c>
+      <c r="M5">
+        <v>100</v>
+      </c>
+      <c r="N5">
         <v>93.8</v>
       </c>
-      <c r="M5">
-        <v>100</v>
-      </c>
-      <c r="N5">
-        <v>100</v>
-      </c>
       <c r="O5">
         <v>100</v>
       </c>
       <c r="P5">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q5">
         <v>100</v>
       </c>
       <c r="R5">
+        <v>100</v>
+      </c>
+      <c r="S5">
+        <v>100</v>
+      </c>
+      <c r="T5">
+        <v>100</v>
+      </c>
+      <c r="U5">
         <v>93.8</v>
       </c>
-      <c r="S5">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19">
+      <c r="V5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B6">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C6">
+        <v>100</v>
+      </c>
+      <c r="D6">
         <v>95</v>
       </c>
-      <c r="D6">
-        <v>100</v>
-      </c>
       <c r="E6">
         <v>100</v>
       </c>
@@ -3862,14 +3892,14 @@
         <v>100</v>
       </c>
       <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>100</v>
+      </c>
+      <c r="K6">
         <v>95</v>
       </c>
-      <c r="J6">
-        <v>100</v>
-      </c>
-      <c r="K6">
-        <v>100</v>
-      </c>
       <c r="L6">
         <v>100</v>
       </c>
@@ -3880,27 +3910,36 @@
         <v>100</v>
       </c>
       <c r="O6">
+        <v>100</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>100</v>
+      </c>
+      <c r="R6">
         <v>95</v>
       </c>
-      <c r="P6">
-        <v>100</v>
-      </c>
-      <c r="Q6">
-        <v>100</v>
-      </c>
-      <c r="R6">
-        <v>100</v>
-      </c>
       <c r="S6">
         <v>100</v>
       </c>
-    </row>
-    <row r="7" spans="1:19">
+      <c r="T6">
+        <v>100</v>
+      </c>
+      <c r="U6">
+        <v>100</v>
+      </c>
+      <c r="V6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22">
       <c r="A7" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B7">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C7">
         <v>100</v>
@@ -3921,7 +3960,7 @@
         <v>100</v>
       </c>
       <c r="I7">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J7">
         <v>100</v>
@@ -3942,7 +3981,7 @@
         <v>100</v>
       </c>
       <c r="P7">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q7">
         <v>100</v>
@@ -3953,13 +3992,22 @@
       <c r="S7">
         <v>100</v>
       </c>
-    </row>
-    <row r="8" spans="1:19">
+      <c r="T7">
+        <v>100</v>
+      </c>
+      <c r="U7">
+        <v>100</v>
+      </c>
+      <c r="V7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22">
       <c r="A8" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B8">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C8">
         <v>100</v>
@@ -3980,7 +4028,7 @@
         <v>100</v>
       </c>
       <c r="I8">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J8">
         <v>100</v>
@@ -4001,7 +4049,7 @@
         <v>100</v>
       </c>
       <c r="P8">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q8">
         <v>100</v>
@@ -4012,131 +4060,158 @@
       <c r="S8">
         <v>100</v>
       </c>
-    </row>
-    <row r="9" spans="1:19">
+      <c r="T8">
+        <v>100</v>
+      </c>
+      <c r="U8">
+        <v>100</v>
+      </c>
+      <c r="V8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22">
       <c r="A9" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B9">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C9">
+        <v>100</v>
+      </c>
+      <c r="D9">
         <v>90</v>
       </c>
-      <c r="D9">
-        <v>100</v>
-      </c>
       <c r="E9">
+        <v>100</v>
+      </c>
+      <c r="F9">
         <v>80</v>
       </c>
-      <c r="F9">
+      <c r="G9">
         <v>87.5</v>
       </c>
-      <c r="G9">
+      <c r="H9">
         <v>90</v>
       </c>
-      <c r="H9">
-        <v>100</v>
-      </c>
       <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>100</v>
+      </c>
+      <c r="K9">
         <v>90</v>
       </c>
-      <c r="J9">
-        <v>100</v>
-      </c>
-      <c r="K9">
+      <c r="L9">
+        <v>100</v>
+      </c>
+      <c r="M9">
         <v>80</v>
       </c>
-      <c r="L9">
+      <c r="N9">
         <v>87.5</v>
-      </c>
-      <c r="M9">
-        <v>90</v>
-      </c>
-      <c r="N9">
-        <v>100</v>
       </c>
       <c r="O9">
         <v>90</v>
       </c>
       <c r="P9">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q9">
+        <v>100</v>
+      </c>
+      <c r="R9">
+        <v>90</v>
+      </c>
+      <c r="S9">
+        <v>100</v>
+      </c>
+      <c r="T9">
         <v>80</v>
       </c>
-      <c r="R9">
+      <c r="U9">
         <v>87.5</v>
       </c>
-      <c r="S9">
+      <c r="V9">
         <v>90</v>
       </c>
     </row>
-    <row r="10" spans="1:19">
+    <row r="10" spans="1:22">
       <c r="A10" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B10">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C10">
+        <v>100</v>
+      </c>
+      <c r="D10">
         <v>95</v>
       </c>
-      <c r="D10">
-        <v>100</v>
-      </c>
       <c r="E10">
+        <v>100</v>
+      </c>
+      <c r="F10">
         <v>85</v>
       </c>
-      <c r="F10">
-        <v>100</v>
-      </c>
       <c r="G10">
+        <v>100</v>
+      </c>
+      <c r="H10">
         <v>90</v>
       </c>
-      <c r="H10">
-        <v>100</v>
-      </c>
       <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>100</v>
+      </c>
+      <c r="K10">
         <v>95</v>
       </c>
-      <c r="J10">
-        <v>100</v>
-      </c>
-      <c r="K10">
+      <c r="L10">
+        <v>100</v>
+      </c>
+      <c r="M10">
         <v>85</v>
       </c>
-      <c r="L10">
-        <v>100</v>
-      </c>
-      <c r="M10">
+      <c r="N10">
+        <v>100</v>
+      </c>
+      <c r="O10">
         <v>90</v>
       </c>
-      <c r="N10">
-        <v>100</v>
-      </c>
-      <c r="O10">
+      <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <v>100</v>
+      </c>
+      <c r="R10">
         <v>95</v>
       </c>
-      <c r="P10">
-        <v>100</v>
-      </c>
-      <c r="Q10">
+      <c r="S10">
+        <v>100</v>
+      </c>
+      <c r="T10">
         <v>85</v>
       </c>
-      <c r="R10">
-        <v>100</v>
-      </c>
-      <c r="S10">
+      <c r="U10">
+        <v>100</v>
+      </c>
+      <c r="V10">
         <v>90</v>
       </c>
     </row>
-    <row r="11" spans="1:19">
+    <row r="11" spans="1:22">
       <c r="A11" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B11">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C11">
         <v>100</v>
@@ -4157,7 +4232,7 @@
         <v>100</v>
       </c>
       <c r="I11">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J11">
         <v>100</v>
@@ -4178,7 +4253,7 @@
         <v>100</v>
       </c>
       <c r="P11">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q11">
         <v>100</v>
@@ -4189,20 +4264,29 @@
       <c r="S11">
         <v>100</v>
       </c>
-    </row>
-    <row r="12" spans="1:19">
+      <c r="T11">
+        <v>100</v>
+      </c>
+      <c r="U11">
+        <v>100</v>
+      </c>
+      <c r="V11">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22">
       <c r="A12" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B12">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C12">
+        <v>100</v>
+      </c>
+      <c r="D12">
         <v>95</v>
       </c>
-      <c r="D12">
-        <v>100</v>
-      </c>
       <c r="E12">
         <v>100</v>
       </c>
@@ -4216,14 +4300,14 @@
         <v>100</v>
       </c>
       <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>100</v>
+      </c>
+      <c r="K12">
         <v>95</v>
       </c>
-      <c r="J12">
-        <v>100</v>
-      </c>
-      <c r="K12">
-        <v>100</v>
-      </c>
       <c r="L12">
         <v>100</v>
       </c>
@@ -4234,34 +4318,43 @@
         <v>100</v>
       </c>
       <c r="O12">
+        <v>100</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="Q12">
+        <v>100</v>
+      </c>
+      <c r="R12">
         <v>95</v>
       </c>
-      <c r="P12">
-        <v>100</v>
-      </c>
-      <c r="Q12">
-        <v>100</v>
-      </c>
-      <c r="R12">
-        <v>100</v>
-      </c>
       <c r="S12">
         <v>100</v>
       </c>
-    </row>
-    <row r="13" spans="1:19">
+      <c r="T12">
+        <v>100</v>
+      </c>
+      <c r="U12">
+        <v>100</v>
+      </c>
+      <c r="V12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22">
       <c r="A13" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B13">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C13">
+        <v>100</v>
+      </c>
+      <c r="D13">
         <v>95</v>
       </c>
-      <c r="D13">
-        <v>100</v>
-      </c>
       <c r="E13">
         <v>100</v>
       </c>
@@ -4269,55 +4362,64 @@
         <v>100</v>
       </c>
       <c r="G13">
+        <v>100</v>
+      </c>
+      <c r="H13">
         <v>90</v>
       </c>
-      <c r="H13">
-        <v>100</v>
-      </c>
       <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>100</v>
+      </c>
+      <c r="K13">
         <v>95</v>
       </c>
-      <c r="J13">
-        <v>100</v>
-      </c>
-      <c r="K13">
-        <v>100</v>
-      </c>
       <c r="L13">
         <v>100</v>
       </c>
       <c r="M13">
+        <v>100</v>
+      </c>
+      <c r="N13">
+        <v>100</v>
+      </c>
+      <c r="O13">
         <v>90</v>
       </c>
-      <c r="N13">
-        <v>100</v>
-      </c>
-      <c r="O13">
+      <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="Q13">
+        <v>100</v>
+      </c>
+      <c r="R13">
         <v>95</v>
       </c>
-      <c r="P13">
-        <v>100</v>
-      </c>
-      <c r="Q13">
-        <v>100</v>
-      </c>
-      <c r="R13">
-        <v>100</v>
-      </c>
       <c r="S13">
+        <v>100</v>
+      </c>
+      <c r="T13">
+        <v>100</v>
+      </c>
+      <c r="U13">
+        <v>100</v>
+      </c>
+      <c r="V13">
         <v>90</v>
       </c>
     </row>
-    <row r="14" spans="1:19">
+    <row r="14" spans="1:22">
       <c r="A14" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B14">
+        <v>0</v>
+      </c>
+      <c r="C14">
         <v>86.7</v>
       </c>
-      <c r="C14">
-        <v>100</v>
-      </c>
       <c r="D14">
         <v>100</v>
       </c>
@@ -4325,54 +4427,63 @@
         <v>100</v>
       </c>
       <c r="F14">
+        <v>100</v>
+      </c>
+      <c r="G14">
         <v>87.5</v>
       </c>
-      <c r="G14">
-        <v>100</v>
-      </c>
       <c r="H14">
+        <v>100</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
         <v>86.7</v>
       </c>
-      <c r="I14">
-        <v>100</v>
-      </c>
-      <c r="J14">
-        <v>100</v>
-      </c>
       <c r="K14">
         <v>100</v>
       </c>
       <c r="L14">
+        <v>100</v>
+      </c>
+      <c r="M14">
+        <v>100</v>
+      </c>
+      <c r="N14">
         <v>87.5</v>
       </c>
-      <c r="M14">
-        <v>100</v>
-      </c>
-      <c r="N14">
+      <c r="O14">
+        <v>100</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14">
         <v>86.7</v>
       </c>
-      <c r="O14">
-        <v>100</v>
-      </c>
-      <c r="P14">
-        <v>100</v>
-      </c>
-      <c r="Q14">
-        <v>100</v>
-      </c>
       <c r="R14">
+        <v>100</v>
+      </c>
+      <c r="S14">
+        <v>100</v>
+      </c>
+      <c r="T14">
+        <v>100</v>
+      </c>
+      <c r="U14">
         <v>87.5</v>
       </c>
-      <c r="S14">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19">
+      <c r="V14">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22">
       <c r="A15" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C15">
         <v>100</v>
@@ -4393,7 +4504,7 @@
         <v>100</v>
       </c>
       <c r="I15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J15">
         <v>100</v>
@@ -4414,7 +4525,7 @@
         <v>100</v>
       </c>
       <c r="P15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q15">
         <v>100</v>
@@ -4425,144 +4536,171 @@
       <c r="S15">
         <v>100</v>
       </c>
-    </row>
-    <row r="16" spans="1:19">
+      <c r="T15">
+        <v>100</v>
+      </c>
+      <c r="U15">
+        <v>100</v>
+      </c>
+      <c r="V15">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22">
       <c r="A16" s="1" t="s">
         <v>25</v>
       </c>
       <c r="B16">
+        <v>0</v>
+      </c>
+      <c r="C16">
         <v>80</v>
       </c>
-      <c r="C16">
+      <c r="D16">
         <v>75</v>
       </c>
-      <c r="D16">
+      <c r="E16">
         <v>73.3</v>
       </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
       <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
         <v>81.3</v>
       </c>
-      <c r="G16">
+      <c r="H16">
         <v>60</v>
       </c>
-      <c r="H16">
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
         <v>80</v>
       </c>
-      <c r="I16">
+      <c r="K16">
         <v>75</v>
       </c>
-      <c r="J16">
+      <c r="L16">
         <v>73.3</v>
       </c>
-      <c r="K16">
-        <v>0</v>
-      </c>
-      <c r="L16">
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
         <v>81.3</v>
       </c>
-      <c r="M16">
+      <c r="O16">
         <v>60</v>
       </c>
-      <c r="N16">
+      <c r="P16">
+        <v>0</v>
+      </c>
+      <c r="Q16">
         <v>80</v>
       </c>
-      <c r="O16">
+      <c r="R16">
         <v>75</v>
       </c>
-      <c r="P16">
+      <c r="S16">
         <v>73.3</v>
       </c>
-      <c r="Q16">
-        <v>0</v>
-      </c>
-      <c r="R16">
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16">
         <v>81.3</v>
       </c>
-      <c r="S16">
+      <c r="V16">
         <v>60</v>
       </c>
     </row>
-    <row r="17" spans="1:19">
+    <row r="17" spans="1:22">
       <c r="A17" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B17">
+        <v>0</v>
+      </c>
+      <c r="C17">
         <v>93.3</v>
       </c>
-      <c r="C17">
+      <c r="D17">
         <v>95</v>
       </c>
-      <c r="D17">
-        <v>100</v>
-      </c>
       <c r="E17">
         <v>100</v>
       </c>
       <c r="F17">
+        <v>100</v>
+      </c>
+      <c r="G17">
         <v>93.8</v>
       </c>
-      <c r="G17">
-        <v>100</v>
-      </c>
       <c r="H17">
+        <v>100</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
         <v>93.3</v>
       </c>
-      <c r="I17">
+      <c r="K17">
         <v>95</v>
       </c>
-      <c r="J17">
-        <v>100</v>
-      </c>
-      <c r="K17">
-        <v>100</v>
-      </c>
       <c r="L17">
+        <v>100</v>
+      </c>
+      <c r="M17">
+        <v>100</v>
+      </c>
+      <c r="N17">
         <v>93.8</v>
       </c>
-      <c r="M17">
-        <v>100</v>
-      </c>
-      <c r="N17">
+      <c r="O17">
+        <v>100</v>
+      </c>
+      <c r="P17">
+        <v>0</v>
+      </c>
+      <c r="Q17">
         <v>93.3</v>
       </c>
-      <c r="O17">
+      <c r="R17">
         <v>95</v>
       </c>
-      <c r="P17">
-        <v>100</v>
-      </c>
-      <c r="Q17">
-        <v>100</v>
-      </c>
-      <c r="R17">
+      <c r="S17">
+        <v>100</v>
+      </c>
+      <c r="T17">
+        <v>100</v>
+      </c>
+      <c r="U17">
         <v>93.8</v>
       </c>
-      <c r="S17">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19">
+      <c r="V17">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22">
       <c r="A18" s="1" t="s">
         <v>27</v>
       </c>
       <c r="B18">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C18">
+        <v>100</v>
+      </c>
+      <c r="D18">
         <v>95</v>
       </c>
-      <c r="D18">
-        <v>100</v>
-      </c>
       <c r="E18">
+        <v>100</v>
+      </c>
+      <c r="F18">
         <v>80</v>
       </c>
-      <c r="F18">
-        <v>100</v>
-      </c>
       <c r="G18">
         <v>100</v>
       </c>
@@ -4570,281 +4708,326 @@
         <v>100</v>
       </c>
       <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>100</v>
+      </c>
+      <c r="K18">
         <v>95</v>
       </c>
-      <c r="J18">
-        <v>100</v>
-      </c>
-      <c r="K18">
+      <c r="L18">
+        <v>100</v>
+      </c>
+      <c r="M18">
         <v>80</v>
       </c>
-      <c r="L18">
-        <v>100</v>
-      </c>
-      <c r="M18">
-        <v>100</v>
-      </c>
       <c r="N18">
         <v>100</v>
       </c>
       <c r="O18">
+        <v>100</v>
+      </c>
+      <c r="P18">
+        <v>0</v>
+      </c>
+      <c r="Q18">
+        <v>100</v>
+      </c>
+      <c r="R18">
         <v>95</v>
       </c>
-      <c r="P18">
-        <v>100</v>
-      </c>
-      <c r="Q18">
+      <c r="S18">
+        <v>100</v>
+      </c>
+      <c r="T18">
         <v>80</v>
       </c>
-      <c r="R18">
-        <v>100</v>
-      </c>
-      <c r="S18">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19">
+      <c r="U18">
+        <v>100</v>
+      </c>
+      <c r="V18">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22">
       <c r="A19" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B19">
+        <v>0</v>
+      </c>
+      <c r="C19">
         <v>93.3</v>
       </c>
-      <c r="C19">
-        <v>100</v>
-      </c>
       <c r="D19">
+        <v>100</v>
+      </c>
+      <c r="E19">
         <v>86.7</v>
       </c>
-      <c r="E19">
+      <c r="F19">
         <v>80</v>
       </c>
-      <c r="F19">
-        <v>100</v>
-      </c>
       <c r="G19">
+        <v>100</v>
+      </c>
+      <c r="H19">
         <v>95</v>
       </c>
-      <c r="H19">
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
         <v>93.3</v>
       </c>
-      <c r="I19">
-        <v>100</v>
-      </c>
-      <c r="J19">
+      <c r="K19">
+        <v>100</v>
+      </c>
+      <c r="L19">
         <v>86.7</v>
       </c>
-      <c r="K19">
+      <c r="M19">
         <v>80</v>
       </c>
-      <c r="L19">
-        <v>100</v>
-      </c>
-      <c r="M19">
+      <c r="N19">
+        <v>100</v>
+      </c>
+      <c r="O19">
         <v>95</v>
       </c>
-      <c r="N19">
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19">
         <v>93.3</v>
       </c>
-      <c r="O19">
-        <v>100</v>
-      </c>
-      <c r="P19">
+      <c r="R19">
+        <v>100</v>
+      </c>
+      <c r="S19">
         <v>86.7</v>
       </c>
-      <c r="Q19">
+      <c r="T19">
         <v>80</v>
       </c>
-      <c r="R19">
-        <v>100</v>
-      </c>
-      <c r="S19">
+      <c r="U19">
+        <v>100</v>
+      </c>
+      <c r="V19">
         <v>95</v>
       </c>
     </row>
-    <row r="20" spans="1:19">
+    <row r="20" spans="1:22">
       <c r="A20" s="1" t="s">
         <v>29</v>
       </c>
       <c r="B20">
+        <v>0</v>
+      </c>
+      <c r="C20">
         <v>86.7</v>
       </c>
-      <c r="C20">
+      <c r="D20">
         <v>90</v>
       </c>
-      <c r="D20">
+      <c r="E20">
         <v>86.7</v>
       </c>
-      <c r="E20">
-        <v>100</v>
-      </c>
       <c r="F20">
+        <v>100</v>
+      </c>
+      <c r="G20">
         <v>87.5</v>
       </c>
-      <c r="G20">
+      <c r="H20">
         <v>85</v>
       </c>
-      <c r="H20">
-        <v>86.7</v>
-      </c>
       <c r="I20">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="J20">
         <v>86.7</v>
       </c>
       <c r="K20">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="L20">
+        <v>86.7</v>
+      </c>
+      <c r="M20">
+        <v>100</v>
+      </c>
+      <c r="N20">
         <v>87.5</v>
       </c>
-      <c r="M20">
+      <c r="O20">
         <v>85</v>
       </c>
-      <c r="N20">
+      <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="Q20">
         <v>86.7</v>
       </c>
-      <c r="O20">
+      <c r="R20">
         <v>90</v>
       </c>
-      <c r="P20">
+      <c r="S20">
         <v>86.7</v>
       </c>
-      <c r="Q20">
-        <v>100</v>
-      </c>
-      <c r="R20">
+      <c r="T20">
+        <v>100</v>
+      </c>
+      <c r="U20">
         <v>87.5</v>
       </c>
-      <c r="S20">
+      <c r="V20">
         <v>85</v>
       </c>
     </row>
-    <row r="21" spans="1:19">
+    <row r="21" spans="1:22">
       <c r="A21" s="1" t="s">
         <v>30</v>
       </c>
       <c r="B21">
+        <v>0</v>
+      </c>
+      <c r="C21">
         <v>86.7</v>
       </c>
-      <c r="C21">
+      <c r="D21">
         <v>95</v>
       </c>
-      <c r="D21">
-        <v>100</v>
-      </c>
       <c r="E21">
+        <v>100</v>
+      </c>
+      <c r="F21">
         <v>80</v>
       </c>
-      <c r="F21">
+      <c r="G21">
         <v>93.8</v>
       </c>
-      <c r="G21">
+      <c r="H21">
         <v>90</v>
       </c>
-      <c r="H21">
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
         <v>86.7</v>
       </c>
-      <c r="I21">
+      <c r="K21">
         <v>95</v>
       </c>
-      <c r="J21">
-        <v>100</v>
-      </c>
-      <c r="K21">
+      <c r="L21">
+        <v>100</v>
+      </c>
+      <c r="M21">
         <v>80</v>
       </c>
-      <c r="L21">
+      <c r="N21">
         <v>93.8</v>
       </c>
-      <c r="M21">
+      <c r="O21">
         <v>90</v>
       </c>
-      <c r="N21">
+      <c r="P21">
+        <v>0</v>
+      </c>
+      <c r="Q21">
         <v>86.7</v>
       </c>
-      <c r="O21">
+      <c r="R21">
         <v>95</v>
       </c>
-      <c r="P21">
-        <v>100</v>
-      </c>
-      <c r="Q21">
+      <c r="S21">
+        <v>100</v>
+      </c>
+      <c r="T21">
         <v>80</v>
       </c>
-      <c r="R21">
+      <c r="U21">
         <v>93.8</v>
       </c>
-      <c r="S21">
+      <c r="V21">
         <v>90</v>
       </c>
     </row>
-    <row r="22" spans="1:19">
+    <row r="22" spans="1:22">
       <c r="A22" s="1" t="s">
         <v>31</v>
       </c>
       <c r="B22">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C22">
+        <v>100</v>
+      </c>
+      <c r="D22">
         <v>95</v>
       </c>
-      <c r="D22">
-        <v>100</v>
-      </c>
       <c r="E22">
         <v>100</v>
       </c>
       <c r="F22">
+        <v>100</v>
+      </c>
+      <c r="G22">
         <v>87.5</v>
       </c>
-      <c r="G22">
-        <v>100</v>
-      </c>
       <c r="H22">
         <v>100</v>
       </c>
       <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>100</v>
+      </c>
+      <c r="K22">
         <v>95</v>
       </c>
-      <c r="J22">
-        <v>100</v>
-      </c>
-      <c r="K22">
-        <v>100</v>
-      </c>
       <c r="L22">
+        <v>100</v>
+      </c>
+      <c r="M22">
+        <v>100</v>
+      </c>
+      <c r="N22">
         <v>87.5</v>
       </c>
-      <c r="M22">
-        <v>100</v>
-      </c>
-      <c r="N22">
-        <v>100</v>
-      </c>
       <c r="O22">
+        <v>100</v>
+      </c>
+      <c r="P22">
+        <v>0</v>
+      </c>
+      <c r="Q22">
+        <v>100</v>
+      </c>
+      <c r="R22">
         <v>95</v>
       </c>
-      <c r="P22">
-        <v>100</v>
-      </c>
-      <c r="Q22">
-        <v>100</v>
-      </c>
-      <c r="R22">
+      <c r="S22">
+        <v>100</v>
+      </c>
+      <c r="T22">
+        <v>100</v>
+      </c>
+      <c r="U22">
         <v>87.5</v>
       </c>
-      <c r="S22">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="23" spans="1:19">
+      <c r="V22">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22">
       <c r="A23" s="1" t="s">
         <v>32</v>
       </c>
       <c r="B23">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C23">
         <v>100</v>
@@ -4856,16 +5039,16 @@
         <v>100</v>
       </c>
       <c r="F23">
+        <v>100</v>
+      </c>
+      <c r="G23">
         <v>93.8</v>
       </c>
-      <c r="G23">
-        <v>100</v>
-      </c>
       <c r="H23">
         <v>100</v>
       </c>
       <c r="I23">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J23">
         <v>100</v>
@@ -4874,66 +5057,75 @@
         <v>100</v>
       </c>
       <c r="L23">
+        <v>100</v>
+      </c>
+      <c r="M23">
+        <v>100</v>
+      </c>
+      <c r="N23">
         <v>93.8</v>
       </c>
-      <c r="M23">
-        <v>100</v>
-      </c>
-      <c r="N23">
-        <v>100</v>
-      </c>
       <c r="O23">
         <v>100</v>
       </c>
       <c r="P23">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q23">
         <v>100</v>
       </c>
       <c r="R23">
+        <v>100</v>
+      </c>
+      <c r="S23">
+        <v>100</v>
+      </c>
+      <c r="T23">
+        <v>100</v>
+      </c>
+      <c r="U23">
         <v>93.8</v>
       </c>
-      <c r="S23">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="24" spans="1:19">
+      <c r="V23">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22">
       <c r="A24" s="1" t="s">
         <v>33</v>
       </c>
       <c r="B24">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C24">
+        <v>100</v>
+      </c>
+      <c r="D24">
         <v>95</v>
       </c>
-      <c r="D24">
+      <c r="E24">
         <v>93.3</v>
       </c>
-      <c r="E24">
+      <c r="F24">
         <v>85</v>
       </c>
-      <c r="F24">
-        <v>100</v>
-      </c>
       <c r="G24">
+        <v>100</v>
+      </c>
+      <c r="H24">
         <v>85</v>
       </c>
-      <c r="H24">
-        <v>100</v>
-      </c>
       <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>100</v>
+      </c>
+      <c r="K24">
         <v>95</v>
       </c>
-      <c r="J24">
+      <c r="L24">
         <v>93.3</v>
-      </c>
-      <c r="K24">
-        <v>85</v>
-      </c>
-      <c r="L24">
-        <v>100</v>
       </c>
       <c r="M24">
         <v>85</v>
@@ -4942,27 +5134,36 @@
         <v>100</v>
       </c>
       <c r="O24">
+        <v>85</v>
+      </c>
+      <c r="P24">
+        <v>0</v>
+      </c>
+      <c r="Q24">
+        <v>100</v>
+      </c>
+      <c r="R24">
         <v>95</v>
       </c>
-      <c r="P24">
+      <c r="S24">
         <v>93.3</v>
       </c>
-      <c r="Q24">
+      <c r="T24">
         <v>85</v>
       </c>
-      <c r="R24">
-        <v>100</v>
-      </c>
-      <c r="S24">
+      <c r="U24">
+        <v>100</v>
+      </c>
+      <c r="V24">
         <v>85</v>
       </c>
     </row>
-    <row r="25" spans="1:19">
+    <row r="25" spans="1:22">
       <c r="A25" s="1" t="s">
         <v>34</v>
       </c>
       <c r="B25">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C25">
         <v>100</v>
@@ -4983,7 +5184,7 @@
         <v>100</v>
       </c>
       <c r="I25">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J25">
         <v>100</v>
@@ -5004,7 +5205,7 @@
         <v>100</v>
       </c>
       <c r="P25">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q25">
         <v>100</v>
@@ -5015,72 +5216,90 @@
       <c r="S25">
         <v>100</v>
       </c>
-    </row>
-    <row r="26" spans="1:19">
+      <c r="T25">
+        <v>100</v>
+      </c>
+      <c r="U25">
+        <v>100</v>
+      </c>
+      <c r="V25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22">
       <c r="A26" s="1" t="s">
         <v>35</v>
       </c>
       <c r="B26">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C26">
+        <v>100</v>
+      </c>
+      <c r="D26">
         <v>95</v>
       </c>
-      <c r="D26">
-        <v>100</v>
-      </c>
       <c r="E26">
         <v>100</v>
       </c>
       <c r="F26">
+        <v>100</v>
+      </c>
+      <c r="G26">
         <v>93.8</v>
       </c>
-      <c r="G26">
-        <v>100</v>
-      </c>
       <c r="H26">
         <v>100</v>
       </c>
       <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>100</v>
+      </c>
+      <c r="K26">
         <v>95</v>
       </c>
-      <c r="J26">
-        <v>100</v>
-      </c>
-      <c r="K26">
-        <v>100</v>
-      </c>
       <c r="L26">
+        <v>100</v>
+      </c>
+      <c r="M26">
+        <v>100</v>
+      </c>
+      <c r="N26">
         <v>93.8</v>
       </c>
-      <c r="M26">
-        <v>100</v>
-      </c>
-      <c r="N26">
-        <v>100</v>
-      </c>
       <c r="O26">
+        <v>100</v>
+      </c>
+      <c r="P26">
+        <v>0</v>
+      </c>
+      <c r="Q26">
+        <v>100</v>
+      </c>
+      <c r="R26">
         <v>95</v>
       </c>
-      <c r="P26">
-        <v>100</v>
-      </c>
-      <c r="Q26">
-        <v>100</v>
-      </c>
-      <c r="R26">
+      <c r="S26">
+        <v>100</v>
+      </c>
+      <c r="T26">
+        <v>100</v>
+      </c>
+      <c r="U26">
         <v>93.8</v>
       </c>
-      <c r="S26">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="27" spans="1:19">
+      <c r="V26">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22">
       <c r="A27" s="1" t="s">
         <v>36</v>
       </c>
       <c r="B27">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C27">
         <v>100</v>
@@ -5092,16 +5311,16 @@
         <v>100</v>
       </c>
       <c r="F27">
+        <v>100</v>
+      </c>
+      <c r="G27">
         <v>93.8</v>
       </c>
-      <c r="G27">
-        <v>100</v>
-      </c>
       <c r="H27">
         <v>100</v>
       </c>
       <c r="I27">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J27">
         <v>100</v>
@@ -5110,105 +5329,123 @@
         <v>100</v>
       </c>
       <c r="L27">
+        <v>100</v>
+      </c>
+      <c r="M27">
+        <v>100</v>
+      </c>
+      <c r="N27">
         <v>93.8</v>
       </c>
-      <c r="M27">
-        <v>100</v>
-      </c>
-      <c r="N27">
-        <v>100</v>
-      </c>
       <c r="O27">
         <v>100</v>
       </c>
       <c r="P27">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q27">
         <v>100</v>
       </c>
       <c r="R27">
+        <v>100</v>
+      </c>
+      <c r="S27">
+        <v>100</v>
+      </c>
+      <c r="T27">
+        <v>100</v>
+      </c>
+      <c r="U27">
         <v>93.8</v>
       </c>
-      <c r="S27">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="28" spans="1:19">
+      <c r="V27">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22">
       <c r="A28" s="1" t="s">
         <v>37</v>
       </c>
       <c r="B28">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C28">
+        <v>100</v>
+      </c>
+      <c r="D28">
         <v>95</v>
       </c>
-      <c r="D28">
-        <v>100</v>
-      </c>
       <c r="E28">
         <v>100</v>
       </c>
       <c r="F28">
+        <v>100</v>
+      </c>
+      <c r="G28">
         <v>93.8</v>
       </c>
-      <c r="G28">
+      <c r="H28">
         <v>90</v>
       </c>
-      <c r="H28">
-        <v>100</v>
-      </c>
       <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>100</v>
+      </c>
+      <c r="K28">
         <v>95</v>
       </c>
-      <c r="J28">
-        <v>100</v>
-      </c>
-      <c r="K28">
-        <v>100</v>
-      </c>
       <c r="L28">
+        <v>100</v>
+      </c>
+      <c r="M28">
+        <v>100</v>
+      </c>
+      <c r="N28">
         <v>93.8</v>
       </c>
-      <c r="M28">
+      <c r="O28">
         <v>90</v>
       </c>
-      <c r="N28">
-        <v>100</v>
-      </c>
-      <c r="O28">
+      <c r="P28">
+        <v>0</v>
+      </c>
+      <c r="Q28">
+        <v>100</v>
+      </c>
+      <c r="R28">
         <v>95</v>
       </c>
-      <c r="P28">
-        <v>100</v>
-      </c>
-      <c r="Q28">
-        <v>100</v>
-      </c>
-      <c r="R28">
+      <c r="S28">
+        <v>100</v>
+      </c>
+      <c r="T28">
+        <v>100</v>
+      </c>
+      <c r="U28">
         <v>93.8</v>
       </c>
-      <c r="S28">
+      <c r="V28">
         <v>90</v>
       </c>
     </row>
-    <row r="29" spans="1:19">
+    <row r="29" spans="1:22">
       <c r="A29" s="1" t="s">
         <v>38</v>
       </c>
       <c r="B29">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C29">
         <v>100</v>
       </c>
       <c r="D29">
+        <v>100</v>
+      </c>
+      <c r="E29">
         <v>93.3</v>
       </c>
-      <c r="E29">
-        <v>100</v>
-      </c>
       <c r="F29">
         <v>100</v>
       </c>
@@ -5219,17 +5456,17 @@
         <v>100</v>
       </c>
       <c r="I29">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J29">
+        <v>100</v>
+      </c>
+      <c r="K29">
+        <v>100</v>
+      </c>
+      <c r="L29">
         <v>93.3</v>
       </c>
-      <c r="K29">
-        <v>100</v>
-      </c>
-      <c r="L29">
-        <v>100</v>
-      </c>
       <c r="M29">
         <v>100</v>
       </c>
@@ -5240,24 +5477,33 @@
         <v>100</v>
       </c>
       <c r="P29">
+        <v>0</v>
+      </c>
+      <c r="Q29">
+        <v>100</v>
+      </c>
+      <c r="R29">
+        <v>100</v>
+      </c>
+      <c r="S29">
         <v>93.3</v>
       </c>
-      <c r="Q29">
-        <v>100</v>
-      </c>
-      <c r="R29">
-        <v>100</v>
-      </c>
-      <c r="S29">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="30" spans="1:19">
+      <c r="T29">
+        <v>100</v>
+      </c>
+      <c r="U29">
+        <v>100</v>
+      </c>
+      <c r="V29">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22">
       <c r="A30" s="1" t="s">
         <v>39</v>
       </c>
       <c r="B30">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C30">
         <v>100</v>
@@ -5278,7 +5524,7 @@
         <v>100</v>
       </c>
       <c r="I30">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J30">
         <v>100</v>
@@ -5299,7 +5545,7 @@
         <v>100</v>
       </c>
       <c r="P30">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q30">
         <v>100</v>
@@ -5310,72 +5556,90 @@
       <c r="S30">
         <v>100</v>
       </c>
-    </row>
-    <row r="31" spans="1:19">
+      <c r="T30">
+        <v>100</v>
+      </c>
+      <c r="U30">
+        <v>100</v>
+      </c>
+      <c r="V30">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22">
       <c r="A31" s="1" t="s">
         <v>40</v>
       </c>
       <c r="B31">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C31">
+        <v>100</v>
+      </c>
+      <c r="D31">
         <v>95</v>
       </c>
-      <c r="D31">
-        <v>100</v>
-      </c>
       <c r="E31">
+        <v>100</v>
+      </c>
+      <c r="F31">
         <v>90</v>
       </c>
-      <c r="F31">
+      <c r="G31">
         <v>93.8</v>
       </c>
-      <c r="G31">
-        <v>100</v>
-      </c>
       <c r="H31">
         <v>100</v>
       </c>
       <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>100</v>
+      </c>
+      <c r="K31">
         <v>95</v>
       </c>
-      <c r="J31">
-        <v>100</v>
-      </c>
-      <c r="K31">
+      <c r="L31">
+        <v>100</v>
+      </c>
+      <c r="M31">
         <v>90</v>
       </c>
-      <c r="L31">
+      <c r="N31">
         <v>93.8</v>
       </c>
-      <c r="M31">
-        <v>100</v>
-      </c>
-      <c r="N31">
-        <v>100</v>
-      </c>
       <c r="O31">
+        <v>100</v>
+      </c>
+      <c r="P31">
+        <v>0</v>
+      </c>
+      <c r="Q31">
+        <v>100</v>
+      </c>
+      <c r="R31">
         <v>95</v>
       </c>
-      <c r="P31">
-        <v>100</v>
-      </c>
-      <c r="Q31">
+      <c r="S31">
+        <v>100</v>
+      </c>
+      <c r="T31">
         <v>90</v>
       </c>
-      <c r="R31">
+      <c r="U31">
         <v>93.8</v>
       </c>
-      <c r="S31">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="32" spans="1:19">
+      <c r="V31">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22">
       <c r="A32" s="1" t="s">
         <v>41</v>
       </c>
       <c r="B32">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C32">
         <v>100</v>
@@ -5384,11 +5648,11 @@
         <v>100</v>
       </c>
       <c r="E32">
+        <v>100</v>
+      </c>
+      <c r="F32">
         <v>90</v>
       </c>
-      <c r="F32">
-        <v>100</v>
-      </c>
       <c r="G32">
         <v>100</v>
       </c>
@@ -5396,20 +5660,20 @@
         <v>100</v>
       </c>
       <c r="I32">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J32">
         <v>100</v>
       </c>
       <c r="K32">
+        <v>100</v>
+      </c>
+      <c r="L32">
+        <v>100</v>
+      </c>
+      <c r="M32">
         <v>90</v>
       </c>
-      <c r="L32">
-        <v>100</v>
-      </c>
-      <c r="M32">
-        <v>100</v>
-      </c>
       <c r="N32">
         <v>100</v>
       </c>
@@ -5417,24 +5681,33 @@
         <v>100</v>
       </c>
       <c r="P32">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q32">
+        <v>100</v>
+      </c>
+      <c r="R32">
+        <v>100</v>
+      </c>
+      <c r="S32">
+        <v>100</v>
+      </c>
+      <c r="T32">
         <v>90</v>
       </c>
-      <c r="R32">
-        <v>100</v>
-      </c>
-      <c r="S32">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="33" spans="1:19">
+      <c r="U32">
+        <v>100</v>
+      </c>
+      <c r="V32">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" spans="1:22">
       <c r="A33" s="1" t="s">
         <v>42</v>
       </c>
       <c r="B33">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C33">
         <v>100</v>
@@ -5446,16 +5719,16 @@
         <v>100</v>
       </c>
       <c r="F33">
+        <v>100</v>
+      </c>
+      <c r="G33">
         <v>93.8</v>
       </c>
-      <c r="G33">
-        <v>100</v>
-      </c>
       <c r="H33">
         <v>100</v>
       </c>
       <c r="I33">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J33">
         <v>100</v>
@@ -5464,35 +5737,44 @@
         <v>100</v>
       </c>
       <c r="L33">
+        <v>100</v>
+      </c>
+      <c r="M33">
+        <v>100</v>
+      </c>
+      <c r="N33">
         <v>93.8</v>
       </c>
-      <c r="M33">
-        <v>100</v>
-      </c>
-      <c r="N33">
-        <v>100</v>
-      </c>
       <c r="O33">
         <v>100</v>
       </c>
       <c r="P33">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q33">
         <v>100</v>
       </c>
       <c r="R33">
+        <v>100</v>
+      </c>
+      <c r="S33">
+        <v>100</v>
+      </c>
+      <c r="T33">
+        <v>100</v>
+      </c>
+      <c r="U33">
         <v>93.8</v>
       </c>
-      <c r="S33">
+      <c r="V33">
         <v>100</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="H1:M1"/>
-    <mergeCell ref="N1:S1"/>
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="I1:O1"/>
+    <mergeCell ref="P1:V1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/grupos/1FM - Estadisticos 20231.xlsx
+++ b/grupos/1FM - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="95">
   <si>
     <t>Materia</t>
   </si>
@@ -188,27 +188,27 @@
     <t>Recursos socioemocionales I</t>
   </si>
   <si>
+    <t>Duran Amezcua María Angélica</t>
+  </si>
+  <si>
+    <t>Herrera Serrano Mayra Iliana</t>
+  </si>
+  <si>
     <t>González Sánchez Rene Aurelio</t>
   </si>
   <si>
-    <t>Duran Amezcua María Angélica</t>
-  </si>
-  <si>
     <t>Ochoa Martínez Mayeli</t>
   </si>
   <si>
-    <t>Herrera Serrano Mayra Iliana</t>
-  </si>
-  <si>
     <t>Velasco Sánchez David</t>
   </si>
   <si>
+    <t>Moreno Aroyo Anél</t>
+  </si>
+  <si>
     <t>Rosas Aguilar Claudia Leonor</t>
   </si>
   <si>
-    <t>Moreno Aroyo Anél</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -221,154 +221,64 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>ABREGO</t>
-  </si>
-  <si>
-    <t>ANGEL</t>
-  </si>
-  <si>
-    <t>BONILLA</t>
-  </si>
-  <si>
     <t>CRUZ</t>
   </si>
   <si>
+    <t>MELO</t>
+  </si>
+  <si>
+    <t>MOLINA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>RIOS</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>NIEVES</t>
+  </si>
+  <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>LARRACILLA</t>
-  </si>
-  <si>
-    <t>MELO</t>
-  </si>
-  <si>
-    <t>MIXCOHUA</t>
-  </si>
-  <si>
-    <t>MOLINA</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>RIOS</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>SALAZAR</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>VELUETA</t>
-  </si>
-  <si>
-    <t>VIVANCO</t>
-  </si>
-  <si>
-    <t>ZGAIP</t>
-  </si>
-  <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
-    <t>TOLENTINO</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>NIEVES</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
     <t>TETLA</t>
   </si>
   <si>
-    <t>AMADOR</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>TENCHIPE</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>COXCAHUA</t>
-  </si>
-  <si>
     <t>MONTIEL</t>
   </si>
   <si>
     <t>CORREA</t>
   </si>
   <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>OJEDA</t>
-  </si>
-  <si>
-    <t>SULU ALAN</t>
-  </si>
-  <si>
-    <t>JOSE ANTONIO</t>
-  </si>
-  <si>
-    <t>MIGUEL ANGEL</t>
-  </si>
-  <si>
     <t>ESTRELLA ESMERALDA</t>
   </si>
   <si>
     <t>ESTRELLA RUBI</t>
   </si>
   <si>
-    <t>EIZA YAMILETH</t>
-  </si>
-  <si>
-    <t>INYANIT</t>
+    <t>KENYA MARIANA</t>
+  </si>
+  <si>
+    <t>LEONARDO GABRIEL</t>
   </si>
   <si>
     <t>JAIR</t>
@@ -377,42 +287,12 @@
     <t>DORIAN ALEXANDER</t>
   </si>
   <si>
-    <t>JUAN PABLO</t>
-  </si>
-  <si>
     <t>HECTOR</t>
   </si>
   <si>
-    <t>JOSELYN</t>
-  </si>
-  <si>
-    <t>KEVIN IVAN</t>
-  </si>
-  <si>
-    <t>KEIRA</t>
-  </si>
-  <si>
-    <t>MONICA</t>
-  </si>
-  <si>
-    <t>KENYA MARIANA</t>
-  </si>
-  <si>
-    <t>YAMILETH</t>
-  </si>
-  <si>
-    <t>LEONARDO GABRIEL</t>
-  </si>
-  <si>
     <t>SALMA JANET</t>
   </si>
   <si>
-    <t>MARCO</t>
-  </si>
-  <si>
-    <t>VICTOR JESUS</t>
-  </si>
-  <si>
     <t>ELIUD EDUARDO</t>
   </si>
   <si>
@@ -422,22 +302,7 @@
     <t>JONATHAN ISAI</t>
   </si>
   <si>
-    <t>MARIEL</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
-  </si>
-  <si>
     <t>JUAN CARLOS</t>
-  </si>
-  <si>
-    <t>DANNAE ADALID</t>
-  </si>
-  <si>
-    <t>LUIS AARON</t>
-  </si>
-  <si>
-    <t>ADAIR DE JESUS</t>
   </si>
 </sst>
 </file>
@@ -943,7 +808,7 @@
         <v>13</v>
       </c>
       <c r="B4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C4">
         <v>5</v>
@@ -967,16 +832,16 @@
         <v>-1</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -1006,7 +871,7 @@
         <v>-1</v>
       </c>
       <c r="W4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X4">
         <v>5</v>
@@ -1015,10 +880,10 @@
         <v>5</v>
       </c>
       <c r="Z4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB4">
         <v>7</v>
@@ -1032,7 +897,7 @@
         <v>14</v>
       </c>
       <c r="B5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C5">
         <v>8</v>
@@ -1056,16 +921,16 @@
         <v>-1</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1095,19 +960,19 @@
         <v>-1</v>
       </c>
       <c r="W5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y5">
         <v>10</v>
       </c>
       <c r="Z5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB5">
         <v>10</v>
@@ -1121,7 +986,7 @@
         <v>15</v>
       </c>
       <c r="B6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C6">
         <v>7</v>
@@ -1145,16 +1010,16 @@
         <v>-1</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1184,16 +1049,16 @@
         <v>-1</v>
       </c>
       <c r="W6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y6">
         <v>9</v>
       </c>
       <c r="Z6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA6">
         <v>7</v>
@@ -1210,7 +1075,7 @@
         <v>16</v>
       </c>
       <c r="B7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C7">
         <v>5</v>
@@ -1234,16 +1099,16 @@
         <v>-1</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1273,19 +1138,19 @@
         <v>-1</v>
       </c>
       <c r="W7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X7">
         <v>5</v>
       </c>
       <c r="Y7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z7">
         <v>8</v>
       </c>
       <c r="AA7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB7">
         <v>10</v>
@@ -1299,13 +1164,13 @@
         <v>17</v>
       </c>
       <c r="B8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C8">
         <v>5</v>
       </c>
       <c r="D8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E8">
         <v>8</v>
@@ -1323,16 +1188,16 @@
         <v>-1</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1362,13 +1227,13 @@
         <v>-1</v>
       </c>
       <c r="W8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X8">
         <v>5</v>
       </c>
       <c r="Y8">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Z8">
         <v>8</v>
@@ -1388,7 +1253,7 @@
         <v>18</v>
       </c>
       <c r="B9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C9">
         <v>5</v>
@@ -1412,16 +1277,16 @@
         <v>-1</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1451,7 +1316,7 @@
         <v>-1</v>
       </c>
       <c r="W9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X9">
         <v>5</v>
@@ -1477,7 +1342,7 @@
         <v>19</v>
       </c>
       <c r="B10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C10">
         <v>8</v>
@@ -1501,16 +1366,16 @@
         <v>-1</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1540,19 +1405,19 @@
         <v>-1</v>
       </c>
       <c r="W10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z10">
         <v>10</v>
       </c>
       <c r="AA10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB10">
         <v>10</v>
@@ -1566,7 +1431,7 @@
         <v>20</v>
       </c>
       <c r="B11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C11">
         <v>6</v>
@@ -1590,16 +1455,16 @@
         <v>-1</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1629,10 +1494,10 @@
         <v>-1</v>
       </c>
       <c r="W11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X11">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y11">
         <v>9</v>
@@ -1655,7 +1520,7 @@
         <v>21</v>
       </c>
       <c r="B12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C12">
         <v>6</v>
@@ -1679,16 +1544,16 @@
         <v>-1</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1718,16 +1583,16 @@
         <v>-1</v>
       </c>
       <c r="W12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA12">
         <v>5</v>
@@ -1744,7 +1609,7 @@
         <v>22</v>
       </c>
       <c r="B13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C13">
         <v>7</v>
@@ -1768,16 +1633,16 @@
         <v>-1</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1807,7 +1672,7 @@
         <v>-1</v>
       </c>
       <c r="W13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X13">
         <v>7</v>
@@ -1816,10 +1681,10 @@
         <v>6</v>
       </c>
       <c r="Z13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA13">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB13">
         <v>10</v>
@@ -1833,7 +1698,7 @@
         <v>23</v>
       </c>
       <c r="B14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C14">
         <v>6</v>
@@ -1857,16 +1722,16 @@
         <v>-1</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1896,19 +1761,19 @@
         <v>-1</v>
       </c>
       <c r="W14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y14">
         <v>5</v>
       </c>
       <c r="Z14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB14">
         <v>10</v>
@@ -1922,7 +1787,7 @@
         <v>24</v>
       </c>
       <c r="B15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C15">
         <v>6</v>
@@ -1946,16 +1811,16 @@
         <v>-1</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1985,16 +1850,16 @@
         <v>-1</v>
       </c>
       <c r="W15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA15">
         <v>5</v>
@@ -2011,7 +1876,7 @@
         <v>25</v>
       </c>
       <c r="B16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C16">
         <v>5</v>
@@ -2035,16 +1900,16 @@
         <v>-1</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -2074,7 +1939,7 @@
         <v>-1</v>
       </c>
       <c r="W16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X16">
         <v>5</v>
@@ -2083,7 +1948,7 @@
         <v>5</v>
       </c>
       <c r="Z16">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA16">
         <v>5</v>
@@ -2100,7 +1965,7 @@
         <v>26</v>
       </c>
       <c r="B17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C17">
         <v>8</v>
@@ -2124,16 +1989,16 @@
         <v>-1</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -2163,7 +2028,7 @@
         <v>-1</v>
       </c>
       <c r="W17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X17">
         <v>8</v>
@@ -2175,7 +2040,7 @@
         <v>10</v>
       </c>
       <c r="AA17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB17">
         <v>10</v>
@@ -2189,7 +2054,7 @@
         <v>27</v>
       </c>
       <c r="B18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C18">
         <v>6</v>
@@ -2213,16 +2078,16 @@
         <v>-1</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2252,7 +2117,7 @@
         <v>-1</v>
       </c>
       <c r="W18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X18">
         <v>6</v>
@@ -2278,7 +2143,7 @@
         <v>28</v>
       </c>
       <c r="B19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C19">
         <v>5</v>
@@ -2302,16 +2167,16 @@
         <v>-1</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2341,16 +2206,16 @@
         <v>-1</v>
       </c>
       <c r="W19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y19">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA19">
         <v>5</v>
@@ -2367,7 +2232,7 @@
         <v>29</v>
       </c>
       <c r="B20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C20">
         <v>5</v>
@@ -2391,16 +2256,16 @@
         <v>-1</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2430,19 +2295,19 @@
         <v>-1</v>
       </c>
       <c r="W20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y20">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Z20">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA20">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AB20">
         <v>10</v>
@@ -2456,7 +2321,7 @@
         <v>30</v>
       </c>
       <c r="B21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C21">
         <v>5</v>
@@ -2480,16 +2345,16 @@
         <v>-1</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2519,7 +2384,7 @@
         <v>-1</v>
       </c>
       <c r="W21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X21">
         <v>5</v>
@@ -2528,7 +2393,7 @@
         <v>6</v>
       </c>
       <c r="Z21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA21">
         <v>5</v>
@@ -2545,7 +2410,7 @@
         <v>31</v>
       </c>
       <c r="B22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C22">
         <v>6</v>
@@ -2569,16 +2434,16 @@
         <v>-1</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2608,13 +2473,13 @@
         <v>-1</v>
       </c>
       <c r="W22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X22">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z22">
         <v>8</v>
@@ -2634,7 +2499,7 @@
         <v>32</v>
       </c>
       <c r="B23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C23">
         <v>5</v>
@@ -2658,16 +2523,16 @@
         <v>-1</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2697,7 +2562,7 @@
         <v>-1</v>
       </c>
       <c r="W23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X23">
         <v>5</v>
@@ -2706,7 +2571,7 @@
         <v>5</v>
       </c>
       <c r="Z23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA23">
         <v>5</v>
@@ -2723,7 +2588,7 @@
         <v>33</v>
       </c>
       <c r="B24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C24">
         <v>5</v>
@@ -2747,16 +2612,16 @@
         <v>-1</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2786,16 +2651,16 @@
         <v>-1</v>
       </c>
       <c r="W24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X24">
         <v>5</v>
       </c>
       <c r="Y24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA24">
         <v>5</v>
@@ -2812,7 +2677,7 @@
         <v>34</v>
       </c>
       <c r="B25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C25">
         <v>5</v>
@@ -2836,16 +2701,16 @@
         <v>-1</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2875,13 +2740,13 @@
         <v>-1</v>
       </c>
       <c r="W25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X25">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y25">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z25">
         <v>9</v>
@@ -2901,7 +2766,7 @@
         <v>35</v>
       </c>
       <c r="B26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C26">
         <v>5</v>
@@ -2925,16 +2790,16 @@
         <v>-1</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2964,16 +2829,16 @@
         <v>-1</v>
       </c>
       <c r="W26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X26">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y26">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA26">
         <v>5</v>
@@ -2990,7 +2855,7 @@
         <v>36</v>
       </c>
       <c r="B27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C27">
         <v>6</v>
@@ -3014,16 +2879,16 @@
         <v>-1</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -3053,7 +2918,7 @@
         <v>-1</v>
       </c>
       <c r="W27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X27">
         <v>6</v>
@@ -3079,7 +2944,7 @@
         <v>37</v>
       </c>
       <c r="B28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C28">
         <v>9</v>
@@ -3103,16 +2968,16 @@
         <v>-1</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -3142,7 +3007,7 @@
         <v>-1</v>
       </c>
       <c r="W28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X28">
         <v>9</v>
@@ -3154,7 +3019,7 @@
         <v>10</v>
       </c>
       <c r="AA28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB28">
         <v>10</v>
@@ -3168,7 +3033,7 @@
         <v>38</v>
       </c>
       <c r="B29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C29">
         <v>7</v>
@@ -3192,16 +3057,16 @@
         <v>-1</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -3231,16 +3096,16 @@
         <v>-1</v>
       </c>
       <c r="W29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA29">
         <v>10</v>
@@ -3257,7 +3122,7 @@
         <v>39</v>
       </c>
       <c r="B30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C30">
         <v>6</v>
@@ -3281,16 +3146,16 @@
         <v>-1</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -3320,7 +3185,7 @@
         <v>-1</v>
       </c>
       <c r="W30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X30">
         <v>6</v>
@@ -3332,7 +3197,7 @@
         <v>8</v>
       </c>
       <c r="AA30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB30">
         <v>10</v>
@@ -3346,7 +3211,7 @@
         <v>40</v>
       </c>
       <c r="B31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C31">
         <v>5</v>
@@ -3370,16 +3235,16 @@
         <v>-1</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -3409,16 +3274,16 @@
         <v>-1</v>
       </c>
       <c r="W31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X31">
         <v>5</v>
       </c>
       <c r="Y31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z31">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA31">
         <v>5</v>
@@ -3435,7 +3300,7 @@
         <v>41</v>
       </c>
       <c r="B32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C32">
         <v>5</v>
@@ -3459,16 +3324,16 @@
         <v>-1</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3498,7 +3363,7 @@
         <v>-1</v>
       </c>
       <c r="W32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X32">
         <v>5</v>
@@ -3524,7 +3389,7 @@
         <v>42</v>
       </c>
       <c r="B33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C33">
         <v>5</v>
@@ -3548,16 +3413,16 @@
         <v>-1</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3587,7 +3452,7 @@
         <v>-1</v>
       </c>
       <c r="W33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X33">
         <v>5</v>
@@ -3735,7 +3600,7 @@
         <v>13</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C4">
         <v>100</v>
@@ -3756,13 +3621,13 @@
         <v>90</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J4">
         <v>100</v>
       </c>
       <c r="K4">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="L4">
         <v>100</v>
@@ -3777,13 +3642,13 @@
         <v>90</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q4">
         <v>100</v>
       </c>
       <c r="R4">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="S4">
         <v>100</v>
@@ -3803,7 +3668,7 @@
         <v>14</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C5">
         <v>100</v>
@@ -3824,7 +3689,7 @@
         <v>100</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J5">
         <v>100</v>
@@ -3845,7 +3710,7 @@
         <v>100</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q5">
         <v>100</v>
@@ -3871,7 +3736,7 @@
         <v>15</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C6">
         <v>100</v>
@@ -3892,7 +3757,7 @@
         <v>100</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J6">
         <v>100</v>
@@ -3913,7 +3778,7 @@
         <v>100</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q6">
         <v>100</v>
@@ -3939,7 +3804,7 @@
         <v>16</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C7">
         <v>100</v>
@@ -3960,7 +3825,7 @@
         <v>100</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J7">
         <v>100</v>
@@ -3972,7 +3837,7 @@
         <v>100</v>
       </c>
       <c r="M7">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="N7">
         <v>100</v>
@@ -3981,7 +3846,7 @@
         <v>100</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q7">
         <v>100</v>
@@ -3993,7 +3858,7 @@
         <v>100</v>
       </c>
       <c r="T7">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="U7">
         <v>100</v>
@@ -4007,7 +3872,7 @@
         <v>17</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C8">
         <v>100</v>
@@ -4028,7 +3893,7 @@
         <v>100</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J8">
         <v>100</v>
@@ -4040,7 +3905,7 @@
         <v>100</v>
       </c>
       <c r="M8">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="N8">
         <v>100</v>
@@ -4049,7 +3914,7 @@
         <v>100</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q8">
         <v>100</v>
@@ -4061,7 +3926,7 @@
         <v>100</v>
       </c>
       <c r="T8">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="U8">
         <v>100</v>
@@ -4075,7 +3940,7 @@
         <v>18</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C9">
         <v>100</v>
@@ -4096,16 +3961,16 @@
         <v>90</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J9">
-        <v>100</v>
+        <v>86.7</v>
       </c>
       <c r="K9">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="L9">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="M9">
         <v>80</v>
@@ -4117,16 +3982,16 @@
         <v>90</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q9">
-        <v>100</v>
+        <v>86.7</v>
       </c>
       <c r="R9">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="S9">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="T9">
         <v>80</v>
@@ -4143,7 +4008,7 @@
         <v>19</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C10">
         <v>100</v>
@@ -4164,7 +4029,7 @@
         <v>90</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J10">
         <v>100</v>
@@ -4176,7 +4041,7 @@
         <v>100</v>
       </c>
       <c r="M10">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="N10">
         <v>100</v>
@@ -4185,7 +4050,7 @@
         <v>90</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q10">
         <v>100</v>
@@ -4197,7 +4062,7 @@
         <v>100</v>
       </c>
       <c r="T10">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="U10">
         <v>100</v>
@@ -4211,7 +4076,7 @@
         <v>20</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C11">
         <v>100</v>
@@ -4232,13 +4097,13 @@
         <v>100</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J11">
         <v>100</v>
       </c>
       <c r="K11">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="L11">
         <v>100</v>
@@ -4253,13 +4118,13 @@
         <v>100</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q11">
         <v>100</v>
       </c>
       <c r="R11">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="S11">
         <v>100</v>
@@ -4279,7 +4144,7 @@
         <v>21</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C12">
         <v>100</v>
@@ -4300,13 +4165,13 @@
         <v>100</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J12">
         <v>100</v>
       </c>
       <c r="K12">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="L12">
         <v>100</v>
@@ -4321,13 +4186,13 @@
         <v>100</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q12">
         <v>100</v>
       </c>
       <c r="R12">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="S12">
         <v>100</v>
@@ -4347,7 +4212,7 @@
         <v>22</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C13">
         <v>100</v>
@@ -4368,19 +4233,19 @@
         <v>90</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J13">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="K13">
+        <v>97.5</v>
+      </c>
+      <c r="L13">
+        <v>100</v>
+      </c>
+      <c r="M13">
         <v>95</v>
-      </c>
-      <c r="L13">
-        <v>100</v>
-      </c>
-      <c r="M13">
-        <v>100</v>
       </c>
       <c r="N13">
         <v>100</v>
@@ -4389,19 +4254,19 @@
         <v>90</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q13">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="R13">
+        <v>97.5</v>
+      </c>
+      <c r="S13">
+        <v>100</v>
+      </c>
+      <c r="T13">
         <v>95</v>
-      </c>
-      <c r="S13">
-        <v>100</v>
-      </c>
-      <c r="T13">
-        <v>100</v>
       </c>
       <c r="U13">
         <v>100</v>
@@ -4415,7 +4280,7 @@
         <v>23</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C14">
         <v>86.7</v>
@@ -4436,13 +4301,13 @@
         <v>100</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J14">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="K14">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="L14">
         <v>100</v>
@@ -4457,13 +4322,13 @@
         <v>100</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q14">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="R14">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="S14">
         <v>100</v>
@@ -4483,7 +4348,7 @@
         <v>24</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C15">
         <v>100</v>
@@ -4504,7 +4369,7 @@
         <v>100</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J15">
         <v>100</v>
@@ -4516,7 +4381,7 @@
         <v>100</v>
       </c>
       <c r="M15">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="N15">
         <v>100</v>
@@ -4525,7 +4390,7 @@
         <v>100</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q15">
         <v>100</v>
@@ -4537,7 +4402,7 @@
         <v>100</v>
       </c>
       <c r="T15">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="U15">
         <v>100</v>
@@ -4551,7 +4416,7 @@
         <v>25</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="C16">
         <v>80</v>
@@ -4572,19 +4437,19 @@
         <v>60</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="J16">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K16">
-        <v>75</v>
+        <v>87.5</v>
       </c>
       <c r="L16">
-        <v>73.3</v>
+        <v>86.7</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N16">
         <v>81.3</v>
@@ -4593,19 +4458,19 @@
         <v>60</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="Q16">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="R16">
-        <v>75</v>
+        <v>87.5</v>
       </c>
       <c r="S16">
-        <v>73.3</v>
+        <v>86.7</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="U16">
         <v>81.3</v>
@@ -4619,7 +4484,7 @@
         <v>26</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C17">
         <v>93.3</v>
@@ -4640,19 +4505,19 @@
         <v>100</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J17">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="K17">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="L17">
         <v>100</v>
       </c>
       <c r="M17">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="N17">
         <v>93.8</v>
@@ -4661,19 +4526,19 @@
         <v>100</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q17">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="R17">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="S17">
         <v>100</v>
       </c>
       <c r="T17">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="U17">
         <v>93.8</v>
@@ -4687,7 +4552,7 @@
         <v>27</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C18">
         <v>100</v>
@@ -4708,19 +4573,19 @@
         <v>100</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J18">
         <v>100</v>
       </c>
       <c r="K18">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="L18">
         <v>100</v>
       </c>
       <c r="M18">
-        <v>80</v>
+        <v>82.5</v>
       </c>
       <c r="N18">
         <v>100</v>
@@ -4729,19 +4594,19 @@
         <v>100</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q18">
         <v>100</v>
       </c>
       <c r="R18">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="S18">
         <v>100</v>
       </c>
       <c r="T18">
-        <v>80</v>
+        <v>82.5</v>
       </c>
       <c r="U18">
         <v>100</v>
@@ -4755,7 +4620,7 @@
         <v>28</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C19">
         <v>93.3</v>
@@ -4776,19 +4641,19 @@
         <v>95</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J19">
+        <v>96.7</v>
+      </c>
+      <c r="K19">
+        <v>97.5</v>
+      </c>
+      <c r="L19">
         <v>93.3</v>
       </c>
-      <c r="K19">
-        <v>100</v>
-      </c>
-      <c r="L19">
-        <v>86.7</v>
-      </c>
       <c r="M19">
-        <v>80</v>
+        <v>87.5</v>
       </c>
       <c r="N19">
         <v>100</v>
@@ -4797,19 +4662,19 @@
         <v>95</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q19">
+        <v>96.7</v>
+      </c>
+      <c r="R19">
+        <v>97.5</v>
+      </c>
+      <c r="S19">
         <v>93.3</v>
       </c>
-      <c r="R19">
-        <v>100</v>
-      </c>
-      <c r="S19">
-        <v>86.7</v>
-      </c>
       <c r="T19">
-        <v>80</v>
+        <v>87.5</v>
       </c>
       <c r="U19">
         <v>100</v>
@@ -4823,7 +4688,7 @@
         <v>29</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C20">
         <v>86.7</v>
@@ -4844,16 +4709,16 @@
         <v>85</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J20">
-        <v>86.7</v>
+        <v>90</v>
       </c>
       <c r="K20">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="L20">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="M20">
         <v>100</v>
@@ -4865,16 +4730,16 @@
         <v>85</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q20">
-        <v>86.7</v>
+        <v>90</v>
       </c>
       <c r="R20">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="S20">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="T20">
         <v>100</v>
@@ -4891,7 +4756,7 @@
         <v>30</v>
       </c>
       <c r="B21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C21">
         <v>86.7</v>
@@ -4912,10 +4777,10 @@
         <v>90</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J21">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="K21">
         <v>95</v>
@@ -4924,7 +4789,7 @@
         <v>100</v>
       </c>
       <c r="M21">
-        <v>80</v>
+        <v>87.5</v>
       </c>
       <c r="N21">
         <v>93.8</v>
@@ -4933,10 +4798,10 @@
         <v>90</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q21">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="R21">
         <v>95</v>
@@ -4945,7 +4810,7 @@
         <v>100</v>
       </c>
       <c r="T21">
-        <v>80</v>
+        <v>87.5</v>
       </c>
       <c r="U21">
         <v>93.8</v>
@@ -4959,7 +4824,7 @@
         <v>31</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C22">
         <v>100</v>
@@ -4980,19 +4845,19 @@
         <v>100</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J22">
         <v>100</v>
       </c>
       <c r="K22">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="L22">
         <v>100</v>
       </c>
       <c r="M22">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="N22">
         <v>87.5</v>
@@ -5001,19 +4866,19 @@
         <v>100</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q22">
         <v>100</v>
       </c>
       <c r="R22">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="S22">
         <v>100</v>
       </c>
       <c r="T22">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="U22">
         <v>87.5</v>
@@ -5027,7 +4892,7 @@
         <v>32</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C23">
         <v>100</v>
@@ -5048,7 +4913,7 @@
         <v>100</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J23">
         <v>100</v>
@@ -5060,7 +4925,7 @@
         <v>100</v>
       </c>
       <c r="M23">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="N23">
         <v>93.8</v>
@@ -5069,7 +4934,7 @@
         <v>100</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q23">
         <v>100</v>
@@ -5081,7 +4946,7 @@
         <v>100</v>
       </c>
       <c r="T23">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="U23">
         <v>93.8</v>
@@ -5095,7 +4960,7 @@
         <v>33</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C24">
         <v>100</v>
@@ -5116,19 +4981,19 @@
         <v>85</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J24">
         <v>100</v>
       </c>
       <c r="K24">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="L24">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="M24">
-        <v>85</v>
+        <v>82.5</v>
       </c>
       <c r="N24">
         <v>100</v>
@@ -5137,19 +5002,19 @@
         <v>85</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q24">
         <v>100</v>
       </c>
       <c r="R24">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="S24">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="T24">
-        <v>85</v>
+        <v>82.5</v>
       </c>
       <c r="U24">
         <v>100</v>
@@ -5163,7 +5028,7 @@
         <v>34</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C25">
         <v>100</v>
@@ -5184,7 +5049,7 @@
         <v>100</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J25">
         <v>100</v>
@@ -5205,7 +5070,7 @@
         <v>100</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q25">
         <v>100</v>
@@ -5231,7 +5096,7 @@
         <v>35</v>
       </c>
       <c r="B26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C26">
         <v>100</v>
@@ -5252,7 +5117,7 @@
         <v>100</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J26">
         <v>100</v>
@@ -5261,10 +5126,10 @@
         <v>95</v>
       </c>
       <c r="L26">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="M26">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="N26">
         <v>93.8</v>
@@ -5273,7 +5138,7 @@
         <v>100</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q26">
         <v>100</v>
@@ -5282,10 +5147,10 @@
         <v>95</v>
       </c>
       <c r="S26">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="T26">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="U26">
         <v>93.8</v>
@@ -5299,7 +5164,7 @@
         <v>36</v>
       </c>
       <c r="B27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C27">
         <v>100</v>
@@ -5320,7 +5185,7 @@
         <v>100</v>
       </c>
       <c r="I27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J27">
         <v>100</v>
@@ -5341,7 +5206,7 @@
         <v>100</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q27">
         <v>100</v>
@@ -5367,7 +5232,7 @@
         <v>37</v>
       </c>
       <c r="B28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C28">
         <v>100</v>
@@ -5388,13 +5253,13 @@
         <v>90</v>
       </c>
       <c r="I28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J28">
         <v>100</v>
       </c>
       <c r="K28">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="L28">
         <v>100</v>
@@ -5409,13 +5274,13 @@
         <v>90</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q28">
         <v>100</v>
       </c>
       <c r="R28">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="S28">
         <v>100</v>
@@ -5435,7 +5300,7 @@
         <v>38</v>
       </c>
       <c r="B29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C29">
         <v>100</v>
@@ -5456,7 +5321,7 @@
         <v>100</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J29">
         <v>100</v>
@@ -5465,7 +5330,7 @@
         <v>100</v>
       </c>
       <c r="L29">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="M29">
         <v>100</v>
@@ -5477,7 +5342,7 @@
         <v>100</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q29">
         <v>100</v>
@@ -5486,7 +5351,7 @@
         <v>100</v>
       </c>
       <c r="S29">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="T29">
         <v>100</v>
@@ -5503,7 +5368,7 @@
         <v>39</v>
       </c>
       <c r="B30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C30">
         <v>100</v>
@@ -5524,7 +5389,7 @@
         <v>100</v>
       </c>
       <c r="I30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J30">
         <v>100</v>
@@ -5545,7 +5410,7 @@
         <v>100</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q30">
         <v>100</v>
@@ -5571,7 +5436,7 @@
         <v>40</v>
       </c>
       <c r="B31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C31">
         <v>100</v>
@@ -5592,19 +5457,19 @@
         <v>100</v>
       </c>
       <c r="I31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J31">
         <v>100</v>
       </c>
       <c r="K31">
+        <v>97.5</v>
+      </c>
+      <c r="L31">
+        <v>90</v>
+      </c>
+      <c r="M31">
         <v>95</v>
-      </c>
-      <c r="L31">
-        <v>100</v>
-      </c>
-      <c r="M31">
-        <v>90</v>
       </c>
       <c r="N31">
         <v>93.8</v>
@@ -5613,19 +5478,19 @@
         <v>100</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q31">
         <v>100</v>
       </c>
       <c r="R31">
+        <v>97.5</v>
+      </c>
+      <c r="S31">
+        <v>90</v>
+      </c>
+      <c r="T31">
         <v>95</v>
-      </c>
-      <c r="S31">
-        <v>100</v>
-      </c>
-      <c r="T31">
-        <v>90</v>
       </c>
       <c r="U31">
         <v>93.8</v>
@@ -5639,7 +5504,7 @@
         <v>41</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C32">
         <v>100</v>
@@ -5660,10 +5525,10 @@
         <v>100</v>
       </c>
       <c r="I32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J32">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="K32">
         <v>100</v>
@@ -5672,7 +5537,7 @@
         <v>100</v>
       </c>
       <c r="M32">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="N32">
         <v>100</v>
@@ -5681,10 +5546,10 @@
         <v>100</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q32">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="R32">
         <v>100</v>
@@ -5693,7 +5558,7 @@
         <v>100</v>
       </c>
       <c r="T32">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="U32">
         <v>100</v>
@@ -5707,7 +5572,7 @@
         <v>42</v>
       </c>
       <c r="B33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C33">
         <v>100</v>
@@ -5728,13 +5593,13 @@
         <v>100</v>
       </c>
       <c r="I33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J33">
         <v>100</v>
       </c>
       <c r="K33">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="L33">
         <v>100</v>
@@ -5749,13 +5614,13 @@
         <v>100</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q33">
         <v>100</v>
       </c>
       <c r="R33">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="S33">
         <v>100</v>
@@ -5824,7 +5689,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
         <v>56</v>
@@ -5833,27 +5698,30 @@
         <v>30</v>
       </c>
       <c r="D2">
+        <v>11</v>
+      </c>
+      <c r="E2">
+        <v>19</v>
+      </c>
+      <c r="F2" s="2">
+        <v>36.7</v>
+      </c>
+      <c r="G2" s="2">
+        <v>63.3</v>
+      </c>
+      <c r="H2">
+        <v>6.1</v>
+      </c>
+      <c r="I2">
         <v>0</v>
       </c>
-      <c r="E2">
+      <c r="J2" s="2">
         <v>0</v>
-      </c>
-      <c r="F2" s="2">
-        <v>0</v>
-      </c>
-      <c r="G2" s="2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>30</v>
-      </c>
-      <c r="J2" s="2">
-        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>57</v>
@@ -5862,19 +5730,19 @@
         <v>30</v>
       </c>
       <c r="D3">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E3">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F3" s="2">
-        <v>30</v>
+        <v>63.3</v>
       </c>
       <c r="G3" s="2">
-        <v>70</v>
+        <v>36.7</v>
       </c>
       <c r="H3">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5885,7 +5753,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>58</v>
@@ -5894,19 +5762,19 @@
         <v>30</v>
       </c>
       <c r="D4">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E4">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="F4" s="2">
-        <v>43.3</v>
+        <v>70</v>
       </c>
       <c r="G4" s="2">
-        <v>56.7</v>
+        <v>30</v>
       </c>
       <c r="H4">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5917,7 +5785,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>59</v>
@@ -5926,19 +5794,19 @@
         <v>30</v>
       </c>
       <c r="D5">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E5">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F5" s="2">
-        <v>50</v>
+        <v>73.3</v>
       </c>
       <c r="G5" s="2">
-        <v>50</v>
+        <v>26.7</v>
       </c>
       <c r="H5">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5981,7 +5849,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
         <v>61</v>
@@ -6002,7 +5870,7 @@
         <v>3.3</v>
       </c>
       <c r="H7">
-        <v>7.9</v>
+        <v>9.5</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6013,7 +5881,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
         <v>62</v>
@@ -6022,19 +5890,19 @@
         <v>30</v>
       </c>
       <c r="D8">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" s="2">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="G8" s="2">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="H8">
-        <v>9.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -6048,7 +5916,7 @@
         <v>55</v>
       </c>
       <c r="B9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -6070,7 +5938,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6097,606 +5965,6 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>23330051920151</v>
-      </c>
-      <c r="B2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C2" t="s">
-        <v>90</v>
-      </c>
-      <c r="D2" t="s">
-        <v>110</v>
-      </c>
-      <c r="E2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>23330051920152</v>
-      </c>
-      <c r="B3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C3" t="s">
-        <v>91</v>
-      </c>
-      <c r="D3" t="s">
-        <v>111</v>
-      </c>
-      <c r="E3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>23330051920153</v>
-      </c>
-      <c r="B4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C4" t="s">
-        <v>92</v>
-      </c>
-      <c r="D4" t="s">
-        <v>112</v>
-      </c>
-      <c r="E4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>23330051920155</v>
-      </c>
-      <c r="B5" t="s">
-        <v>70</v>
-      </c>
-      <c r="C5" t="s">
-        <v>93</v>
-      </c>
-      <c r="D5" t="s">
-        <v>113</v>
-      </c>
-      <c r="E5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F5" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>23330051920154</v>
-      </c>
-      <c r="B6" t="s">
-        <v>70</v>
-      </c>
-      <c r="C6" t="s">
-        <v>93</v>
-      </c>
-      <c r="D6" t="s">
-        <v>114</v>
-      </c>
-      <c r="E6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>23330051920156</v>
-      </c>
-      <c r="B7" t="s">
-        <v>71</v>
-      </c>
-      <c r="C7" t="s">
-        <v>72</v>
-      </c>
-      <c r="D7" t="s">
-        <v>115</v>
-      </c>
-      <c r="E7" t="s">
-        <v>5</v>
-      </c>
-      <c r="F7" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>23330051920337</v>
-      </c>
-      <c r="B8" t="s">
-        <v>71</v>
-      </c>
-      <c r="C8" t="s">
-        <v>94</v>
-      </c>
-      <c r="D8" t="s">
-        <v>116</v>
-      </c>
-      <c r="E8" t="s">
-        <v>5</v>
-      </c>
-      <c r="F8" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>23330051920157</v>
-      </c>
-      <c r="B9" t="s">
-        <v>72</v>
-      </c>
-      <c r="C9" t="s">
-        <v>95</v>
-      </c>
-      <c r="D9" t="s">
-        <v>117</v>
-      </c>
-      <c r="E9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>23330051920158</v>
-      </c>
-      <c r="B10" t="s">
-        <v>72</v>
-      </c>
-      <c r="C10" t="s">
-        <v>84</v>
-      </c>
-      <c r="D10" t="s">
-        <v>118</v>
-      </c>
-      <c r="E10" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>23330051920159</v>
-      </c>
-      <c r="B11" t="s">
-        <v>72</v>
-      </c>
-      <c r="C11" t="s">
-        <v>84</v>
-      </c>
-      <c r="D11" t="s">
-        <v>119</v>
-      </c>
-      <c r="E11" t="s">
-        <v>5</v>
-      </c>
-      <c r="F11" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>23330051920160</v>
-      </c>
-      <c r="B12" t="s">
-        <v>72</v>
-      </c>
-      <c r="C12" t="s">
-        <v>96</v>
-      </c>
-      <c r="D12" t="s">
-        <v>120</v>
-      </c>
-      <c r="E12" t="s">
-        <v>5</v>
-      </c>
-      <c r="F12" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>23330051920161</v>
-      </c>
-      <c r="B13" t="s">
-        <v>73</v>
-      </c>
-      <c r="C13" t="s">
-        <v>97</v>
-      </c>
-      <c r="D13" t="s">
-        <v>121</v>
-      </c>
-      <c r="E13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F13" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>23330051920162</v>
-      </c>
-      <c r="B14" t="s">
-        <v>73</v>
-      </c>
-      <c r="C14" t="s">
-        <v>98</v>
-      </c>
-      <c r="D14" t="s">
-        <v>122</v>
-      </c>
-      <c r="E14" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>23330051920163</v>
-      </c>
-      <c r="B15" t="s">
-        <v>74</v>
-      </c>
-      <c r="C15" t="s">
-        <v>99</v>
-      </c>
-      <c r="D15" t="s">
-        <v>123</v>
-      </c>
-      <c r="E15" t="s">
-        <v>5</v>
-      </c>
-      <c r="F15" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>23330051920164</v>
-      </c>
-      <c r="B16" t="s">
-        <v>75</v>
-      </c>
-      <c r="C16" t="s">
-        <v>100</v>
-      </c>
-      <c r="D16" t="s">
-        <v>124</v>
-      </c>
-      <c r="E16" t="s">
-        <v>5</v>
-      </c>
-      <c r="F16" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>23330051920165</v>
-      </c>
-      <c r="B17" t="s">
-        <v>76</v>
-      </c>
-      <c r="C17" t="s">
-        <v>71</v>
-      </c>
-      <c r="D17" t="s">
-        <v>125</v>
-      </c>
-      <c r="E17" t="s">
-        <v>5</v>
-      </c>
-      <c r="F17" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>23330051920316</v>
-      </c>
-      <c r="B18" t="s">
-        <v>77</v>
-      </c>
-      <c r="C18" t="s">
-        <v>101</v>
-      </c>
-      <c r="D18" t="s">
-        <v>126</v>
-      </c>
-      <c r="E18" t="s">
-        <v>5</v>
-      </c>
-      <c r="F18" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>23330051920166</v>
-      </c>
-      <c r="B19" t="s">
-        <v>78</v>
-      </c>
-      <c r="C19" t="s">
-        <v>84</v>
-      </c>
-      <c r="D19" t="s">
-        <v>127</v>
-      </c>
-      <c r="E19" t="s">
-        <v>5</v>
-      </c>
-      <c r="F19" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>23330051920167</v>
-      </c>
-      <c r="B20" t="s">
-        <v>79</v>
-      </c>
-      <c r="C20" t="s">
-        <v>95</v>
-      </c>
-      <c r="D20" t="s">
-        <v>128</v>
-      </c>
-      <c r="E20" t="s">
-        <v>5</v>
-      </c>
-      <c r="F20" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>23330051920168</v>
-      </c>
-      <c r="B21" t="s">
-        <v>80</v>
-      </c>
-      <c r="C21" t="s">
-        <v>102</v>
-      </c>
-      <c r="D21" t="s">
-        <v>129</v>
-      </c>
-      <c r="E21" t="s">
-        <v>5</v>
-      </c>
-      <c r="F21" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>23330051920169</v>
-      </c>
-      <c r="B22" t="s">
-        <v>81</v>
-      </c>
-      <c r="C22" t="s">
-        <v>103</v>
-      </c>
-      <c r="D22" t="s">
-        <v>130</v>
-      </c>
-      <c r="E22" t="s">
-        <v>5</v>
-      </c>
-      <c r="F22" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>23330051920354</v>
-      </c>
-      <c r="B23" t="s">
-        <v>81</v>
-      </c>
-      <c r="C23" t="s">
-        <v>104</v>
-      </c>
-      <c r="D23" t="s">
-        <v>131</v>
-      </c>
-      <c r="E23" t="s">
-        <v>5</v>
-      </c>
-      <c r="F23" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>23330051920170</v>
-      </c>
-      <c r="B24" t="s">
-        <v>82</v>
-      </c>
-      <c r="C24" t="s">
-        <v>105</v>
-      </c>
-      <c r="D24" t="s">
-        <v>132</v>
-      </c>
-      <c r="E24" t="s">
-        <v>5</v>
-      </c>
-      <c r="F24" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>23330051920171</v>
-      </c>
-      <c r="B25" t="s">
-        <v>83</v>
-      </c>
-      <c r="C25" t="s">
-        <v>72</v>
-      </c>
-      <c r="D25" t="s">
-        <v>133</v>
-      </c>
-      <c r="E25" t="s">
-        <v>5</v>
-      </c>
-      <c r="F25" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>23330051920173</v>
-      </c>
-      <c r="B26" t="s">
-        <v>84</v>
-      </c>
-      <c r="C26" t="s">
-        <v>106</v>
-      </c>
-      <c r="D26" t="s">
-        <v>134</v>
-      </c>
-      <c r="E26" t="s">
-        <v>5</v>
-      </c>
-      <c r="F26" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>23330051920172</v>
-      </c>
-      <c r="B27" t="s">
-        <v>85</v>
-      </c>
-      <c r="C27" t="s">
-        <v>107</v>
-      </c>
-      <c r="D27" t="s">
-        <v>135</v>
-      </c>
-      <c r="E27" t="s">
-        <v>5</v>
-      </c>
-      <c r="F27" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>23330051920174</v>
-      </c>
-      <c r="B28" t="s">
-        <v>86</v>
-      </c>
-      <c r="C28" t="s">
-        <v>86</v>
-      </c>
-      <c r="D28" t="s">
-        <v>136</v>
-      </c>
-      <c r="E28" t="s">
-        <v>5</v>
-      </c>
-      <c r="F28" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>23330051920175</v>
-      </c>
-      <c r="B29" t="s">
-        <v>87</v>
-      </c>
-      <c r="C29" t="s">
-        <v>108</v>
-      </c>
-      <c r="D29" t="s">
-        <v>137</v>
-      </c>
-      <c r="E29" t="s">
-        <v>5</v>
-      </c>
-      <c r="F29" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>23330051920313</v>
-      </c>
-      <c r="B30" t="s">
-        <v>88</v>
-      </c>
-      <c r="C30" t="s">
-        <v>88</v>
-      </c>
-      <c r="D30" t="s">
-        <v>138</v>
-      </c>
-      <c r="E30" t="s">
-        <v>5</v>
-      </c>
-      <c r="F30" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>23330051920176</v>
-      </c>
-      <c r="B31" t="s">
-        <v>89</v>
-      </c>
-      <c r="C31" t="s">
-        <v>109</v>
-      </c>
-      <c r="D31" t="s">
-        <v>139</v>
-      </c>
-      <c r="E31" t="s">
-        <v>5</v>
-      </c>
-      <c r="F31" t="s">
-        <v>56</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6704,7 +5972,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6736,45 +6004,45 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920157</v>
+        <v>23330051920155</v>
       </c>
       <c r="B2" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="D2" t="s">
-        <v>117</v>
+        <v>83</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920157</v>
+        <v>23330051920155</v>
       </c>
       <c r="B3" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="C3" t="s">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="D3" t="s">
-        <v>117</v>
+        <v>83</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -6782,45 +6050,45 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920158</v>
+        <v>23330051920154</v>
       </c>
       <c r="B4" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="C4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D4" t="s">
         <v>84</v>
       </c>
-      <c r="D4" t="s">
-        <v>118</v>
-      </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920158</v>
+        <v>23330051920154</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="C5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D5" t="s">
         <v>84</v>
       </c>
-      <c r="D5" t="s">
-        <v>118</v>
-      </c>
       <c r="E5" t="s">
         <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -6828,45 +6096,45 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920159</v>
+        <v>23330051920165</v>
       </c>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="D6" t="s">
-        <v>119</v>
+        <v>85</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920159</v>
+        <v>23330051920165</v>
       </c>
       <c r="B7" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="D7" t="s">
-        <v>119</v>
+        <v>85</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -6874,45 +6142,45 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920167</v>
+        <v>23330051920166</v>
       </c>
       <c r="B8" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="D8" t="s">
-        <v>128</v>
+        <v>86</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920167</v>
+        <v>23330051920166</v>
       </c>
       <c r="B9" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="C9" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="D9" t="s">
-        <v>128</v>
+        <v>86</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -6920,45 +6188,45 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920171</v>
+        <v>23330051920157</v>
       </c>
       <c r="B10" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="C10" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="D10" t="s">
-        <v>133</v>
+        <v>87</v>
       </c>
       <c r="E10" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
         <v>56</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920171</v>
+        <v>23330051920158</v>
       </c>
       <c r="B11" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="C11" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="D11" t="s">
-        <v>133</v>
+        <v>88</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -6966,163 +6234,140 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920152</v>
+        <v>23330051920160</v>
       </c>
       <c r="B12" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C12" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="D12" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
       <c r="E12" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F12" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920153</v>
+        <v>23330051920167</v>
       </c>
       <c r="B13" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C13" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D13" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="E13" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F13" t="s">
         <v>56</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920337</v>
+        <v>23330051920354</v>
       </c>
       <c r="B14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C14" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="D14" t="s">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="E14" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F14" t="s">
         <v>56</v>
       </c>
       <c r="G14">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330051920163</v>
+        <v>23330051920170</v>
       </c>
       <c r="B15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C15" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="D15" t="s">
-        <v>123</v>
+        <v>92</v>
       </c>
       <c r="E15" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F15" t="s">
         <v>56</v>
       </c>
       <c r="G15">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>23330051920173</v>
+        <v>23330051920171</v>
       </c>
       <c r="B16" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="C16" t="s">
-        <v>106</v>
+        <v>70</v>
       </c>
       <c r="D16" t="s">
-        <v>134</v>
+        <v>93</v>
       </c>
       <c r="E16" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F16" t="s">
         <v>56</v>
       </c>
       <c r="G16">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>23330051920172</v>
+        <v>23330051920174</v>
       </c>
       <c r="B17" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="C17" t="s">
-        <v>107</v>
+        <v>75</v>
       </c>
       <c r="D17" t="s">
-        <v>135</v>
+        <v>94</v>
       </c>
       <c r="E17" t="s">
         <v>5</v>
       </c>
       <c r="F17" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G17">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>23330051920174</v>
-      </c>
-      <c r="B18" t="s">
-        <v>86</v>
-      </c>
-      <c r="C18" t="s">
-        <v>86</v>
-      </c>
-      <c r="D18" t="s">
-        <v>136</v>
-      </c>
-      <c r="E18" t="s">
-        <v>5</v>
-      </c>
-      <c r="F18" t="s">
-        <v>56</v>
-      </c>
-      <c r="G18">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/1FM - Estadisticos 20231.xlsx
+++ b/grupos/1FM - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="97">
   <si>
     <t>Materia</t>
   </si>
@@ -203,12 +203,12 @@
     <t>Velasco Sánchez David</t>
   </si>
   <si>
+    <t>Rosas Aguilar Claudia Leonor</t>
+  </si>
+  <si>
     <t>Moreno Aroyo Anél</t>
   </si>
   <si>
-    <t>Rosas Aguilar Claudia Leonor</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -224,45 +224,48 @@
     <t>CRUZ</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>MOLINA</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
     <t>MELO</t>
   </si>
   <si>
-    <t>MOLINA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
     <t>ORTIZ</t>
   </si>
   <si>
-    <t>REYES</t>
-  </si>
-  <si>
     <t>RIOS</t>
   </si>
   <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
     <t>TEXCAHUA</t>
   </si>
   <si>
     <t>NIEVES</t>
   </si>
   <si>
+    <t>TETLA</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>COXCAHUA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>TETLA</t>
-  </si>
-  <si>
     <t>MONTIEL</t>
   </si>
   <si>
@@ -275,21 +278,27 @@
     <t>ESTRELLA RUBI</t>
   </si>
   <si>
+    <t>HECTOR</t>
+  </si>
+  <si>
+    <t>LEONARDO GABRIEL</t>
+  </si>
+  <si>
+    <t>VICTOR JESUS</t>
+  </si>
+  <si>
+    <t>JONATHAN ISAI</t>
+  </si>
+  <si>
+    <t>JAIR</t>
+  </si>
+  <si>
+    <t>DORIAN ALEXANDER</t>
+  </si>
+  <si>
     <t>KENYA MARIANA</t>
   </si>
   <si>
-    <t>LEONARDO GABRIEL</t>
-  </si>
-  <si>
-    <t>JAIR</t>
-  </si>
-  <si>
-    <t>DORIAN ALEXANDER</t>
-  </si>
-  <si>
-    <t>HECTOR</t>
-  </si>
-  <si>
     <t>SALMA JANET</t>
   </si>
   <si>
@@ -297,9 +306,6 @@
   </si>
   <si>
     <t>KAORY AYELEN</t>
-  </si>
-  <si>
-    <t>JONATHAN ISAI</t>
   </si>
   <si>
     <t>JUAN CARLOS</t>
@@ -829,7 +835,7 @@
         <v>8</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J4">
         <v>6</v>
@@ -844,7 +850,7 @@
         <v>5</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O4">
         <v>-1</v>
@@ -886,7 +892,7 @@
         <v>7</v>
       </c>
       <c r="AB4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC4">
         <v>8</v>
@@ -918,7 +924,7 @@
         <v>9</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J5">
         <v>10</v>
@@ -933,7 +939,7 @@
         <v>10</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O5">
         <v>-1</v>
@@ -960,7 +966,7 @@
         <v>-1</v>
       </c>
       <c r="W5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X5">
         <v>9</v>
@@ -1007,7 +1013,7 @@
         <v>10</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J6">
         <v>9</v>
@@ -1022,7 +1028,7 @@
         <v>7</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O6">
         <v>-1</v>
@@ -1049,7 +1055,7 @@
         <v>-1</v>
       </c>
       <c r="W6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X6">
         <v>8</v>
@@ -1096,7 +1102,7 @@
         <v>9</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J7">
         <v>6</v>
@@ -1111,7 +1117,7 @@
         <v>5</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O7">
         <v>-1</v>
@@ -1185,7 +1191,7 @@
         <v>10</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J8">
         <v>6</v>
@@ -1200,7 +1206,7 @@
         <v>6</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O8">
         <v>-1</v>
@@ -1242,7 +1248,7 @@
         <v>5</v>
       </c>
       <c r="AB8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC8">
         <v>10</v>
@@ -1274,7 +1280,7 @@
         <v>8</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J9">
         <v>5</v>
@@ -1289,7 +1295,7 @@
         <v>5</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O9">
         <v>-1</v>
@@ -1331,7 +1337,7 @@
         <v>5</v>
       </c>
       <c r="AB9">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC9">
         <v>8</v>
@@ -1363,7 +1369,7 @@
         <v>8</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J10">
         <v>9</v>
@@ -1378,7 +1384,7 @@
         <v>10</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O10">
         <v>-1</v>
@@ -1452,7 +1458,7 @@
         <v>10</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J11">
         <v>9</v>
@@ -1467,7 +1473,7 @@
         <v>6</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O11">
         <v>-1</v>
@@ -1541,7 +1547,7 @@
         <v>8</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J12">
         <v>7</v>
@@ -1556,7 +1562,7 @@
         <v>6</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O12">
         <v>-1</v>
@@ -1583,7 +1589,7 @@
         <v>-1</v>
       </c>
       <c r="W12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X12">
         <v>7</v>
@@ -1598,7 +1604,7 @@
         <v>5</v>
       </c>
       <c r="AB12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC12">
         <v>8</v>
@@ -1630,7 +1636,7 @@
         <v>7</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J13">
         <v>6</v>
@@ -1645,7 +1651,7 @@
         <v>9</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O13">
         <v>-1</v>
@@ -1672,7 +1678,7 @@
         <v>-1</v>
       </c>
       <c r="W13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X13">
         <v>7</v>
@@ -1687,7 +1693,7 @@
         <v>7</v>
       </c>
       <c r="AB13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC13">
         <v>7</v>
@@ -1719,7 +1725,7 @@
         <v>9</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J14">
         <v>9</v>
@@ -1734,7 +1740,7 @@
         <v>8</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O14">
         <v>-1</v>
@@ -1761,7 +1767,7 @@
         <v>-1</v>
       </c>
       <c r="W14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X14">
         <v>8</v>
@@ -1776,7 +1782,7 @@
         <v>7</v>
       </c>
       <c r="AB14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC14">
         <v>9</v>
@@ -1808,7 +1814,7 @@
         <v>5</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J15">
         <v>8</v>
@@ -1823,7 +1829,7 @@
         <v>5</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O15">
         <v>-1</v>
@@ -1865,7 +1871,7 @@
         <v>5</v>
       </c>
       <c r="AB15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC15">
         <v>5</v>
@@ -1897,7 +1903,7 @@
         <v>4</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J16">
         <v>6</v>
@@ -1912,7 +1918,7 @@
         <v>5</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O16">
         <v>-1</v>
@@ -1954,7 +1960,7 @@
         <v>5</v>
       </c>
       <c r="AB16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC16">
         <v>5</v>
@@ -1986,7 +1992,7 @@
         <v>9</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J17">
         <v>8</v>
@@ -2001,7 +2007,7 @@
         <v>10</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O17">
         <v>-1</v>
@@ -2028,7 +2034,7 @@
         <v>-1</v>
       </c>
       <c r="W17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X17">
         <v>8</v>
@@ -2075,7 +2081,7 @@
         <v>7</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J18">
         <v>6</v>
@@ -2090,7 +2096,7 @@
         <v>5</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O18">
         <v>-1</v>
@@ -2132,7 +2138,7 @@
         <v>5</v>
       </c>
       <c r="AB18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC18">
         <v>7</v>
@@ -2164,7 +2170,7 @@
         <v>7</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J19">
         <v>7</v>
@@ -2179,7 +2185,7 @@
         <v>6</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O19">
         <v>-1</v>
@@ -2206,7 +2212,7 @@
         <v>-1</v>
       </c>
       <c r="W19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X19">
         <v>6</v>
@@ -2221,7 +2227,7 @@
         <v>5</v>
       </c>
       <c r="AB19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC19">
         <v>7</v>
@@ -2253,7 +2259,7 @@
         <v>7</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J20">
         <v>7</v>
@@ -2268,7 +2274,7 @@
         <v>10</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O20">
         <v>-1</v>
@@ -2295,7 +2301,7 @@
         <v>-1</v>
       </c>
       <c r="W20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X20">
         <v>6</v>
@@ -2310,7 +2316,7 @@
         <v>8</v>
       </c>
       <c r="AB20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC20">
         <v>7</v>
@@ -2342,7 +2348,7 @@
         <v>9</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J21">
         <v>5</v>
@@ -2357,7 +2363,7 @@
         <v>6</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O21">
         <v>-1</v>
@@ -2384,7 +2390,7 @@
         <v>-1</v>
       </c>
       <c r="W21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X21">
         <v>5</v>
@@ -2431,7 +2437,7 @@
         <v>10</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J22">
         <v>9</v>
@@ -2446,7 +2452,7 @@
         <v>6</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O22">
         <v>-1</v>
@@ -2520,7 +2526,7 @@
         <v>5</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J23">
         <v>5</v>
@@ -2535,7 +2541,7 @@
         <v>5</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O23">
         <v>-1</v>
@@ -2577,7 +2583,7 @@
         <v>5</v>
       </c>
       <c r="AB23">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC23">
         <v>5</v>
@@ -2609,7 +2615,7 @@
         <v>9</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J24">
         <v>6</v>
@@ -2624,7 +2630,7 @@
         <v>6</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O24">
         <v>-1</v>
@@ -2651,7 +2657,7 @@
         <v>-1</v>
       </c>
       <c r="W24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X24">
         <v>5</v>
@@ -2666,7 +2672,7 @@
         <v>5</v>
       </c>
       <c r="AB24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC24">
         <v>9</v>
@@ -2698,7 +2704,7 @@
         <v>6</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J25">
         <v>8</v>
@@ -2713,7 +2719,7 @@
         <v>6</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O25">
         <v>-1</v>
@@ -2755,7 +2761,7 @@
         <v>5</v>
       </c>
       <c r="AB25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC25">
         <v>6</v>
@@ -2787,7 +2793,7 @@
         <v>7</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J26">
         <v>8</v>
@@ -2802,7 +2808,7 @@
         <v>6</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O26">
         <v>-1</v>
@@ -2844,7 +2850,7 @@
         <v>5</v>
       </c>
       <c r="AB26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC26">
         <v>7</v>
@@ -2876,7 +2882,7 @@
         <v>8</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J27">
         <v>6</v>
@@ -2891,7 +2897,7 @@
         <v>5</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O27">
         <v>-1</v>
@@ -2918,7 +2924,7 @@
         <v>-1</v>
       </c>
       <c r="W27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X27">
         <v>6</v>
@@ -2933,7 +2939,7 @@
         <v>5</v>
       </c>
       <c r="AB27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC27">
         <v>8</v>
@@ -2965,7 +2971,7 @@
         <v>10</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J28">
         <v>9</v>
@@ -2980,7 +2986,7 @@
         <v>8</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O28">
         <v>-1</v>
@@ -3054,7 +3060,7 @@
         <v>8</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J29">
         <v>8</v>
@@ -3069,7 +3075,7 @@
         <v>10</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O29">
         <v>-1</v>
@@ -3143,7 +3149,7 @@
         <v>7</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J30">
         <v>6</v>
@@ -3158,7 +3164,7 @@
         <v>7</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O30">
         <v>-1</v>
@@ -3200,7 +3206,7 @@
         <v>7</v>
       </c>
       <c r="AB30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC30">
         <v>7</v>
@@ -3232,7 +3238,7 @@
         <v>5</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J31">
         <v>6</v>
@@ -3247,7 +3253,7 @@
         <v>5</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O31">
         <v>-1</v>
@@ -3274,7 +3280,7 @@
         <v>-1</v>
       </c>
       <c r="W31">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X31">
         <v>5</v>
@@ -3289,7 +3295,7 @@
         <v>5</v>
       </c>
       <c r="AB31">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AC31">
         <v>5</v>
@@ -3321,7 +3327,7 @@
         <v>5</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J32">
         <v>6</v>
@@ -3336,7 +3342,7 @@
         <v>5</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O32">
         <v>-1</v>
@@ -3363,7 +3369,7 @@
         <v>-1</v>
       </c>
       <c r="W32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X32">
         <v>5</v>
@@ -3378,7 +3384,7 @@
         <v>5</v>
       </c>
       <c r="AB32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC32">
         <v>5</v>
@@ -3410,7 +3416,7 @@
         <v>9</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J33">
         <v>5</v>
@@ -3425,7 +3431,7 @@
         <v>6</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O33">
         <v>-1</v>
@@ -3452,7 +3458,7 @@
         <v>-1</v>
       </c>
       <c r="W33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X33">
         <v>5</v>
@@ -3467,7 +3473,7 @@
         <v>5</v>
       </c>
       <c r="AB33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC33">
         <v>9</v>
@@ -3621,7 +3627,7 @@
         <v>90</v>
       </c>
       <c r="I4">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="J4">
         <v>100</v>
@@ -3642,7 +3648,7 @@
         <v>90</v>
       </c>
       <c r="P4">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="Q4">
         <v>100</v>
@@ -3704,7 +3710,7 @@
         <v>100</v>
       </c>
       <c r="N5">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O5">
         <v>100</v>
@@ -3725,7 +3731,7 @@
         <v>100</v>
       </c>
       <c r="U5">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="V5">
         <v>100</v>
@@ -3961,7 +3967,7 @@
         <v>90</v>
       </c>
       <c r="I9">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="J9">
         <v>86.7</v>
@@ -3982,7 +3988,7 @@
         <v>90</v>
       </c>
       <c r="P9">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="Q9">
         <v>86.7</v>
@@ -4248,7 +4254,7 @@
         <v>95</v>
       </c>
       <c r="N13">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="O13">
         <v>90</v>
@@ -4269,7 +4275,7 @@
         <v>95</v>
       </c>
       <c r="U13">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="V13">
         <v>90</v>
@@ -4316,7 +4322,7 @@
         <v>100</v>
       </c>
       <c r="N14">
-        <v>87.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="O14">
         <v>100</v>
@@ -4337,7 +4343,7 @@
         <v>100</v>
       </c>
       <c r="U14">
-        <v>87.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="V14">
         <v>100</v>
@@ -4437,7 +4443,7 @@
         <v>60</v>
       </c>
       <c r="I16">
-        <v>62.5</v>
+        <v>85</v>
       </c>
       <c r="J16">
         <v>90</v>
@@ -4452,13 +4458,13 @@
         <v>50</v>
       </c>
       <c r="N16">
-        <v>81.3</v>
+        <v>87.5</v>
       </c>
       <c r="O16">
         <v>60</v>
       </c>
       <c r="P16">
-        <v>62.5</v>
+        <v>85</v>
       </c>
       <c r="Q16">
         <v>90</v>
@@ -4473,7 +4479,7 @@
         <v>50</v>
       </c>
       <c r="U16">
-        <v>81.3</v>
+        <v>87.5</v>
       </c>
       <c r="V16">
         <v>60</v>
@@ -4520,7 +4526,7 @@
         <v>92.5</v>
       </c>
       <c r="N17">
-        <v>93.8</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="O17">
         <v>100</v>
@@ -4541,7 +4547,7 @@
         <v>92.5</v>
       </c>
       <c r="U17">
-        <v>93.8</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="V17">
         <v>100</v>
@@ -4588,7 +4594,7 @@
         <v>82.5</v>
       </c>
       <c r="N18">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O18">
         <v>100</v>
@@ -4609,7 +4615,7 @@
         <v>82.5</v>
       </c>
       <c r="U18">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="V18">
         <v>100</v>
@@ -4724,7 +4730,7 @@
         <v>100</v>
       </c>
       <c r="N20">
-        <v>87.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="O20">
         <v>85</v>
@@ -4745,7 +4751,7 @@
         <v>100</v>
       </c>
       <c r="U20">
-        <v>87.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="V20">
         <v>85</v>
@@ -4792,7 +4798,7 @@
         <v>87.5</v>
       </c>
       <c r="N21">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O21">
         <v>90</v>
@@ -4813,7 +4819,7 @@
         <v>87.5</v>
       </c>
       <c r="U21">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="V21">
         <v>90</v>
@@ -4860,7 +4866,7 @@
         <v>97.5</v>
       </c>
       <c r="N22">
-        <v>87.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="O22">
         <v>100</v>
@@ -4881,7 +4887,7 @@
         <v>97.5</v>
       </c>
       <c r="U22">
-        <v>87.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="V22">
         <v>100</v>
@@ -4913,7 +4919,7 @@
         <v>100</v>
       </c>
       <c r="I23">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="J23">
         <v>100</v>
@@ -4928,13 +4934,13 @@
         <v>90</v>
       </c>
       <c r="N23">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O23">
         <v>100</v>
       </c>
       <c r="P23">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Q23">
         <v>100</v>
@@ -4949,7 +4955,7 @@
         <v>90</v>
       </c>
       <c r="U23">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="V23">
         <v>100</v>
@@ -5064,7 +5070,7 @@
         <v>100</v>
       </c>
       <c r="N25">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O25">
         <v>100</v>
@@ -5085,7 +5091,7 @@
         <v>100</v>
       </c>
       <c r="U25">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="V25">
         <v>100</v>
@@ -5132,7 +5138,7 @@
         <v>90</v>
       </c>
       <c r="N26">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O26">
         <v>100</v>
@@ -5153,7 +5159,7 @@
         <v>90</v>
       </c>
       <c r="U26">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="V26">
         <v>100</v>
@@ -5185,7 +5191,7 @@
         <v>100</v>
       </c>
       <c r="I27">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="J27">
         <v>100</v>
@@ -5200,13 +5206,13 @@
         <v>100</v>
       </c>
       <c r="N27">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O27">
         <v>100</v>
       </c>
       <c r="P27">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Q27">
         <v>100</v>
@@ -5221,7 +5227,7 @@
         <v>100</v>
       </c>
       <c r="U27">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="V27">
         <v>100</v>
@@ -5268,7 +5274,7 @@
         <v>100</v>
       </c>
       <c r="N28">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O28">
         <v>90</v>
@@ -5289,7 +5295,7 @@
         <v>100</v>
       </c>
       <c r="U28">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="V28">
         <v>90</v>
@@ -5389,7 +5395,7 @@
         <v>100</v>
       </c>
       <c r="I30">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="J30">
         <v>100</v>
@@ -5410,7 +5416,7 @@
         <v>100</v>
       </c>
       <c r="P30">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Q30">
         <v>100</v>
@@ -5525,7 +5531,7 @@
         <v>100</v>
       </c>
       <c r="I32">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="J32">
         <v>93.3</v>
@@ -5540,13 +5546,13 @@
         <v>95</v>
       </c>
       <c r="N32">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O32">
         <v>100</v>
       </c>
       <c r="P32">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Q32">
         <v>93.3</v>
@@ -5561,7 +5567,7 @@
         <v>95</v>
       </c>
       <c r="U32">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="V32">
         <v>100</v>
@@ -5593,7 +5599,7 @@
         <v>100</v>
       </c>
       <c r="I33">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="J33">
         <v>100</v>
@@ -5608,13 +5614,13 @@
         <v>100</v>
       </c>
       <c r="N33">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O33">
         <v>100</v>
       </c>
       <c r="P33">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Q33">
         <v>100</v>
@@ -5629,7 +5635,7 @@
         <v>100</v>
       </c>
       <c r="U33">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="V33">
         <v>100</v>
@@ -5762,16 +5768,16 @@
         <v>30</v>
       </c>
       <c r="D4">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F4" s="2">
-        <v>70</v>
+        <v>66.7</v>
       </c>
       <c r="G4" s="2">
-        <v>30</v>
+        <v>33.3</v>
       </c>
       <c r="H4">
         <v>6.5</v>
@@ -5849,7 +5855,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>61</v>
@@ -5858,19 +5864,19 @@
         <v>30</v>
       </c>
       <c r="D7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" s="2">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="G7" s="2">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>9.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5881,7 +5887,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
         <v>62</v>
@@ -5902,7 +5908,7 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>8.300000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -5916,7 +5922,7 @@
         <v>55</v>
       </c>
       <c r="B9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -5972,7 +5978,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6013,7 +6019,7 @@
         <v>76</v>
       </c>
       <c r="D2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -6036,7 +6042,7 @@
         <v>76</v>
       </c>
       <c r="D3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -6059,7 +6065,7 @@
         <v>76</v>
       </c>
       <c r="D4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -6082,7 +6088,7 @@
         <v>76</v>
       </c>
       <c r="D5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -6096,7 +6102,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920165</v>
+        <v>23330051920160</v>
       </c>
       <c r="B6" t="s">
         <v>68</v>
@@ -6105,7 +6111,7 @@
         <v>77</v>
       </c>
       <c r="D6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
@@ -6119,7 +6125,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920165</v>
+        <v>23330051920160</v>
       </c>
       <c r="B7" t="s">
         <v>68</v>
@@ -6128,13 +6134,13 @@
         <v>77</v>
       </c>
       <c r="D7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -6151,7 +6157,7 @@
         <v>78</v>
       </c>
       <c r="D8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
@@ -6174,7 +6180,7 @@
         <v>78</v>
       </c>
       <c r="D9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -6188,7 +6194,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920157</v>
+        <v>23330051920169</v>
       </c>
       <c r="B10" t="s">
         <v>70</v>
@@ -6197,13 +6203,13 @@
         <v>79</v>
       </c>
       <c r="D10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E10" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -6211,13 +6217,13 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920158</v>
+        <v>23330051920169</v>
       </c>
       <c r="B11" t="s">
         <v>70</v>
       </c>
       <c r="C11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D11" t="s">
         <v>88</v>
@@ -6234,22 +6240,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920160</v>
+        <v>23330051920171</v>
       </c>
       <c r="B12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C12" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="D12" t="s">
         <v>89</v>
       </c>
       <c r="E12" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -6257,16 +6263,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920167</v>
+        <v>23330051920171</v>
       </c>
       <c r="B13" t="s">
         <v>71</v>
       </c>
       <c r="C13" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="D13" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
@@ -6280,16 +6286,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920354</v>
+        <v>23330051920157</v>
       </c>
       <c r="B14" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C14" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D14" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E14" t="s">
         <v>9</v>
@@ -6303,16 +6309,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330051920170</v>
+        <v>23330051920158</v>
       </c>
       <c r="B15" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C15" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D15" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E15" t="s">
         <v>9</v>
@@ -6326,16 +6332,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>23330051920171</v>
+        <v>23330051920165</v>
       </c>
       <c r="B16" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C16" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E16" t="s">
         <v>9</v>
@@ -6349,24 +6355,93 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
+        <v>23330051920167</v>
+      </c>
+      <c r="B17" t="s">
+        <v>73</v>
+      </c>
+      <c r="C17" t="s">
+        <v>80</v>
+      </c>
+      <c r="D17" t="s">
+        <v>93</v>
+      </c>
+      <c r="E17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" t="s">
+        <v>56</v>
+      </c>
+      <c r="G17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>23330051920354</v>
+      </c>
+      <c r="B18" t="s">
+        <v>70</v>
+      </c>
+      <c r="C18" t="s">
+        <v>82</v>
+      </c>
+      <c r="D18" t="s">
+        <v>94</v>
+      </c>
+      <c r="E18" t="s">
+        <v>9</v>
+      </c>
+      <c r="F18" t="s">
+        <v>56</v>
+      </c>
+      <c r="G18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>23330051920170</v>
+      </c>
+      <c r="B19" t="s">
+        <v>74</v>
+      </c>
+      <c r="C19" t="s">
+        <v>83</v>
+      </c>
+      <c r="D19" t="s">
+        <v>95</v>
+      </c>
+      <c r="E19" t="s">
+        <v>9</v>
+      </c>
+      <c r="F19" t="s">
+        <v>56</v>
+      </c>
+      <c r="G19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
         <v>23330051920174</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B20" t="s">
         <v>75</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C20" t="s">
         <v>75</v>
       </c>
-      <c r="D17" t="s">
-        <v>94</v>
-      </c>
-      <c r="E17" t="s">
-        <v>5</v>
-      </c>
-      <c r="F17" t="s">
+      <c r="D20" t="s">
+        <v>96</v>
+      </c>
+      <c r="E20" t="s">
+        <v>5</v>
+      </c>
+      <c r="F20" t="s">
         <v>58</v>
       </c>
-      <c r="G17">
+      <c r="G20">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1FM - Estadisticos 20231.xlsx
+++ b/grupos/1FM - Estadisticos 20231.xlsx
@@ -853,7 +853,7 @@
         <v>8</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P4">
         <v>-1</v>
@@ -895,7 +895,7 @@
         <v>8</v>
       </c>
       <c r="AC4">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -942,7 +942,7 @@
         <v>10</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P5">
         <v>-1</v>
@@ -984,7 +984,7 @@
         <v>10</v>
       </c>
       <c r="AC5">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -1031,7 +1031,7 @@
         <v>10</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P6">
         <v>-1</v>
@@ -1120,7 +1120,7 @@
         <v>10</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P7">
         <v>-1</v>
@@ -1162,7 +1162,7 @@
         <v>10</v>
       </c>
       <c r="AC7">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:29">
@@ -1209,7 +1209,7 @@
         <v>8</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P8">
         <v>-1</v>
@@ -1251,7 +1251,7 @@
         <v>9</v>
       </c>
       <c r="AC8">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -1298,7 +1298,7 @@
         <v>5</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P9">
         <v>-1</v>
@@ -1340,7 +1340,7 @@
         <v>8</v>
       </c>
       <c r="AC9">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:29">
@@ -1387,7 +1387,7 @@
         <v>9</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P10">
         <v>-1</v>
@@ -1429,7 +1429,7 @@
         <v>10</v>
       </c>
       <c r="AC10">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -1476,7 +1476,7 @@
         <v>10</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P11">
         <v>-1</v>
@@ -1518,7 +1518,7 @@
         <v>10</v>
       </c>
       <c r="AC11">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -1565,7 +1565,7 @@
         <v>5</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P12">
         <v>-1</v>
@@ -1654,7 +1654,7 @@
         <v>8</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P13">
         <v>-1</v>
@@ -1696,7 +1696,7 @@
         <v>9</v>
       </c>
       <c r="AC13">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -1743,7 +1743,7 @@
         <v>8</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P14">
         <v>-1</v>
@@ -1832,7 +1832,7 @@
         <v>8</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P15">
         <v>-1</v>
@@ -1921,7 +1921,7 @@
         <v>7</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P16">
         <v>-1</v>
@@ -2010,7 +2010,7 @@
         <v>10</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P17">
         <v>-1</v>
@@ -2052,7 +2052,7 @@
         <v>10</v>
       </c>
       <c r="AC17">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -2099,7 +2099,7 @@
         <v>8</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P18">
         <v>-1</v>
@@ -2188,7 +2188,7 @@
         <v>8</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P19">
         <v>-1</v>
@@ -2277,7 +2277,7 @@
         <v>8</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P20">
         <v>-1</v>
@@ -2319,7 +2319,7 @@
         <v>9</v>
       </c>
       <c r="AC20">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -2366,7 +2366,7 @@
         <v>9</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P21">
         <v>-1</v>
@@ -2408,7 +2408,7 @@
         <v>10</v>
       </c>
       <c r="AC21">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:29">
@@ -2455,7 +2455,7 @@
         <v>10</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P22">
         <v>-1</v>
@@ -2544,7 +2544,7 @@
         <v>5</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P23">
         <v>-1</v>
@@ -2633,7 +2633,7 @@
         <v>8</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P24">
         <v>-1</v>
@@ -2722,7 +2722,7 @@
         <v>7</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P25">
         <v>-1</v>
@@ -2764,7 +2764,7 @@
         <v>8</v>
       </c>
       <c r="AC25">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:29">
@@ -2811,7 +2811,7 @@
         <v>8</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P26">
         <v>-1</v>
@@ -2853,7 +2853,7 @@
         <v>9</v>
       </c>
       <c r="AC26">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:29">
@@ -2900,7 +2900,7 @@
         <v>7</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P27">
         <v>-1</v>
@@ -2942,7 +2942,7 @@
         <v>9</v>
       </c>
       <c r="AC27">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:29">
@@ -2989,7 +2989,7 @@
         <v>10</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P28">
         <v>-1</v>
@@ -3078,7 +3078,7 @@
         <v>10</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P29">
         <v>-1</v>
@@ -3120,7 +3120,7 @@
         <v>10</v>
       </c>
       <c r="AC29">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:29">
@@ -3167,7 +3167,7 @@
         <v>7</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P30">
         <v>-1</v>
@@ -3256,7 +3256,7 @@
         <v>5</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P31">
         <v>-1</v>
@@ -3345,7 +3345,7 @@
         <v>7</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P32">
         <v>-1</v>
@@ -3387,7 +3387,7 @@
         <v>8</v>
       </c>
       <c r="AC32">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33" spans="1:29">
@@ -3434,7 +3434,7 @@
         <v>6</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P33">
         <v>-1</v>
@@ -3476,7 +3476,7 @@
         <v>7</v>
       </c>
       <c r="AC33">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -3645,7 +3645,7 @@
         <v>100</v>
       </c>
       <c r="O4">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="P4">
         <v>80</v>
@@ -3666,7 +3666,7 @@
         <v>100</v>
       </c>
       <c r="V4">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -3781,7 +3781,7 @@
         <v>100</v>
       </c>
       <c r="O6">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="P6">
         <v>100</v>
@@ -3802,7 +3802,7 @@
         <v>100</v>
       </c>
       <c r="V6">
-        <v>100</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -3985,7 +3985,7 @@
         <v>87.5</v>
       </c>
       <c r="O9">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="P9">
         <v>80</v>
@@ -4006,7 +4006,7 @@
         <v>87.5</v>
       </c>
       <c r="V9">
-        <v>90</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -4053,7 +4053,7 @@
         <v>100</v>
       </c>
       <c r="O10">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="P10">
         <v>100</v>
@@ -4074,7 +4074,7 @@
         <v>100</v>
       </c>
       <c r="V10">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -4257,7 +4257,7 @@
         <v>93.8</v>
       </c>
       <c r="O13">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="P13">
         <v>100</v>
@@ -4278,7 +4278,7 @@
         <v>93.8</v>
       </c>
       <c r="V13">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -4325,7 +4325,7 @@
         <v>90.59999999999999</v>
       </c>
       <c r="O14">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="P14">
         <v>100</v>
@@ -4346,7 +4346,7 @@
         <v>90.59999999999999</v>
       </c>
       <c r="V14">
-        <v>100</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -4461,7 +4461,7 @@
         <v>87.5</v>
       </c>
       <c r="O16">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="P16">
         <v>85</v>
@@ -4482,7 +4482,7 @@
         <v>87.5</v>
       </c>
       <c r="V16">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -4733,7 +4733,7 @@
         <v>90.59999999999999</v>
       </c>
       <c r="O20">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="P20">
         <v>100</v>
@@ -4754,7 +4754,7 @@
         <v>90.59999999999999</v>
       </c>
       <c r="V20">
-        <v>85</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="21" spans="1:22">
@@ -4801,7 +4801,7 @@
         <v>96.90000000000001</v>
       </c>
       <c r="O21">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="P21">
         <v>100</v>
@@ -4822,7 +4822,7 @@
         <v>96.90000000000001</v>
       </c>
       <c r="V21">
-        <v>90</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -5005,7 +5005,7 @@
         <v>100</v>
       </c>
       <c r="O24">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="P24">
         <v>100</v>
@@ -5026,7 +5026,7 @@
         <v>100</v>
       </c>
       <c r="V24">
-        <v>85</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -5073,7 +5073,7 @@
         <v>96.90000000000001</v>
       </c>
       <c r="O25">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="P25">
         <v>100</v>
@@ -5094,7 +5094,7 @@
         <v>96.90000000000001</v>
       </c>
       <c r="V25">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="26" spans="1:22">
@@ -5141,7 +5141,7 @@
         <v>96.90000000000001</v>
       </c>
       <c r="O26">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="P26">
         <v>100</v>
@@ -5162,7 +5162,7 @@
         <v>96.90000000000001</v>
       </c>
       <c r="V26">
-        <v>100</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="27" spans="1:22">
@@ -5277,7 +5277,7 @@
         <v>96.90000000000001</v>
       </c>
       <c r="O28">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="P28">
         <v>100</v>
@@ -5298,7 +5298,7 @@
         <v>96.90000000000001</v>
       </c>
       <c r="V28">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="29" spans="1:22">
@@ -5481,7 +5481,7 @@
         <v>93.8</v>
       </c>
       <c r="O31">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="P31">
         <v>100</v>
@@ -5502,7 +5502,7 @@
         <v>93.8</v>
       </c>
       <c r="V31">
-        <v>100</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="32" spans="1:22">
@@ -5832,19 +5832,19 @@
         <v>30</v>
       </c>
       <c r="D6">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F6" s="2">
-        <v>83.3</v>
+        <v>86.7</v>
       </c>
       <c r="G6" s="2">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="H6">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="I6">
         <v>0</v>

--- a/grupos/1FM - Estadisticos 20231.xlsx
+++ b/grupos/1FM - Estadisticos 20231.xlsx
@@ -4434,7 +4434,7 @@
         <v>73.3</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="G16">
         <v>81.3</v>
@@ -4455,7 +4455,7 @@
         <v>86.7</v>
       </c>
       <c r="M16">
-        <v>50</v>
+        <v>95</v>
       </c>
       <c r="N16">
         <v>87.5</v>
@@ -4476,7 +4476,7 @@
         <v>86.7</v>
       </c>
       <c r="T16">
-        <v>50</v>
+        <v>95</v>
       </c>
       <c r="U16">
         <v>87.5</v>

--- a/grupos/1FM - Estadisticos 20231.xlsx
+++ b/grupos/1FM - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="101">
   <si>
     <t>Materia</t>
   </si>
@@ -191,24 +191,24 @@
     <t>Duran Amezcua María Angélica</t>
   </si>
   <si>
+    <t>Ochoa Martínez Mayeli</t>
+  </si>
+  <si>
     <t>Herrera Serrano Mayra Iliana</t>
   </si>
   <si>
     <t>González Sánchez Rene Aurelio</t>
   </si>
   <si>
-    <t>Ochoa Martínez Mayeli</t>
+    <t>Rosas Aguilar Claudia Leonor</t>
+  </si>
+  <si>
+    <t>Moreno Aroyo Anél</t>
   </si>
   <si>
     <t>Velasco Sánchez David</t>
   </si>
   <si>
-    <t>Rosas Aguilar Claudia Leonor</t>
-  </si>
-  <si>
-    <t>Moreno Aroyo Anél</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -221,13 +221,25 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>CRUZ</t>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>VELUETA</t>
+  </si>
+  <si>
+    <t>VIVANCO</t>
+  </si>
+  <si>
+    <t>ABREGO</t>
   </si>
   <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>MOLINA</t>
+    <t>LARRACILLA</t>
+  </si>
+  <si>
+    <t>MIXCOHUA</t>
   </si>
   <si>
     <t>REYES</t>
@@ -236,52 +248,70 @@
     <t>ROJAS</t>
   </si>
   <si>
-    <t>MELO</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>RIOS</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>NIEVES</t>
+    <t>ZGAIP</t>
+  </si>
+  <si>
+    <t>CERON</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>SOLIS</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
   </si>
   <si>
     <t>TETLA</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
+    <t>AMADOR</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
   </si>
   <si>
     <t>COXCAHUA</t>
   </si>
   <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>CORREA</t>
-  </si>
-  <si>
-    <t>ESTRELLA ESMERALDA</t>
-  </si>
-  <si>
-    <t>ESTRELLA RUBI</t>
+    <t>OJEDA</t>
+  </si>
+  <si>
+    <t>KEVIN IVAN</t>
+  </si>
+  <si>
+    <t>DANNAE ADALID</t>
+  </si>
+  <si>
+    <t>LUIS AARON</t>
+  </si>
+  <si>
+    <t>SULU ALAN</t>
+  </si>
+  <si>
+    <t>JAIR</t>
+  </si>
+  <si>
+    <t>DORIAN ALEXANDER</t>
   </si>
   <si>
     <t>HECTOR</t>
   </si>
   <si>
-    <t>LEONARDO GABRIEL</t>
+    <t>JOSELYN</t>
+  </si>
+  <si>
+    <t>MONICA</t>
+  </si>
+  <si>
+    <t>YAMILETH</t>
   </si>
   <si>
     <t>VICTOR JESUS</t>
@@ -290,25 +320,7 @@
     <t>JONATHAN ISAI</t>
   </si>
   <si>
-    <t>JAIR</t>
-  </si>
-  <si>
-    <t>DORIAN ALEXANDER</t>
-  </si>
-  <si>
-    <t>KENYA MARIANA</t>
-  </si>
-  <si>
-    <t>SALMA JANET</t>
-  </si>
-  <si>
-    <t>ELIUD EDUARDO</t>
-  </si>
-  <si>
-    <t>KAORY AYELEN</t>
-  </si>
-  <si>
-    <t>JUAN CARLOS</t>
+    <t>ADAIR DE JESUS</t>
   </si>
 </sst>
 </file>
@@ -856,43 +868,43 @@
         <v>6</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y4">
         <v>5</v>
       </c>
       <c r="Z4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC4">
         <v>7</v>
@@ -945,25 +957,25 @@
         <v>10</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W5">
         <v>8</v>
@@ -1034,34 +1046,34 @@
         <v>9</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X6">
         <v>8</v>
       </c>
       <c r="Y6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z6">
         <v>9</v>
@@ -1070,10 +1082,10 @@
         <v>7</v>
       </c>
       <c r="AB6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC6">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -1087,7 +1099,7 @@
         <v>5</v>
       </c>
       <c r="D7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E7">
         <v>8</v>
@@ -1123,43 +1135,43 @@
         <v>7</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W7">
         <v>7</v>
       </c>
       <c r="X7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z7">
         <v>8</v>
       </c>
       <c r="AA7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC7">
         <v>8</v>
@@ -1212,43 +1224,43 @@
         <v>8</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W8">
         <v>7</v>
       </c>
       <c r="X8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z8">
         <v>8</v>
       </c>
       <c r="AA8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC8">
         <v>9</v>
@@ -1301,25 +1313,25 @@
         <v>5</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W9">
         <v>5</v>
@@ -1331,16 +1343,16 @@
         <v>5</v>
       </c>
       <c r="Z9">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AA9">
         <v>5</v>
       </c>
       <c r="AB9">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AC9">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:29">
@@ -1390,34 +1402,34 @@
         <v>9</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X10">
         <v>9</v>
       </c>
       <c r="Y10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z10">
         <v>10</v>
@@ -1426,10 +1438,10 @@
         <v>9</v>
       </c>
       <c r="AB10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC10">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -1479,34 +1491,34 @@
         <v>8</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X11">
         <v>8</v>
       </c>
       <c r="Y11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z11">
         <v>9</v>
@@ -1568,46 +1580,46 @@
         <v>7</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X12">
         <v>7</v>
       </c>
       <c r="Y12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA12">
         <v>5</v>
       </c>
       <c r="AB12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC12">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -1657,25 +1669,25 @@
         <v>9</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W13">
         <v>7</v>
@@ -1684,16 +1696,16 @@
         <v>7</v>
       </c>
       <c r="Y13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC13">
         <v>8</v>
@@ -1746,46 +1758,46 @@
         <v>8</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y14">
         <v>5</v>
       </c>
       <c r="Z14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC14">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:29">
@@ -1835,46 +1847,46 @@
         <v>6</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X15">
         <v>7</v>
       </c>
       <c r="Y15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA15">
         <v>5</v>
       </c>
       <c r="AB15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC15">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -1924,31 +1936,31 @@
         <v>7</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y16">
         <v>5</v>
@@ -1963,7 +1975,7 @@
         <v>6</v>
       </c>
       <c r="AC16">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:29">
@@ -2013,31 +2025,31 @@
         <v>10</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W17">
         <v>7</v>
       </c>
       <c r="X17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y17">
         <v>9</v>
@@ -2049,10 +2061,10 @@
         <v>9</v>
       </c>
       <c r="AB17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC17">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -2102,28 +2114,28 @@
         <v>6</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X18">
         <v>6</v>
@@ -2135,13 +2147,13 @@
         <v>7</v>
       </c>
       <c r="AA18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC18">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:29">
@@ -2191,25 +2203,25 @@
         <v>7</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W19">
         <v>6</v>
@@ -2218,16 +2230,16 @@
         <v>6</v>
       </c>
       <c r="Y19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z19">
         <v>9</v>
       </c>
       <c r="AA19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC19">
         <v>7</v>
@@ -2280,34 +2292,34 @@
         <v>10</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W20">
         <v>7</v>
       </c>
       <c r="X20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z20">
         <v>8</v>
@@ -2316,10 +2328,10 @@
         <v>8</v>
       </c>
       <c r="AB20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC20">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -2369,31 +2381,31 @@
         <v>6</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W21">
         <v>6</v>
       </c>
       <c r="X21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y21">
         <v>6</v>
@@ -2402,10 +2414,10 @@
         <v>8</v>
       </c>
       <c r="AA21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB21">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC21">
         <v>8</v>
@@ -2458,46 +2470,46 @@
         <v>9</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W22">
         <v>9</v>
       </c>
       <c r="X22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z22">
         <v>8</v>
       </c>
       <c r="AA22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC22">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:29">
@@ -2547,28 +2559,28 @@
         <v>6</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X23">
         <v>5</v>
@@ -2583,7 +2595,7 @@
         <v>5</v>
       </c>
       <c r="AB23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC23">
         <v>5</v>
@@ -2636,43 +2648,43 @@
         <v>8</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W24">
         <v>6</v>
       </c>
       <c r="X24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA24">
         <v>5</v>
       </c>
       <c r="AB24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC24">
         <v>9</v>
@@ -2725,28 +2737,28 @@
         <v>7</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X25">
         <v>7</v>
@@ -2758,7 +2770,7 @@
         <v>9</v>
       </c>
       <c r="AA25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB25">
         <v>8</v>
@@ -2814,46 +2826,46 @@
         <v>8</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y26">
         <v>7</v>
       </c>
       <c r="Z26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC26">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:29">
@@ -2903,28 +2915,28 @@
         <v>10</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X27">
         <v>6</v>
@@ -2939,10 +2951,10 @@
         <v>5</v>
       </c>
       <c r="AB27">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AC27">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:29">
@@ -2992,25 +3004,25 @@
         <v>10</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W28">
         <v>9</v>
@@ -3081,25 +3093,25 @@
         <v>10</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W29">
         <v>9</v>
@@ -3170,31 +3182,31 @@
         <v>6</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y30">
         <v>7</v>
@@ -3203,10 +3215,10 @@
         <v>8</v>
       </c>
       <c r="AA30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB30">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AC30">
         <v>7</v>
@@ -3259,46 +3271,46 @@
         <v>6</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y31">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA31">
         <v>5</v>
       </c>
       <c r="AB31">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC31">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:29">
@@ -3348,31 +3360,31 @@
         <v>7</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W32">
         <v>6</v>
       </c>
       <c r="X32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y32">
         <v>5</v>
@@ -3384,7 +3396,7 @@
         <v>5</v>
       </c>
       <c r="AB32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC32">
         <v>6</v>
@@ -3437,40 +3449,40 @@
         <v>7</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W33">
         <v>6</v>
       </c>
       <c r="X33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y33">
         <v>5</v>
       </c>
       <c r="Z33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB33">
         <v>7</v>
@@ -3648,25 +3660,25 @@
         <v>95</v>
       </c>
       <c r="P4">
-        <v>80</v>
+        <v>87.5</v>
       </c>
       <c r="Q4">
         <v>100</v>
       </c>
       <c r="R4">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S4">
         <v>100</v>
       </c>
       <c r="T4">
-        <v>90</v>
+        <v>93.3</v>
       </c>
       <c r="U4">
-        <v>100</v>
+        <v>95.7</v>
       </c>
       <c r="V4">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -3731,7 +3743,7 @@
         <v>100</v>
       </c>
       <c r="U5">
-        <v>96.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="V5">
         <v>100</v>
@@ -3790,7 +3802,7 @@
         <v>100</v>
       </c>
       <c r="R6">
-        <v>95</v>
+        <v>93.8</v>
       </c>
       <c r="S6">
         <v>100</v>
@@ -3802,7 +3814,7 @@
         <v>100</v>
       </c>
       <c r="V6">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -3864,7 +3876,7 @@
         <v>100</v>
       </c>
       <c r="T7">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="U7">
         <v>100</v>
@@ -3932,10 +3944,10 @@
         <v>100</v>
       </c>
       <c r="T8">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="U8">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V8">
         <v>100</v>
@@ -3988,25 +4000,25 @@
         <v>87.5</v>
       </c>
       <c r="P9">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="Q9">
-        <v>86.7</v>
+        <v>60.4</v>
       </c>
       <c r="R9">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="S9">
-        <v>96.7</v>
+        <v>60.4</v>
       </c>
       <c r="T9">
-        <v>80</v>
+        <v>53.3</v>
       </c>
       <c r="U9">
-        <v>87.5</v>
+        <v>59.6</v>
       </c>
       <c r="V9">
-        <v>87.5</v>
+        <v>89.09999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -4062,19 +4074,19 @@
         <v>100</v>
       </c>
       <c r="R10">
-        <v>95</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="S10">
         <v>100</v>
       </c>
       <c r="T10">
-        <v>90</v>
+        <v>93.3</v>
       </c>
       <c r="U10">
-        <v>100</v>
+        <v>95.7</v>
       </c>
       <c r="V10">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -4130,7 +4142,7 @@
         <v>100</v>
       </c>
       <c r="R11">
-        <v>97.5</v>
+        <v>95.3</v>
       </c>
       <c r="S11">
         <v>100</v>
@@ -4198,16 +4210,16 @@
         <v>100</v>
       </c>
       <c r="R12">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S12">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="T12">
         <v>100</v>
       </c>
       <c r="U12">
-        <v>100</v>
+        <v>95.7</v>
       </c>
       <c r="V12">
         <v>100</v>
@@ -4263,22 +4275,22 @@
         <v>100</v>
       </c>
       <c r="Q13">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="R13">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="S13">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="T13">
         <v>96.7</v>
       </c>
-      <c r="R13">
-        <v>97.5</v>
-      </c>
-      <c r="S13">
-        <v>100</v>
-      </c>
-      <c r="T13">
-        <v>95</v>
-      </c>
       <c r="U13">
-        <v>93.8</v>
+        <v>91.5</v>
       </c>
       <c r="V13">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -4331,22 +4343,22 @@
         <v>100</v>
       </c>
       <c r="Q14">
-        <v>93.3</v>
+        <v>95.8</v>
       </c>
       <c r="R14">
-        <v>97.5</v>
+        <v>93.8</v>
       </c>
       <c r="S14">
-        <v>100</v>
+        <v>91.7</v>
       </c>
       <c r="T14">
         <v>100</v>
       </c>
       <c r="U14">
-        <v>90.59999999999999</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="V14">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -4402,16 +4414,16 @@
         <v>100</v>
       </c>
       <c r="R15">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S15">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="T15">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="U15">
-        <v>100</v>
+        <v>95.7</v>
       </c>
       <c r="V15">
         <v>100</v>
@@ -4464,25 +4476,25 @@
         <v>75</v>
       </c>
       <c r="P16">
-        <v>85</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q16">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="R16">
-        <v>87.5</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="S16">
-        <v>86.7</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="T16">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="U16">
-        <v>87.5</v>
+        <v>87.2</v>
       </c>
       <c r="V16">
-        <v>75</v>
+        <v>84.40000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -4535,19 +4547,19 @@
         <v>100</v>
       </c>
       <c r="Q17">
-        <v>96.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="R17">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S17">
         <v>100</v>
       </c>
       <c r="T17">
-        <v>92.5</v>
+        <v>95</v>
       </c>
       <c r="U17">
-        <v>90.59999999999999</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="V17">
         <v>100</v>
@@ -4606,16 +4618,16 @@
         <v>100</v>
       </c>
       <c r="R18">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S18">
         <v>100</v>
       </c>
       <c r="T18">
-        <v>82.5</v>
+        <v>88.3</v>
       </c>
       <c r="U18">
-        <v>96.90000000000001</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="V18">
         <v>100</v>
@@ -4671,22 +4683,22 @@
         <v>100</v>
       </c>
       <c r="Q19">
-        <v>96.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="R19">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S19">
-        <v>93.3</v>
+        <v>91.7</v>
       </c>
       <c r="T19">
-        <v>87.5</v>
+        <v>91.7</v>
       </c>
       <c r="U19">
-        <v>100</v>
+        <v>95.7</v>
       </c>
       <c r="V19">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -4739,22 +4751,22 @@
         <v>100</v>
       </c>
       <c r="Q20">
-        <v>90</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="R20">
-        <v>92.5</v>
+        <v>95.3</v>
       </c>
       <c r="S20">
-        <v>93.3</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="T20">
         <v>100</v>
       </c>
       <c r="U20">
-        <v>90.59999999999999</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="V20">
-        <v>92.5</v>
+        <v>92.2</v>
       </c>
     </row>
     <row r="21" spans="1:22">
@@ -4807,22 +4819,22 @@
         <v>100</v>
       </c>
       <c r="Q21">
-        <v>93.3</v>
+        <v>93.8</v>
       </c>
       <c r="R21">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S21">
         <v>100</v>
       </c>
       <c r="T21">
-        <v>87.5</v>
+        <v>91.7</v>
       </c>
       <c r="U21">
-        <v>96.90000000000001</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="V21">
-        <v>92.5</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -4878,16 +4890,16 @@
         <v>100</v>
       </c>
       <c r="R22">
-        <v>97.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S22">
         <v>100</v>
       </c>
       <c r="T22">
-        <v>97.5</v>
+        <v>98.3</v>
       </c>
       <c r="U22">
-        <v>90.59999999999999</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="V22">
         <v>100</v>
@@ -4940,25 +4952,25 @@
         <v>100</v>
       </c>
       <c r="P23">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="Q23">
         <v>100</v>
       </c>
       <c r="R23">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S23">
         <v>100</v>
       </c>
       <c r="T23">
-        <v>90</v>
+        <v>93.3</v>
       </c>
       <c r="U23">
+        <v>93.59999999999999</v>
+      </c>
+      <c r="V23">
         <v>96.90000000000001</v>
-      </c>
-      <c r="V23">
-        <v>100</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -5014,19 +5026,19 @@
         <v>100</v>
       </c>
       <c r="R24">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S24">
-        <v>96.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="T24">
-        <v>82.5</v>
+        <v>88.3</v>
       </c>
       <c r="U24">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="V24">
-        <v>92.5</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -5091,10 +5103,10 @@
         <v>100</v>
       </c>
       <c r="U25">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="V25">
         <v>96.90000000000001</v>
-      </c>
-      <c r="V25">
-        <v>95</v>
       </c>
     </row>
     <row r="26" spans="1:22">
@@ -5150,19 +5162,19 @@
         <v>100</v>
       </c>
       <c r="R26">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S26">
+        <v>95.8</v>
+      </c>
+      <c r="T26">
         <v>93.3</v>
       </c>
-      <c r="T26">
-        <v>90</v>
-      </c>
       <c r="U26">
-        <v>96.90000000000001</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="V26">
-        <v>92.5</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="27" spans="1:22">
@@ -5212,7 +5224,7 @@
         <v>100</v>
       </c>
       <c r="P27">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="Q27">
         <v>100</v>
@@ -5221,13 +5233,13 @@
         <v>100</v>
       </c>
       <c r="S27">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="T27">
         <v>100</v>
       </c>
       <c r="U27">
-        <v>96.90000000000001</v>
+        <v>91.5</v>
       </c>
       <c r="V27">
         <v>100</v>
@@ -5286,7 +5298,7 @@
         <v>100</v>
       </c>
       <c r="R28">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S28">
         <v>100</v>
@@ -5295,10 +5307,10 @@
         <v>100</v>
       </c>
       <c r="U28">
+        <v>100</v>
+      </c>
+      <c r="V28">
         <v>96.90000000000001</v>
-      </c>
-      <c r="V28">
-        <v>95</v>
       </c>
     </row>
     <row r="29" spans="1:22">
@@ -5354,10 +5366,10 @@
         <v>100</v>
       </c>
       <c r="R29">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S29">
-        <v>96.7</v>
+        <v>93.8</v>
       </c>
       <c r="T29">
         <v>100</v>
@@ -5416,7 +5428,7 @@
         <v>100</v>
       </c>
       <c r="P30">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="Q30">
         <v>100</v>
@@ -5431,7 +5443,7 @@
         <v>100</v>
       </c>
       <c r="U30">
-        <v>100</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="V30">
         <v>100</v>
@@ -5490,19 +5502,19 @@
         <v>100</v>
       </c>
       <c r="R31">
-        <v>97.5</v>
+        <v>93.8</v>
       </c>
       <c r="S31">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="T31">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="U31">
-        <v>93.8</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="V31">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="32" spans="1:22">
@@ -5552,10 +5564,10 @@
         <v>100</v>
       </c>
       <c r="P32">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="Q32">
-        <v>93.3</v>
+        <v>95.8</v>
       </c>
       <c r="R32">
         <v>100</v>
@@ -5564,10 +5576,10 @@
         <v>100</v>
       </c>
       <c r="T32">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="U32">
-        <v>96.90000000000001</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="V32">
         <v>100</v>
@@ -5620,13 +5632,13 @@
         <v>100</v>
       </c>
       <c r="P33">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="Q33">
         <v>100</v>
       </c>
       <c r="R33">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S33">
         <v>100</v>
@@ -5635,7 +5647,7 @@
         <v>100</v>
       </c>
       <c r="U33">
-        <v>96.90000000000001</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="V33">
         <v>100</v>
@@ -5704,19 +5716,19 @@
         <v>30</v>
       </c>
       <c r="D2">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E2">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F2" s="2">
-        <v>36.7</v>
+        <v>66.7</v>
       </c>
       <c r="G2" s="2">
-        <v>63.3</v>
+        <v>33.3</v>
       </c>
       <c r="H2">
-        <v>6.1</v>
+        <v>6.3</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5727,7 +5739,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>57</v>
@@ -5736,19 +5748,19 @@
         <v>30</v>
       </c>
       <c r="D3">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E3">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F3" s="2">
-        <v>63.3</v>
+        <v>70</v>
       </c>
       <c r="G3" s="2">
-        <v>36.7</v>
+        <v>30</v>
       </c>
       <c r="H3">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5759,7 +5771,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>58</v>
@@ -5768,19 +5780,19 @@
         <v>30</v>
       </c>
       <c r="D4">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="E4">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F4" s="2">
-        <v>66.7</v>
+        <v>90</v>
       </c>
       <c r="G4" s="2">
-        <v>33.3</v>
+        <v>10</v>
       </c>
       <c r="H4">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5791,7 +5803,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>59</v>
@@ -5800,19 +5812,19 @@
         <v>30</v>
       </c>
       <c r="D5">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="E5">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F5" s="2">
-        <v>73.3</v>
+        <v>96.7</v>
       </c>
       <c r="G5" s="2">
-        <v>26.7</v>
+        <v>3.3</v>
       </c>
       <c r="H5">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5823,7 +5835,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>60</v>
@@ -5832,16 +5844,16 @@
         <v>30</v>
       </c>
       <c r="D6">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2">
-        <v>86.7</v>
+        <v>96.7</v>
       </c>
       <c r="G6" s="2">
-        <v>13.3</v>
+        <v>3.3</v>
       </c>
       <c r="H6">
         <v>7.9</v>
@@ -5855,7 +5867,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
         <v>61</v>
@@ -5864,19 +5876,19 @@
         <v>30</v>
       </c>
       <c r="D7">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" s="2">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="G7" s="2">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="H7">
-        <v>8.300000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5887,7 +5899,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
         <v>62</v>
@@ -5896,19 +5908,19 @@
         <v>30</v>
       </c>
       <c r="D8">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="2">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="G8" s="2">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="H8">
-        <v>8.9</v>
+        <v>7.7</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -5922,7 +5934,7 @@
         <v>55</v>
       </c>
       <c r="B9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -5978,7 +5990,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6010,19 +6022,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920155</v>
+        <v>23330051920162</v>
       </c>
       <c r="B2" t="s">
         <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D2" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
         <v>57</v>
@@ -6033,16 +6045,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920155</v>
+        <v>23330051920162</v>
       </c>
       <c r="B3" t="s">
         <v>67</v>
       </c>
       <c r="C3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D3" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -6056,19 +6068,19 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920154</v>
+        <v>23330051920175</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D4" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
         <v>57</v>
@@ -6079,16 +6091,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920154</v>
+        <v>23330051920175</v>
       </c>
       <c r="B5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D5" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -6102,22 +6114,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920160</v>
+        <v>23330051920313</v>
       </c>
       <c r="B6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="D6" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -6125,22 +6137,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920160</v>
+        <v>23330051920313</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C7" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="D7" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -6148,19 +6160,19 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920166</v>
+        <v>23330051920151</v>
       </c>
       <c r="B8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D8" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
         <v>57</v>
@@ -6171,16 +6183,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920166</v>
+        <v>23330051920157</v>
       </c>
       <c r="B9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C9" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D9" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -6194,22 +6206,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920169</v>
+        <v>23330051920158</v>
       </c>
       <c r="B10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C10" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D10" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="E10" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -6217,22 +6229,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920169</v>
+        <v>23330051920160</v>
       </c>
       <c r="B11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C11" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D11" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="E11" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -6240,22 +6252,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920171</v>
+        <v>23330051920161</v>
       </c>
       <c r="B12" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C12" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="D12" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="E12" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -6263,22 +6275,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920171</v>
+        <v>23330051920164</v>
       </c>
       <c r="B13" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C13" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="D13" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -6286,22 +6298,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920157</v>
+        <v>23330051920316</v>
       </c>
       <c r="B14" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C14" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D14" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="E14" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F14" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -6309,16 +6321,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330051920158</v>
+        <v>23330051920169</v>
       </c>
       <c r="B15" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C15" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="D15" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="E15" t="s">
         <v>9</v>
@@ -6332,16 +6344,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>23330051920165</v>
+        <v>23330051920171</v>
       </c>
       <c r="B16" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C16" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="D16" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="E16" t="s">
         <v>9</v>
@@ -6355,93 +6367,24 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>23330051920167</v>
+        <v>23330051920176</v>
       </c>
       <c r="B17" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C17" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="D17" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="E17" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F17" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>23330051920354</v>
-      </c>
-      <c r="B18" t="s">
-        <v>70</v>
-      </c>
-      <c r="C18" t="s">
-        <v>82</v>
-      </c>
-      <c r="D18" t="s">
-        <v>94</v>
-      </c>
-      <c r="E18" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18" t="s">
-        <v>56</v>
-      </c>
-      <c r="G18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>23330051920170</v>
-      </c>
-      <c r="B19" t="s">
-        <v>74</v>
-      </c>
-      <c r="C19" t="s">
-        <v>83</v>
-      </c>
-      <c r="D19" t="s">
-        <v>95</v>
-      </c>
-      <c r="E19" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19" t="s">
-        <v>56</v>
-      </c>
-      <c r="G19">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>23330051920174</v>
-      </c>
-      <c r="B20" t="s">
-        <v>75</v>
-      </c>
-      <c r="C20" t="s">
-        <v>75</v>
-      </c>
-      <c r="D20" t="s">
-        <v>96</v>
-      </c>
-      <c r="E20" t="s">
-        <v>5</v>
-      </c>
-      <c r="F20" t="s">
-        <v>58</v>
-      </c>
-      <c r="G20">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1FM - Estadisticos 20231.xlsx
+++ b/grupos/1FM - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="101">
   <si>
     <t>Materia</t>
   </si>
@@ -56,6 +56,9 @@
     <t>Pensamiento matemático I</t>
   </si>
   <si>
+    <t>Recursos socioemocionales I</t>
+  </si>
+  <si>
     <t>Nombre</t>
   </si>
   <si>
@@ -183,9 +186,6 @@
   </si>
   <si>
     <t>Por_Blancos</t>
-  </si>
-  <si>
-    <t>Recursos socioemocionales I</t>
   </si>
   <si>
     <t>Duran Amezcua María Angélica</t>
@@ -682,13 +682,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC33"/>
+  <dimension ref="A1:AG33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29">
+    <row r="1" spans="1:33">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -699,35 +699,39 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="1"/>
+      <c r="J1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="1"/>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
-      <c r="W1" s="1" t="s">
-        <v>4</v>
-      </c>
+      <c r="W1" s="1"/>
       <c r="X1" s="1"/>
       <c r="Y1" s="1"/>
-      <c r="Z1" s="1"/>
+      <c r="Z1" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="AA1" s="1"/>
       <c r="AB1" s="1"/>
       <c r="AC1" s="1"/>
-    </row>
-    <row r="2" spans="1:29">
+      <c r="AD1" s="1"/>
+      <c r="AE1" s="1"/>
+      <c r="AF1" s="1"/>
+      <c r="AG1" s="1"/>
+    </row>
+    <row r="2" spans="1:33">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -753,77 +757,89 @@
         <v>11</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="P2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="P2" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="Q2" s="1" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="X2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="W2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="Y2" s="1" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AA2" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AB2" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF2" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:29">
+      <c r="AG2" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:33">
       <c r="A3" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:29">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:33">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B4">
         <v>5</v>
@@ -847,72 +863,84 @@
         <v>8</v>
       </c>
       <c r="I4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K4">
         <v>6</v>
       </c>
       <c r="L4">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M4">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N4">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="O4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P4">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Q4">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R4">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="S4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U4">
         <v>5</v>
       </c>
       <c r="V4">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="W4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA4">
         <v>6</v>
       </c>
       <c r="AB4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AC4">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="1:29">
+      <c r="AD4">
+        <v>6</v>
+      </c>
+      <c r="AE4">
+        <v>7</v>
+      </c>
+      <c r="AF4">
+        <v>7</v>
+      </c>
+      <c r="AG4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:33">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B5">
         <v>7</v>
@@ -936,19 +964,19 @@
         <v>9</v>
       </c>
       <c r="I5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K5">
         <v>10</v>
       </c>
       <c r="L5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N5">
         <v>10</v>
@@ -957,31 +985,31 @@
         <v>10</v>
       </c>
       <c r="P5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q5">
         <v>10</v>
       </c>
       <c r="R5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T5">
         <v>10</v>
       </c>
       <c r="U5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V5">
         <v>10</v>
       </c>
       <c r="W5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y5">
         <v>10</v>
@@ -990,18 +1018,30 @@
         <v>8</v>
       </c>
       <c r="AA5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB5">
         <v>10</v>
       </c>
       <c r="AC5">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:29">
+        <v>8</v>
+      </c>
+      <c r="AD5">
+        <v>10</v>
+      </c>
+      <c r="AE5">
+        <v>10</v>
+      </c>
+      <c r="AF5">
+        <v>10</v>
+      </c>
+      <c r="AG5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:33">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6">
         <v>7</v>
@@ -1025,72 +1065,84 @@
         <v>10</v>
       </c>
       <c r="I6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M6">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="N6">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="O6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P6">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="Q6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R6">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="S6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T6">
         <v>8</v>
       </c>
       <c r="U6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AA6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC6">
         <v>9</v>
       </c>
-    </row>
-    <row r="7" spans="1:29">
+      <c r="AD6">
+        <v>7</v>
+      </c>
+      <c r="AE6">
+        <v>9</v>
+      </c>
+      <c r="AF6">
+        <v>9</v>
+      </c>
+      <c r="AG6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:33">
       <c r="A7" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B7">
         <v>7</v>
@@ -1114,43 +1166,43 @@
         <v>9</v>
       </c>
       <c r="I7">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J7">
         <v>6</v>
       </c>
       <c r="K7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M7">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N7">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="O7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="P7">
         <v>7</v>
       </c>
       <c r="Q7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S7">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T7">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U7">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V7">
         <v>8</v>
@@ -1159,27 +1211,39 @@
         <v>7</v>
       </c>
       <c r="X7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA7">
         <v>6</v>
       </c>
       <c r="AB7">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AC7">
         <v>8</v>
       </c>
-    </row>
-    <row r="8" spans="1:29">
+      <c r="AD7">
+        <v>6</v>
+      </c>
+      <c r="AE7">
+        <v>9</v>
+      </c>
+      <c r="AF7">
+        <v>8</v>
+      </c>
+      <c r="AG7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B8">
         <v>7</v>
@@ -1203,22 +1267,22 @@
         <v>10</v>
       </c>
       <c r="I8">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J8">
         <v>6</v>
       </c>
       <c r="K8">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L8">
         <v>8</v>
       </c>
       <c r="M8">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N8">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O8">
         <v>8</v>
@@ -1227,48 +1291,60 @@
         <v>8</v>
       </c>
       <c r="Q8">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R8">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="S8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T8">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U8">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V8">
         <v>8</v>
       </c>
       <c r="W8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X8">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y8">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA8">
         <v>6</v>
       </c>
       <c r="AB8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC8">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:29">
+        <v>8</v>
+      </c>
+      <c r="AD8">
+        <v>6</v>
+      </c>
+      <c r="AE8">
+        <v>8</v>
+      </c>
+      <c r="AF8">
+        <v>9</v>
+      </c>
+      <c r="AG8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B9">
         <v>5</v>
@@ -1292,19 +1368,19 @@
         <v>8</v>
       </c>
       <c r="I9">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J9">
         <v>5</v>
       </c>
       <c r="K9">
+        <v>5</v>
+      </c>
+      <c r="L9">
         <v>0</v>
       </c>
-      <c r="L9">
-        <v>7</v>
-      </c>
       <c r="M9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N9">
         <v>5</v>
@@ -1316,10 +1392,10 @@
         <v>5</v>
       </c>
       <c r="Q9">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S9">
         <v>5</v>
@@ -1331,7 +1407,7 @@
         <v>5</v>
       </c>
       <c r="V9">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W9">
         <v>5</v>
@@ -1340,7 +1416,7 @@
         <v>5</v>
       </c>
       <c r="Y9">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z9">
         <v>5</v>
@@ -1352,12 +1428,24 @@
         <v>5</v>
       </c>
       <c r="AC9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:29">
+        <v>5</v>
+      </c>
+      <c r="AD9">
+        <v>5</v>
+      </c>
+      <c r="AE9">
+        <v>5</v>
+      </c>
+      <c r="AF9">
+        <v>6</v>
+      </c>
+      <c r="AG9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33">
       <c r="A10" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B10">
         <v>7</v>
@@ -1381,31 +1469,31 @@
         <v>8</v>
       </c>
       <c r="I10">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J10">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K10">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L10">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M10">
         <v>10</v>
       </c>
       <c r="N10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O10">
         <v>9</v>
       </c>
       <c r="P10">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="Q10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R10">
         <v>5</v>
@@ -1414,39 +1502,51 @@
         <v>9</v>
       </c>
       <c r="T10">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="U10">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="V10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z10">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA10">
         <v>9</v>
       </c>
       <c r="AB10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC10">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:29">
+        <v>10</v>
+      </c>
+      <c r="AD10">
+        <v>9</v>
+      </c>
+      <c r="AE10">
+        <v>8</v>
+      </c>
+      <c r="AF10">
+        <v>8</v>
+      </c>
+      <c r="AG10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33">
       <c r="A11" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B11">
         <v>8</v>
@@ -1470,10 +1570,10 @@
         <v>10</v>
       </c>
       <c r="I11">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J11">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K11">
         <v>9</v>
@@ -1482,60 +1582,72 @@
         <v>9</v>
       </c>
       <c r="M11">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N11">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O11">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R11">
         <v>7</v>
       </c>
       <c r="S11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V11">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="W11">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y11">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z11">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AA11">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AB11">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC11">
         <v>9</v>
       </c>
-    </row>
-    <row r="12" spans="1:29">
+      <c r="AD11">
+        <v>5</v>
+      </c>
+      <c r="AE11">
+        <v>10</v>
+      </c>
+      <c r="AF11">
+        <v>9</v>
+      </c>
+      <c r="AG11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:33">
       <c r="A12" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12">
         <v>7</v>
@@ -1559,72 +1671,84 @@
         <v>8</v>
       </c>
       <c r="I12">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L12">
         <v>8</v>
       </c>
       <c r="M12">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O12">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q12">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R12">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="S12">
         <v>7</v>
       </c>
       <c r="T12">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="U12">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W12">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="X12">
         <v>7</v>
       </c>
       <c r="Y12">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z12">
         <v>7</v>
       </c>
       <c r="AA12">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB12">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AC12">
         <v>7</v>
       </c>
-    </row>
-    <row r="13" spans="1:29">
+      <c r="AD12">
+        <v>5</v>
+      </c>
+      <c r="AE12">
+        <v>6</v>
+      </c>
+      <c r="AF12">
+        <v>7</v>
+      </c>
+      <c r="AG12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33">
       <c r="A13" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13">
         <v>6</v>
@@ -1648,72 +1772,84 @@
         <v>7</v>
       </c>
       <c r="I13">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K13">
         <v>6</v>
       </c>
       <c r="L13">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M13">
         <v>9</v>
       </c>
       <c r="N13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q13">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R13">
         <v>8</v>
       </c>
       <c r="S13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U13">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V13">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y13">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC13">
         <v>8</v>
       </c>
-    </row>
-    <row r="14" spans="1:29">
+      <c r="AD13">
+        <v>8</v>
+      </c>
+      <c r="AE13">
+        <v>8</v>
+      </c>
+      <c r="AF13">
+        <v>8</v>
+      </c>
+      <c r="AG13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33">
       <c r="A14" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B14">
         <v>6</v>
@@ -1737,16 +1873,16 @@
         <v>9</v>
       </c>
       <c r="I14">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J14">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="K14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M14">
         <v>8</v>
@@ -1761,48 +1897,60 @@
         <v>8</v>
       </c>
       <c r="Q14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="S14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V14">
         <v>6</v>
       </c>
       <c r="W14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y14">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AA14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AC14">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:29">
+      <c r="AD14">
+        <v>6</v>
+      </c>
+      <c r="AE14">
+        <v>8</v>
+      </c>
+      <c r="AF14">
+        <v>8</v>
+      </c>
+      <c r="AG14">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33">
       <c r="A15" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B15">
         <v>5</v>
@@ -1826,46 +1974,46 @@
         <v>5</v>
       </c>
       <c r="I15">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J15">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L15">
         <v>9</v>
       </c>
       <c r="M15">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="N15">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="O15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S15">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W15">
         <v>6</v>
@@ -1874,24 +2022,36 @@
         <v>7</v>
       </c>
       <c r="Y15">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB15">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AC15">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:29">
+        <v>7</v>
+      </c>
+      <c r="AD15">
+        <v>5</v>
+      </c>
+      <c r="AE15">
+        <v>8</v>
+      </c>
+      <c r="AF15">
+        <v>6</v>
+      </c>
+      <c r="AG15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33">
       <c r="A16" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B16">
         <v>5</v>
@@ -1915,72 +2075,84 @@
         <v>4</v>
       </c>
       <c r="I16">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L16">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M16">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N16">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O16">
         <v>7</v>
       </c>
       <c r="P16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q16">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R16">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="S16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U16">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W16">
         <v>6</v>
       </c>
       <c r="X16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y16">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC16">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:29">
+        <v>7</v>
+      </c>
+      <c r="AD16">
+        <v>5</v>
+      </c>
+      <c r="AE16">
+        <v>6</v>
+      </c>
+      <c r="AF16">
+        <v>6</v>
+      </c>
+      <c r="AG16">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:33">
       <c r="A17" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B17">
         <v>6</v>
@@ -2004,16 +2176,16 @@
         <v>9</v>
       </c>
       <c r="I17">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J17">
         <v>8</v>
       </c>
       <c r="K17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M17">
         <v>10</v>
@@ -2025,7 +2197,7 @@
         <v>10</v>
       </c>
       <c r="P17">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Q17">
         <v>10</v>
@@ -2037,25 +2209,25 @@
         <v>10</v>
       </c>
       <c r="T17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U17">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V17">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z17">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA17">
         <v>9</v>
@@ -2064,12 +2236,24 @@
         <v>9</v>
       </c>
       <c r="AC17">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="18" spans="1:29">
+        <v>10</v>
+      </c>
+      <c r="AD17">
+        <v>9</v>
+      </c>
+      <c r="AE17">
+        <v>9</v>
+      </c>
+      <c r="AF17">
+        <v>9</v>
+      </c>
+      <c r="AG17">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:33">
       <c r="A18" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B18">
         <v>5</v>
@@ -2093,46 +2277,46 @@
         <v>7</v>
       </c>
       <c r="I18">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N18">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="O18">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P18">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Q18">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R18">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="S18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T18">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U18">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V18">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W18">
         <v>6</v>
@@ -2141,24 +2325,36 @@
         <v>6</v>
       </c>
       <c r="Y18">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA18">
         <v>6</v>
       </c>
       <c r="AB18">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AC18">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="19" spans="1:29">
+        <v>7</v>
+      </c>
+      <c r="AD18">
+        <v>6</v>
+      </c>
+      <c r="AE18">
+        <v>8</v>
+      </c>
+      <c r="AF18">
+        <v>6</v>
+      </c>
+      <c r="AG18">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:33">
       <c r="A19" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B19">
         <v>5</v>
@@ -2182,72 +2378,84 @@
         <v>7</v>
       </c>
       <c r="I19">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J19">
         <v>7</v>
       </c>
       <c r="K19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M19">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N19">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P19">
         <v>7</v>
       </c>
       <c r="Q19">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S19">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T19">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U19">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="V19">
         <v>8</v>
       </c>
       <c r="W19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X19">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y19">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z19">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AA19">
         <v>6</v>
       </c>
       <c r="AB19">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AC19">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="20" spans="1:29">
+        <v>9</v>
+      </c>
+      <c r="AD19">
+        <v>6</v>
+      </c>
+      <c r="AE19">
+        <v>8</v>
+      </c>
+      <c r="AF19">
+        <v>7</v>
+      </c>
+      <c r="AG19">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:33">
       <c r="A20" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B20">
         <v>6</v>
@@ -2271,13 +2479,13 @@
         <v>7</v>
       </c>
       <c r="I20">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J20">
         <v>7</v>
       </c>
       <c r="K20">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="L20">
         <v>10</v>
@@ -2286,57 +2494,69 @@
         <v>10</v>
       </c>
       <c r="N20">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O20">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="P20">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q20">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="R20">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S20">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T20">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U20">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="V20">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="W20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X20">
         <v>5</v>
       </c>
       <c r="Y20">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA20">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AB20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC20">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="21" spans="1:29">
+        <v>8</v>
+      </c>
+      <c r="AD20">
+        <v>8</v>
+      </c>
+      <c r="AE20">
+        <v>8</v>
+      </c>
+      <c r="AF20">
+        <v>7</v>
+      </c>
+      <c r="AG20">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:33">
       <c r="A21" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B21">
         <v>7</v>
@@ -2360,72 +2580,84 @@
         <v>9</v>
       </c>
       <c r="I21">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J21">
         <v>5</v>
       </c>
       <c r="K21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L21">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M21">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N21">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O21">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q21">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U21">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="V21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X21">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y21">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z21">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AA21">
         <v>6</v>
       </c>
       <c r="AB21">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AC21">
         <v>8</v>
       </c>
-    </row>
-    <row r="22" spans="1:29">
+      <c r="AD21">
+        <v>6</v>
+      </c>
+      <c r="AE21">
+        <v>8</v>
+      </c>
+      <c r="AF21">
+        <v>8</v>
+      </c>
+      <c r="AG21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:33">
       <c r="A22" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B22">
         <v>9</v>
@@ -2449,72 +2681,84 @@
         <v>10</v>
       </c>
       <c r="I22">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L22">
         <v>8</v>
       </c>
       <c r="M22">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N22">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P22">
         <v>9</v>
       </c>
       <c r="Q22">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R22">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="S22">
         <v>7</v>
       </c>
       <c r="T22">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V22">
         <v>8</v>
       </c>
       <c r="W22">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="X22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y22">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB22">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AC22">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="23" spans="1:29">
+        <v>8</v>
+      </c>
+      <c r="AD22">
+        <v>6</v>
+      </c>
+      <c r="AE22">
+        <v>9</v>
+      </c>
+      <c r="AF22">
+        <v>9</v>
+      </c>
+      <c r="AG22">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:33">
       <c r="A23" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B23">
         <v>5</v>
@@ -2538,7 +2782,7 @@
         <v>5</v>
       </c>
       <c r="I23">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J23">
         <v>5</v>
@@ -2556,37 +2800,37 @@
         <v>5</v>
       </c>
       <c r="O23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P23">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Q23">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="R23">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="S23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X23">
         <v>5</v>
       </c>
       <c r="Y23">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z23">
         <v>6</v>
@@ -2595,15 +2839,27 @@
         <v>5</v>
       </c>
       <c r="AB23">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AC23">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:29">
+        <v>6</v>
+      </c>
+      <c r="AD23">
+        <v>5</v>
+      </c>
+      <c r="AE23">
+        <v>7</v>
+      </c>
+      <c r="AF23">
+        <v>5</v>
+      </c>
+      <c r="AG23">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:33">
       <c r="A24" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B24">
         <v>5</v>
@@ -2627,72 +2883,84 @@
         <v>9</v>
       </c>
       <c r="I24">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K24">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L24">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M24">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N24">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O24">
         <v>8</v>
       </c>
       <c r="P24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q24">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="S24">
         <v>8</v>
       </c>
       <c r="T24">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V24">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="W24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X24">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Y24">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z24">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AA24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC24">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="25" spans="1:29">
+        <v>8</v>
+      </c>
+      <c r="AD24">
+        <v>5</v>
+      </c>
+      <c r="AE24">
+        <v>8</v>
+      </c>
+      <c r="AF24">
+        <v>9</v>
+      </c>
+      <c r="AG24">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:33">
       <c r="A25" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B25">
         <v>8</v>
@@ -2716,10 +2984,10 @@
         <v>6</v>
       </c>
       <c r="I25">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K25">
         <v>8</v>
@@ -2728,60 +2996,72 @@
         <v>8</v>
       </c>
       <c r="M25">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O25">
         <v>7</v>
       </c>
       <c r="P25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q25">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T25">
         <v>7</v>
       </c>
       <c r="U25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V25">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X25">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y25">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z25">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AA25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC25">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="26" spans="1:29">
+        <v>9</v>
+      </c>
+      <c r="AD25">
+        <v>6</v>
+      </c>
+      <c r="AE25">
+        <v>8</v>
+      </c>
+      <c r="AF25">
+        <v>7</v>
+      </c>
+      <c r="AG25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:33">
       <c r="A26" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B26">
         <v>7</v>
@@ -2805,55 +3085,55 @@
         <v>7</v>
       </c>
       <c r="I26">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M26">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N26">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O26">
         <v>8</v>
       </c>
       <c r="P26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q26">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R26">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="S26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V26">
         <v>7</v>
       </c>
       <c r="W26">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="X26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y26">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z26">
         <v>8</v>
@@ -2862,15 +3142,27 @@
         <v>6</v>
       </c>
       <c r="AB26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC26">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="27" spans="1:29">
+        <v>8</v>
+      </c>
+      <c r="AD26">
+        <v>6</v>
+      </c>
+      <c r="AE26">
+        <v>8</v>
+      </c>
+      <c r="AF26">
+        <v>7</v>
+      </c>
+      <c r="AG26">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" spans="1:33">
       <c r="A27" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B27">
         <v>6</v>
@@ -2894,72 +3186,84 @@
         <v>8</v>
       </c>
       <c r="I27">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K27">
         <v>6</v>
       </c>
       <c r="L27">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M27">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="N27">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O27">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="P27">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q27">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S27">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T27">
         <v>6</v>
       </c>
       <c r="U27">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="V27">
         <v>6</v>
       </c>
       <c r="W27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X27">
         <v>6</v>
       </c>
       <c r="Y27">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z27">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AA27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC27">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="28" spans="1:29">
+        <v>9</v>
+      </c>
+      <c r="AD27">
+        <v>5</v>
+      </c>
+      <c r="AE27">
+        <v>7</v>
+      </c>
+      <c r="AF27">
+        <v>8</v>
+      </c>
+      <c r="AG27">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" spans="1:33">
       <c r="A28" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B28">
         <v>9</v>
@@ -2983,72 +3287,84 @@
         <v>10</v>
       </c>
       <c r="I28">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K28">
         <v>9</v>
       </c>
       <c r="L28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M28">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N28">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O28">
         <v>10</v>
       </c>
       <c r="P28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q28">
         <v>10</v>
       </c>
       <c r="R28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S28">
         <v>10</v>
       </c>
       <c r="T28">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="U28">
         <v>10</v>
       </c>
       <c r="V28">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA28">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AB28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC28">
         <v>10</v>
       </c>
-    </row>
-    <row r="29" spans="1:29">
+      <c r="AD28">
+        <v>7</v>
+      </c>
+      <c r="AE28">
+        <v>10</v>
+      </c>
+      <c r="AF28">
+        <v>10</v>
+      </c>
+      <c r="AG28">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="1:33">
       <c r="A29" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B29">
         <v>9</v>
@@ -3072,13 +3388,13 @@
         <v>8</v>
       </c>
       <c r="I29">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J29">
         <v>8</v>
       </c>
       <c r="K29">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L29">
         <v>10</v>
@@ -3096,19 +3412,19 @@
         <v>10</v>
       </c>
       <c r="Q29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R29">
         <v>10</v>
       </c>
       <c r="S29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T29">
         <v>10</v>
       </c>
       <c r="U29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V29">
         <v>10</v>
@@ -3117,27 +3433,39 @@
         <v>9</v>
       </c>
       <c r="X29">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z29">
         <v>9</v>
       </c>
       <c r="AA29">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC29">
         <v>9</v>
       </c>
-    </row>
-    <row r="30" spans="1:29">
+      <c r="AD29">
+        <v>10</v>
+      </c>
+      <c r="AE29">
+        <v>10</v>
+      </c>
+      <c r="AF29">
+        <v>9</v>
+      </c>
+      <c r="AG29">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="1:33">
       <c r="A30" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B30">
         <v>5</v>
@@ -3161,31 +3489,31 @@
         <v>7</v>
       </c>
       <c r="I30">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K30">
         <v>6</v>
       </c>
       <c r="L30">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N30">
         <v>7</v>
       </c>
       <c r="O30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P30">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Q30">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R30">
         <v>8</v>
@@ -3194,39 +3522,51 @@
         <v>8</v>
       </c>
       <c r="T30">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U30">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="V30">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="W30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y30">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z30">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AA30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB30">
         <v>7</v>
       </c>
       <c r="AC30">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="31" spans="1:29">
+        <v>8</v>
+      </c>
+      <c r="AD30">
+        <v>6</v>
+      </c>
+      <c r="AE30">
+        <v>7</v>
+      </c>
+      <c r="AF30">
+        <v>7</v>
+      </c>
+      <c r="AG30">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31" spans="1:33">
       <c r="A31" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B31">
         <v>6</v>
@@ -3250,72 +3590,84 @@
         <v>5</v>
       </c>
       <c r="I31">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J31">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K31">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M31">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N31">
         <v>5</v>
       </c>
       <c r="O31">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P31">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q31">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R31">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T31">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V31">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="W31">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X31">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Y31">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z31">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB31">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC31">
         <v>7</v>
       </c>
-    </row>
-    <row r="32" spans="1:29">
+      <c r="AD31">
+        <v>5</v>
+      </c>
+      <c r="AE31">
+        <v>6</v>
+      </c>
+      <c r="AF31">
+        <v>7</v>
+      </c>
+      <c r="AG31">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" spans="1:33">
       <c r="A32" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B32">
         <v>7</v>
@@ -3339,22 +3691,22 @@
         <v>5</v>
       </c>
       <c r="I32">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J32">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L32">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N32">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O32">
         <v>7</v>
@@ -3363,48 +3715,60 @@
         <v>7</v>
       </c>
       <c r="Q32">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R32">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S32">
         <v>7</v>
       </c>
       <c r="T32">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W32">
         <v>6</v>
       </c>
       <c r="X32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y32">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z32">
         <v>6</v>
       </c>
       <c r="AA32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB32">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AC32">
         <v>6</v>
       </c>
-    </row>
-    <row r="33" spans="1:29">
+      <c r="AD32">
+        <v>5</v>
+      </c>
+      <c r="AE32">
+        <v>7</v>
+      </c>
+      <c r="AF32">
+        <v>6</v>
+      </c>
+      <c r="AG32">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33" spans="1:33">
       <c r="A33" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B33">
         <v>7</v>
@@ -3428,7 +3792,7 @@
         <v>9</v>
       </c>
       <c r="I33">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J33">
         <v>5</v>
@@ -3437,34 +3801,34 @@
         <v>5</v>
       </c>
       <c r="L33">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N33">
         <v>6</v>
       </c>
       <c r="O33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q33">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T33">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V33">
         <v>7</v>
@@ -3473,30 +3837,42 @@
         <v>6</v>
       </c>
       <c r="X33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y33">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA33">
         <v>6</v>
       </c>
       <c r="AB33">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AC33">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="AD33">
+        <v>6</v>
+      </c>
+      <c r="AE33">
+        <v>7</v>
+      </c>
+      <c r="AF33">
+        <v>8</v>
+      </c>
+      <c r="AG33">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="I1:O1"/>
-    <mergeCell ref="P1:V1"/>
-    <mergeCell ref="W1:AC1"/>
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="J1:Q1"/>
+    <mergeCell ref="R1:Y1"/>
+    <mergeCell ref="Z1:AG1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3504,16 +3880,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V33"/>
+  <dimension ref="A1:Y33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22">
+    <row r="1" spans="1:25">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -3521,26 +3897,29 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
-      <c r="I1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="J1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
-      <c r="P1" s="1" t="s">
-        <v>45</v>
-      </c>
+      <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
+      <c r="R1" s="1" t="s">
+        <v>46</v>
+      </c>
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
-    </row>
-    <row r="2" spans="1:22">
+      <c r="W1" s="1"/>
+      <c r="X1" s="1"/>
+      <c r="Y1" s="1"/>
+    </row>
+    <row r="2" spans="1:25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -3566,56 +3945,65 @@
         <v>11</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="P2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="P2" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="Q2" s="1" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="X2" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:22">
+      <c r="Y2" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25">
       <c r="A3" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B4">
         <v>100</v>
@@ -3639,51 +4027,60 @@
         <v>90</v>
       </c>
       <c r="I4">
+        <v>100</v>
+      </c>
+      <c r="J4">
         <v>80</v>
       </c>
-      <c r="J4">
-        <v>100</v>
-      </c>
       <c r="K4">
+        <v>100</v>
+      </c>
+      <c r="L4">
         <v>97.5</v>
       </c>
-      <c r="L4">
-        <v>100</v>
-      </c>
       <c r="M4">
+        <v>100</v>
+      </c>
+      <c r="N4">
         <v>90</v>
       </c>
-      <c r="N4">
-        <v>100</v>
-      </c>
       <c r="O4">
+        <v>100</v>
+      </c>
+      <c r="P4">
         <v>95</v>
       </c>
-      <c r="P4">
+      <c r="Q4">
+        <v>100</v>
+      </c>
+      <c r="R4">
         <v>87.5</v>
       </c>
-      <c r="Q4">
-        <v>100</v>
-      </c>
-      <c r="R4">
+      <c r="S4">
+        <v>100</v>
+      </c>
+      <c r="T4">
         <v>98.40000000000001</v>
       </c>
-      <c r="S4">
-        <v>100</v>
-      </c>
-      <c r="T4">
+      <c r="U4">
+        <v>100</v>
+      </c>
+      <c r="V4">
         <v>93.3</v>
       </c>
-      <c r="U4">
+      <c r="W4">
         <v>95.7</v>
       </c>
-      <c r="V4">
+      <c r="X4">
         <v>96.90000000000001</v>
       </c>
-    </row>
-    <row r="5" spans="1:22">
+      <c r="Y4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B5">
         <v>100</v>
@@ -3722,11 +4119,11 @@
         <v>100</v>
       </c>
       <c r="N5">
+        <v>100</v>
+      </c>
+      <c r="O5">
         <v>96.90000000000001</v>
       </c>
-      <c r="O5">
-        <v>100</v>
-      </c>
       <c r="P5">
         <v>100</v>
       </c>
@@ -3748,10 +4145,19 @@
       <c r="V5">
         <v>100</v>
       </c>
-    </row>
-    <row r="6" spans="1:22">
+      <c r="W5">
+        <v>100</v>
+      </c>
+      <c r="X5">
+        <v>100</v>
+      </c>
+      <c r="Y5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6">
         <v>100</v>
@@ -3781,11 +4187,11 @@
         <v>100</v>
       </c>
       <c r="K6">
+        <v>100</v>
+      </c>
+      <c r="L6">
         <v>95</v>
       </c>
-      <c r="L6">
-        <v>100</v>
-      </c>
       <c r="M6">
         <v>100</v>
       </c>
@@ -3793,33 +4199,42 @@
         <v>100</v>
       </c>
       <c r="O6">
+        <v>100</v>
+      </c>
+      <c r="P6">
         <v>97.5</v>
       </c>
-      <c r="P6">
-        <v>100</v>
-      </c>
       <c r="Q6">
         <v>100</v>
       </c>
       <c r="R6">
+        <v>100</v>
+      </c>
+      <c r="S6">
+        <v>100</v>
+      </c>
+      <c r="T6">
         <v>93.8</v>
       </c>
-      <c r="S6">
-        <v>100</v>
-      </c>
-      <c r="T6">
-        <v>100</v>
-      </c>
       <c r="U6">
         <v>100</v>
       </c>
       <c r="V6">
+        <v>100</v>
+      </c>
+      <c r="W6">
+        <v>100</v>
+      </c>
+      <c r="X6">
         <v>98.40000000000001</v>
       </c>
-    </row>
-    <row r="7" spans="1:22">
+      <c r="Y6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25">
       <c r="A7" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B7">
         <v>100</v>
@@ -3855,11 +4270,11 @@
         <v>100</v>
       </c>
       <c r="M7">
+        <v>100</v>
+      </c>
+      <c r="N7">
         <v>95</v>
       </c>
-      <c r="N7">
-        <v>100</v>
-      </c>
       <c r="O7">
         <v>100</v>
       </c>
@@ -3876,18 +4291,27 @@
         <v>100</v>
       </c>
       <c r="T7">
+        <v>100</v>
+      </c>
+      <c r="U7">
+        <v>100</v>
+      </c>
+      <c r="V7">
         <v>96.7</v>
       </c>
-      <c r="U7">
-        <v>100</v>
-      </c>
-      <c r="V7">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22">
+      <c r="W7">
+        <v>100</v>
+      </c>
+      <c r="X7">
+        <v>100</v>
+      </c>
+      <c r="Y7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B8">
         <v>100</v>
@@ -3923,11 +4347,11 @@
         <v>100</v>
       </c>
       <c r="M8">
+        <v>100</v>
+      </c>
+      <c r="N8">
         <v>95</v>
       </c>
-      <c r="N8">
-        <v>100</v>
-      </c>
       <c r="O8">
         <v>100</v>
       </c>
@@ -3944,18 +4368,27 @@
         <v>100</v>
       </c>
       <c r="T8">
+        <v>100</v>
+      </c>
+      <c r="U8">
+        <v>100</v>
+      </c>
+      <c r="V8">
         <v>96.7</v>
       </c>
-      <c r="U8">
+      <c r="W8">
         <v>97.90000000000001</v>
       </c>
-      <c r="V8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22">
+      <c r="X8">
+        <v>100</v>
+      </c>
+      <c r="Y8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B9">
         <v>100</v>
@@ -3979,31 +4412,31 @@
         <v>90</v>
       </c>
       <c r="I9">
+        <v>100</v>
+      </c>
+      <c r="J9">
         <v>80</v>
       </c>
-      <c r="J9">
+      <c r="K9">
         <v>86.7</v>
       </c>
-      <c r="K9">
+      <c r="L9">
         <v>80</v>
       </c>
-      <c r="L9">
+      <c r="M9">
         <v>96.7</v>
       </c>
-      <c r="M9">
+      <c r="N9">
         <v>80</v>
-      </c>
-      <c r="N9">
-        <v>87.5</v>
       </c>
       <c r="O9">
         <v>87.5</v>
       </c>
       <c r="P9">
-        <v>50</v>
+        <v>87.5</v>
       </c>
       <c r="Q9">
-        <v>60.4</v>
+        <v>100</v>
       </c>
       <c r="R9">
         <v>50</v>
@@ -4012,18 +4445,27 @@
         <v>60.4</v>
       </c>
       <c r="T9">
+        <v>50</v>
+      </c>
+      <c r="U9">
+        <v>60.4</v>
+      </c>
+      <c r="V9">
         <v>53.3</v>
       </c>
-      <c r="U9">
+      <c r="W9">
         <v>59.6</v>
       </c>
-      <c r="V9">
+      <c r="X9">
         <v>89.09999999999999</v>
       </c>
-    </row>
-    <row r="10" spans="1:22">
+      <c r="Y9">
+        <v>66.7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25">
       <c r="A10" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B10">
         <v>100</v>
@@ -4053,45 +4495,54 @@
         <v>100</v>
       </c>
       <c r="K10">
+        <v>100</v>
+      </c>
+      <c r="L10">
         <v>95</v>
       </c>
-      <c r="L10">
-        <v>100</v>
-      </c>
       <c r="M10">
+        <v>100</v>
+      </c>
+      <c r="N10">
         <v>90</v>
       </c>
-      <c r="N10">
-        <v>100</v>
-      </c>
       <c r="O10">
+        <v>100</v>
+      </c>
+      <c r="P10">
         <v>95</v>
       </c>
-      <c r="P10">
-        <v>100</v>
-      </c>
       <c r="Q10">
         <v>100</v>
       </c>
       <c r="R10">
+        <v>100</v>
+      </c>
+      <c r="S10">
+        <v>100</v>
+      </c>
+      <c r="T10">
         <v>90.59999999999999</v>
       </c>
-      <c r="S10">
-        <v>100</v>
-      </c>
-      <c r="T10">
+      <c r="U10">
+        <v>100</v>
+      </c>
+      <c r="V10">
         <v>93.3</v>
       </c>
-      <c r="U10">
+      <c r="W10">
         <v>95.7</v>
       </c>
-      <c r="V10">
+      <c r="X10">
         <v>96.90000000000001</v>
       </c>
-    </row>
-    <row r="11" spans="1:22">
+      <c r="Y10">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25">
       <c r="A11" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B11">
         <v>100</v>
@@ -4121,11 +4572,11 @@
         <v>100</v>
       </c>
       <c r="K11">
+        <v>100</v>
+      </c>
+      <c r="L11">
         <v>97.5</v>
       </c>
-      <c r="L11">
-        <v>100</v>
-      </c>
       <c r="M11">
         <v>100</v>
       </c>
@@ -4142,24 +4593,33 @@
         <v>100</v>
       </c>
       <c r="R11">
+        <v>100</v>
+      </c>
+      <c r="S11">
+        <v>100</v>
+      </c>
+      <c r="T11">
         <v>95.3</v>
       </c>
-      <c r="S11">
-        <v>100</v>
-      </c>
-      <c r="T11">
-        <v>100</v>
-      </c>
       <c r="U11">
         <v>100</v>
       </c>
       <c r="V11">
         <v>100</v>
       </c>
-    </row>
-    <row r="12" spans="1:22">
+      <c r="W11">
+        <v>100</v>
+      </c>
+      <c r="X11">
+        <v>100</v>
+      </c>
+      <c r="Y11">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25">
       <c r="A12" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12">
         <v>100</v>
@@ -4189,11 +4649,11 @@
         <v>100</v>
       </c>
       <c r="K12">
+        <v>100</v>
+      </c>
+      <c r="L12">
         <v>97.5</v>
       </c>
-      <c r="L12">
-        <v>100</v>
-      </c>
       <c r="M12">
         <v>100</v>
       </c>
@@ -4210,24 +4670,33 @@
         <v>100</v>
       </c>
       <c r="R12">
+        <v>100</v>
+      </c>
+      <c r="S12">
+        <v>100</v>
+      </c>
+      <c r="T12">
         <v>98.40000000000001</v>
       </c>
-      <c r="S12">
+      <c r="U12">
         <v>97.90000000000001</v>
       </c>
-      <c r="T12">
-        <v>100</v>
-      </c>
-      <c r="U12">
+      <c r="V12">
+        <v>100</v>
+      </c>
+      <c r="W12">
         <v>95.7</v>
       </c>
-      <c r="V12">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22">
+      <c r="X12">
+        <v>100</v>
+      </c>
+      <c r="Y12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25">
       <c r="A13" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13">
         <v>100</v>
@@ -4254,48 +4723,57 @@
         <v>100</v>
       </c>
       <c r="J13">
+        <v>100</v>
+      </c>
+      <c r="K13">
         <v>96.7</v>
       </c>
-      <c r="K13">
+      <c r="L13">
         <v>97.5</v>
       </c>
-      <c r="L13">
-        <v>100</v>
-      </c>
       <c r="M13">
+        <v>100</v>
+      </c>
+      <c r="N13">
         <v>95</v>
       </c>
-      <c r="N13">
+      <c r="O13">
         <v>93.8</v>
       </c>
-      <c r="O13">
+      <c r="P13">
         <v>95</v>
       </c>
-      <c r="P13">
-        <v>100</v>
-      </c>
       <c r="Q13">
-        <v>97.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="R13">
-        <v>98.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="S13">
         <v>97.90000000000001</v>
       </c>
       <c r="T13">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="U13">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="V13">
         <v>96.7</v>
       </c>
-      <c r="U13">
+      <c r="W13">
         <v>91.5</v>
       </c>
-      <c r="V13">
+      <c r="X13">
         <v>96.90000000000001</v>
       </c>
-    </row>
-    <row r="14" spans="1:22">
+      <c r="Y13">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25">
       <c r="A14" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B14">
         <v>100</v>
@@ -4322,48 +4800,57 @@
         <v>100</v>
       </c>
       <c r="J14">
+        <v>100</v>
+      </c>
+      <c r="K14">
         <v>93.3</v>
       </c>
-      <c r="K14">
+      <c r="L14">
         <v>97.5</v>
       </c>
-      <c r="L14">
-        <v>100</v>
-      </c>
       <c r="M14">
         <v>100</v>
       </c>
       <c r="N14">
+        <v>100</v>
+      </c>
+      <c r="O14">
         <v>90.59999999999999</v>
       </c>
-      <c r="O14">
+      <c r="P14">
         <v>97.5</v>
       </c>
-      <c r="P14">
-        <v>100</v>
-      </c>
       <c r="Q14">
+        <v>100</v>
+      </c>
+      <c r="R14">
+        <v>100</v>
+      </c>
+      <c r="S14">
         <v>95.8</v>
       </c>
-      <c r="R14">
+      <c r="T14">
         <v>93.8</v>
       </c>
-      <c r="S14">
+      <c r="U14">
         <v>91.7</v>
       </c>
-      <c r="T14">
-        <v>100</v>
-      </c>
-      <c r="U14">
+      <c r="V14">
+        <v>100</v>
+      </c>
+      <c r="W14">
         <v>89.40000000000001</v>
       </c>
-      <c r="V14">
+      <c r="X14">
         <v>98.40000000000001</v>
       </c>
-    </row>
-    <row r="15" spans="1:22">
+      <c r="Y14">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25">
       <c r="A15" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B15">
         <v>100</v>
@@ -4399,11 +4886,11 @@
         <v>100</v>
       </c>
       <c r="M15">
+        <v>100</v>
+      </c>
+      <c r="N15">
         <v>95</v>
       </c>
-      <c r="N15">
-        <v>100</v>
-      </c>
       <c r="O15">
         <v>100</v>
       </c>
@@ -4414,24 +4901,33 @@
         <v>100</v>
       </c>
       <c r="R15">
+        <v>100</v>
+      </c>
+      <c r="S15">
+        <v>100</v>
+      </c>
+      <c r="T15">
         <v>98.40000000000001</v>
       </c>
-      <c r="S15">
+      <c r="U15">
         <v>97.90000000000001</v>
       </c>
-      <c r="T15">
+      <c r="V15">
         <v>96.7</v>
       </c>
-      <c r="U15">
+      <c r="W15">
         <v>95.7</v>
       </c>
-      <c r="V15">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="16" spans="1:22">
+      <c r="X15">
+        <v>100</v>
+      </c>
+      <c r="Y15">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25">
       <c r="A16" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B16">
         <v>62.5</v>
@@ -4455,51 +4951,60 @@
         <v>60</v>
       </c>
       <c r="I16">
+        <v>100</v>
+      </c>
+      <c r="J16">
         <v>85</v>
       </c>
-      <c r="J16">
+      <c r="K16">
         <v>90</v>
       </c>
-      <c r="K16">
+      <c r="L16">
         <v>87.5</v>
       </c>
-      <c r="L16">
+      <c r="M16">
         <v>86.7</v>
       </c>
-      <c r="M16">
+      <c r="N16">
         <v>95</v>
       </c>
-      <c r="N16">
+      <c r="O16">
         <v>87.5</v>
       </c>
-      <c r="O16">
+      <c r="P16">
         <v>75</v>
       </c>
-      <c r="P16">
+      <c r="Q16">
+        <v>100</v>
+      </c>
+      <c r="R16">
         <v>90.59999999999999</v>
       </c>
-      <c r="Q16">
+      <c r="S16">
         <v>93.8</v>
       </c>
-      <c r="R16">
+      <c r="T16">
         <v>85.90000000000001</v>
       </c>
-      <c r="S16">
+      <c r="U16">
         <v>89.59999999999999</v>
       </c>
-      <c r="T16">
+      <c r="V16">
         <v>96.7</v>
       </c>
-      <c r="U16">
+      <c r="W16">
         <v>87.2</v>
       </c>
-      <c r="V16">
+      <c r="X16">
         <v>84.40000000000001</v>
       </c>
-    </row>
-    <row r="17" spans="1:22">
+      <c r="Y16">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25">
       <c r="A17" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B17">
         <v>100</v>
@@ -4526,48 +5031,57 @@
         <v>100</v>
       </c>
       <c r="J17">
+        <v>100</v>
+      </c>
+      <c r="K17">
         <v>96.7</v>
       </c>
-      <c r="K17">
+      <c r="L17">
         <v>97.5</v>
       </c>
-      <c r="L17">
-        <v>100</v>
-      </c>
       <c r="M17">
+        <v>100</v>
+      </c>
+      <c r="N17">
         <v>92.5</v>
       </c>
-      <c r="N17">
+      <c r="O17">
         <v>90.59999999999999</v>
       </c>
-      <c r="O17">
-        <v>100</v>
-      </c>
       <c r="P17">
         <v>100</v>
       </c>
       <c r="Q17">
+        <v>100</v>
+      </c>
+      <c r="R17">
+        <v>100</v>
+      </c>
+      <c r="S17">
         <v>97.90000000000001</v>
       </c>
-      <c r="R17">
+      <c r="T17">
         <v>98.40000000000001</v>
       </c>
-      <c r="S17">
-        <v>100</v>
-      </c>
-      <c r="T17">
+      <c r="U17">
+        <v>100</v>
+      </c>
+      <c r="V17">
         <v>95</v>
       </c>
-      <c r="U17">
+      <c r="W17">
         <v>89.40000000000001</v>
       </c>
-      <c r="V17">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="18" spans="1:22">
+      <c r="X17">
+        <v>100</v>
+      </c>
+      <c r="Y17">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25">
       <c r="A18" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B18">
         <v>100</v>
@@ -4597,20 +5111,20 @@
         <v>100</v>
       </c>
       <c r="K18">
+        <v>100</v>
+      </c>
+      <c r="L18">
         <v>97.5</v>
       </c>
-      <c r="L18">
-        <v>100</v>
-      </c>
       <c r="M18">
+        <v>100</v>
+      </c>
+      <c r="N18">
         <v>82.5</v>
       </c>
-      <c r="N18">
+      <c r="O18">
         <v>96.90000000000001</v>
       </c>
-      <c r="O18">
-        <v>100</v>
-      </c>
       <c r="P18">
         <v>100</v>
       </c>
@@ -4618,24 +5132,33 @@
         <v>100</v>
       </c>
       <c r="R18">
+        <v>100</v>
+      </c>
+      <c r="S18">
+        <v>100</v>
+      </c>
+      <c r="T18">
         <v>98.40000000000001</v>
       </c>
-      <c r="S18">
-        <v>100</v>
-      </c>
-      <c r="T18">
+      <c r="U18">
+        <v>100</v>
+      </c>
+      <c r="V18">
         <v>88.3</v>
       </c>
-      <c r="U18">
+      <c r="W18">
         <v>93.59999999999999</v>
       </c>
-      <c r="V18">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="19" spans="1:22">
+      <c r="X18">
+        <v>100</v>
+      </c>
+      <c r="Y18">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25">
       <c r="A19" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B19">
         <v>100</v>
@@ -4662,48 +5185,57 @@
         <v>100</v>
       </c>
       <c r="J19">
+        <v>100</v>
+      </c>
+      <c r="K19">
         <v>96.7</v>
       </c>
-      <c r="K19">
+      <c r="L19">
         <v>97.5</v>
       </c>
-      <c r="L19">
+      <c r="M19">
         <v>93.3</v>
       </c>
-      <c r="M19">
+      <c r="N19">
         <v>87.5</v>
       </c>
-      <c r="N19">
-        <v>100</v>
-      </c>
       <c r="O19">
+        <v>100</v>
+      </c>
+      <c r="P19">
         <v>95</v>
       </c>
-      <c r="P19">
-        <v>100</v>
-      </c>
       <c r="Q19">
+        <v>100</v>
+      </c>
+      <c r="R19">
+        <v>100</v>
+      </c>
+      <c r="S19">
         <v>97.90000000000001</v>
       </c>
-      <c r="R19">
+      <c r="T19">
         <v>98.40000000000001</v>
       </c>
-      <c r="S19">
+      <c r="U19">
         <v>91.7</v>
       </c>
-      <c r="T19">
+      <c r="V19">
         <v>91.7</v>
       </c>
-      <c r="U19">
+      <c r="W19">
         <v>95.7</v>
       </c>
-      <c r="V19">
+      <c r="X19">
         <v>96.90000000000001</v>
       </c>
-    </row>
-    <row r="20" spans="1:22">
+      <c r="Y19">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25">
       <c r="A20" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B20">
         <v>100</v>
@@ -4730,48 +5262,57 @@
         <v>100</v>
       </c>
       <c r="J20">
+        <v>100</v>
+      </c>
+      <c r="K20">
         <v>90</v>
       </c>
-      <c r="K20">
+      <c r="L20">
         <v>92.5</v>
       </c>
-      <c r="L20">
+      <c r="M20">
         <v>93.3</v>
       </c>
-      <c r="M20">
-        <v>100</v>
-      </c>
       <c r="N20">
+        <v>100</v>
+      </c>
+      <c r="O20">
         <v>90.59999999999999</v>
       </c>
-      <c r="O20">
+      <c r="P20">
         <v>92.5</v>
       </c>
-      <c r="P20">
-        <v>100</v>
-      </c>
       <c r="Q20">
+        <v>100</v>
+      </c>
+      <c r="R20">
+        <v>100</v>
+      </c>
+      <c r="S20">
         <v>85.40000000000001</v>
       </c>
-      <c r="R20">
+      <c r="T20">
         <v>95.3</v>
       </c>
-      <c r="S20">
+      <c r="U20">
         <v>89.59999999999999</v>
       </c>
-      <c r="T20">
-        <v>100</v>
-      </c>
-      <c r="U20">
+      <c r="V20">
+        <v>100</v>
+      </c>
+      <c r="W20">
         <v>89.40000000000001</v>
       </c>
-      <c r="V20">
+      <c r="X20">
         <v>92.2</v>
       </c>
-    </row>
-    <row r="21" spans="1:22">
+      <c r="Y20">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25">
       <c r="A21" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B21">
         <v>100</v>
@@ -4798,48 +5339,57 @@
         <v>100</v>
       </c>
       <c r="J21">
+        <v>100</v>
+      </c>
+      <c r="K21">
         <v>93.3</v>
       </c>
-      <c r="K21">
+      <c r="L21">
         <v>95</v>
       </c>
-      <c r="L21">
-        <v>100</v>
-      </c>
       <c r="M21">
+        <v>100</v>
+      </c>
+      <c r="N21">
         <v>87.5</v>
       </c>
-      <c r="N21">
+      <c r="O21">
         <v>96.90000000000001</v>
       </c>
-      <c r="O21">
+      <c r="P21">
         <v>92.5</v>
       </c>
-      <c r="P21">
-        <v>100</v>
-      </c>
       <c r="Q21">
+        <v>100</v>
+      </c>
+      <c r="R21">
+        <v>100</v>
+      </c>
+      <c r="S21">
         <v>93.8</v>
       </c>
-      <c r="R21">
+      <c r="T21">
         <v>96.90000000000001</v>
       </c>
-      <c r="S21">
-        <v>100</v>
-      </c>
-      <c r="T21">
+      <c r="U21">
+        <v>100</v>
+      </c>
+      <c r="V21">
         <v>91.7</v>
       </c>
-      <c r="U21">
+      <c r="W21">
         <v>93.59999999999999</v>
       </c>
-      <c r="V21">
+      <c r="X21">
         <v>95.3</v>
       </c>
-    </row>
-    <row r="22" spans="1:22">
+      <c r="Y21">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25">
       <c r="A22" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B22">
         <v>100</v>
@@ -4869,20 +5419,20 @@
         <v>100</v>
       </c>
       <c r="K22">
+        <v>100</v>
+      </c>
+      <c r="L22">
         <v>97.5</v>
       </c>
-      <c r="L22">
-        <v>100</v>
-      </c>
       <c r="M22">
+        <v>100</v>
+      </c>
+      <c r="N22">
         <v>97.5</v>
       </c>
-      <c r="N22">
+      <c r="O22">
         <v>90.59999999999999</v>
       </c>
-      <c r="O22">
-        <v>100</v>
-      </c>
       <c r="P22">
         <v>100</v>
       </c>
@@ -4890,24 +5440,33 @@
         <v>100</v>
       </c>
       <c r="R22">
+        <v>100</v>
+      </c>
+      <c r="S22">
+        <v>100</v>
+      </c>
+      <c r="T22">
         <v>96.90000000000001</v>
       </c>
-      <c r="S22">
-        <v>100</v>
-      </c>
-      <c r="T22">
+      <c r="U22">
+        <v>100</v>
+      </c>
+      <c r="V22">
         <v>98.3</v>
       </c>
-      <c r="U22">
+      <c r="W22">
         <v>89.40000000000001</v>
       </c>
-      <c r="V22">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="23" spans="1:22">
+      <c r="X22">
+        <v>100</v>
+      </c>
+      <c r="Y22">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25">
       <c r="A23" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B23">
         <v>100</v>
@@ -4931,11 +5490,11 @@
         <v>100</v>
       </c>
       <c r="I23">
+        <v>100</v>
+      </c>
+      <c r="J23">
         <v>90</v>
       </c>
-      <c r="J23">
-        <v>100</v>
-      </c>
       <c r="K23">
         <v>100</v>
       </c>
@@ -4943,39 +5502,48 @@
         <v>100</v>
       </c>
       <c r="M23">
+        <v>100</v>
+      </c>
+      <c r="N23">
         <v>90</v>
       </c>
-      <c r="N23">
+      <c r="O23">
         <v>96.90000000000001</v>
       </c>
-      <c r="O23">
-        <v>100</v>
-      </c>
       <c r="P23">
+        <v>100</v>
+      </c>
+      <c r="Q23">
+        <v>100</v>
+      </c>
+      <c r="R23">
         <v>93.8</v>
       </c>
-      <c r="Q23">
-        <v>100</v>
-      </c>
-      <c r="R23">
+      <c r="S23">
+        <v>100</v>
+      </c>
+      <c r="T23">
         <v>98.40000000000001</v>
       </c>
-      <c r="S23">
-        <v>100</v>
-      </c>
-      <c r="T23">
+      <c r="U23">
+        <v>100</v>
+      </c>
+      <c r="V23">
         <v>93.3</v>
       </c>
-      <c r="U23">
+      <c r="W23">
         <v>93.59999999999999</v>
       </c>
-      <c r="V23">
+      <c r="X23">
         <v>96.90000000000001</v>
       </c>
-    </row>
-    <row r="24" spans="1:22">
+      <c r="Y23">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25">
       <c r="A24" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B24">
         <v>100</v>
@@ -5005,45 +5573,54 @@
         <v>100</v>
       </c>
       <c r="K24">
+        <v>100</v>
+      </c>
+      <c r="L24">
         <v>97.5</v>
       </c>
-      <c r="L24">
+      <c r="M24">
         <v>96.7</v>
       </c>
-      <c r="M24">
+      <c r="N24">
         <v>82.5</v>
       </c>
-      <c r="N24">
-        <v>100</v>
-      </c>
       <c r="O24">
+        <v>100</v>
+      </c>
+      <c r="P24">
         <v>92.5</v>
       </c>
-      <c r="P24">
-        <v>100</v>
-      </c>
       <c r="Q24">
         <v>100</v>
       </c>
       <c r="R24">
+        <v>100</v>
+      </c>
+      <c r="S24">
+        <v>100</v>
+      </c>
+      <c r="T24">
         <v>98.40000000000001</v>
-      </c>
-      <c r="S24">
-        <v>97.90000000000001</v>
-      </c>
-      <c r="T24">
-        <v>88.3</v>
       </c>
       <c r="U24">
         <v>97.90000000000001</v>
       </c>
       <c r="V24">
+        <v>88.3</v>
+      </c>
+      <c r="W24">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="X24">
         <v>95.3</v>
       </c>
-    </row>
-    <row r="25" spans="1:22">
+      <c r="Y24">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25">
       <c r="A25" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B25">
         <v>100</v>
@@ -5082,14 +5659,14 @@
         <v>100</v>
       </c>
       <c r="N25">
+        <v>100</v>
+      </c>
+      <c r="O25">
         <v>96.90000000000001</v>
       </c>
-      <c r="O25">
+      <c r="P25">
         <v>95</v>
       </c>
-      <c r="P25">
-        <v>100</v>
-      </c>
       <c r="Q25">
         <v>100</v>
       </c>
@@ -5103,15 +5680,24 @@
         <v>100</v>
       </c>
       <c r="U25">
+        <v>100</v>
+      </c>
+      <c r="V25">
+        <v>100</v>
+      </c>
+      <c r="W25">
         <v>97.90000000000001</v>
       </c>
-      <c r="V25">
+      <c r="X25">
         <v>96.90000000000001</v>
       </c>
-    </row>
-    <row r="26" spans="1:22">
+      <c r="Y25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25">
       <c r="A26" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B26">
         <v>100</v>
@@ -5141,45 +5727,54 @@
         <v>100</v>
       </c>
       <c r="K26">
+        <v>100</v>
+      </c>
+      <c r="L26">
         <v>95</v>
       </c>
-      <c r="L26">
+      <c r="M26">
         <v>93.3</v>
       </c>
-      <c r="M26">
+      <c r="N26">
         <v>90</v>
       </c>
-      <c r="N26">
+      <c r="O26">
         <v>96.90000000000001</v>
       </c>
-      <c r="O26">
+      <c r="P26">
         <v>92.5</v>
       </c>
-      <c r="P26">
-        <v>100</v>
-      </c>
       <c r="Q26">
         <v>100</v>
       </c>
       <c r="R26">
+        <v>100</v>
+      </c>
+      <c r="S26">
+        <v>100</v>
+      </c>
+      <c r="T26">
         <v>96.90000000000001</v>
       </c>
-      <c r="S26">
+      <c r="U26">
         <v>95.8</v>
       </c>
-      <c r="T26">
+      <c r="V26">
         <v>93.3</v>
       </c>
-      <c r="U26">
+      <c r="W26">
         <v>93.59999999999999</v>
       </c>
-      <c r="V26">
+      <c r="X26">
         <v>95.3</v>
       </c>
-    </row>
-    <row r="27" spans="1:22">
+      <c r="Y26">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25">
       <c r="A27" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B27">
         <v>100</v>
@@ -5203,11 +5798,11 @@
         <v>100</v>
       </c>
       <c r="I27">
+        <v>100</v>
+      </c>
+      <c r="J27">
         <v>90</v>
       </c>
-      <c r="J27">
-        <v>100</v>
-      </c>
       <c r="K27">
         <v>100</v>
       </c>
@@ -5218,36 +5813,45 @@
         <v>100</v>
       </c>
       <c r="N27">
+        <v>100</v>
+      </c>
+      <c r="O27">
         <v>96.90000000000001</v>
       </c>
-      <c r="O27">
-        <v>100</v>
-      </c>
       <c r="P27">
+        <v>100</v>
+      </c>
+      <c r="Q27">
+        <v>100</v>
+      </c>
+      <c r="R27">
         <v>93.8</v>
       </c>
-      <c r="Q27">
-        <v>100</v>
-      </c>
-      <c r="R27">
-        <v>100</v>
-      </c>
       <c r="S27">
+        <v>100</v>
+      </c>
+      <c r="T27">
+        <v>100</v>
+      </c>
+      <c r="U27">
         <v>95.8</v>
       </c>
-      <c r="T27">
-        <v>100</v>
-      </c>
-      <c r="U27">
+      <c r="V27">
+        <v>100</v>
+      </c>
+      <c r="W27">
         <v>91.5</v>
       </c>
-      <c r="V27">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="28" spans="1:22">
+      <c r="X27">
+        <v>100</v>
+      </c>
+      <c r="Y27">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25">
       <c r="A28" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B28">
         <v>100</v>
@@ -5277,45 +5881,54 @@
         <v>100</v>
       </c>
       <c r="K28">
+        <v>100</v>
+      </c>
+      <c r="L28">
         <v>97.5</v>
       </c>
-      <c r="L28">
-        <v>100</v>
-      </c>
       <c r="M28">
         <v>100</v>
       </c>
       <c r="N28">
+        <v>100</v>
+      </c>
+      <c r="O28">
         <v>96.90000000000001</v>
       </c>
-      <c r="O28">
+      <c r="P28">
         <v>95</v>
       </c>
-      <c r="P28">
-        <v>100</v>
-      </c>
       <c r="Q28">
         <v>100</v>
       </c>
       <c r="R28">
+        <v>100</v>
+      </c>
+      <c r="S28">
+        <v>100</v>
+      </c>
+      <c r="T28">
         <v>98.40000000000001</v>
       </c>
-      <c r="S28">
-        <v>100</v>
-      </c>
-      <c r="T28">
-        <v>100</v>
-      </c>
       <c r="U28">
         <v>100</v>
       </c>
       <c r="V28">
+        <v>100</v>
+      </c>
+      <c r="W28">
+        <v>100</v>
+      </c>
+      <c r="X28">
         <v>96.90000000000001</v>
       </c>
-    </row>
-    <row r="29" spans="1:22">
+      <c r="Y28">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25">
       <c r="A29" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B29">
         <v>100</v>
@@ -5348,11 +5961,11 @@
         <v>100</v>
       </c>
       <c r="L29">
+        <v>100</v>
+      </c>
+      <c r="M29">
         <v>96.7</v>
       </c>
-      <c r="M29">
-        <v>100</v>
-      </c>
       <c r="N29">
         <v>100</v>
       </c>
@@ -5366,24 +5979,33 @@
         <v>100</v>
       </c>
       <c r="R29">
+        <v>100</v>
+      </c>
+      <c r="S29">
+        <v>100</v>
+      </c>
+      <c r="T29">
         <v>98.40000000000001</v>
       </c>
-      <c r="S29">
+      <c r="U29">
         <v>93.8</v>
       </c>
-      <c r="T29">
-        <v>100</v>
-      </c>
-      <c r="U29">
-        <v>100</v>
-      </c>
       <c r="V29">
         <v>100</v>
       </c>
-    </row>
-    <row r="30" spans="1:22">
+      <c r="W29">
+        <v>100</v>
+      </c>
+      <c r="X29">
+        <v>100</v>
+      </c>
+      <c r="Y29">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25">
       <c r="A30" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B30">
         <v>100</v>
@@ -5407,11 +6029,11 @@
         <v>100</v>
       </c>
       <c r="I30">
+        <v>100</v>
+      </c>
+      <c r="J30">
         <v>90</v>
       </c>
-      <c r="J30">
-        <v>100</v>
-      </c>
       <c r="K30">
         <v>100</v>
       </c>
@@ -5428,14 +6050,14 @@
         <v>100</v>
       </c>
       <c r="P30">
+        <v>100</v>
+      </c>
+      <c r="Q30">
+        <v>100</v>
+      </c>
+      <c r="R30">
         <v>93.8</v>
       </c>
-      <c r="Q30">
-        <v>100</v>
-      </c>
-      <c r="R30">
-        <v>100</v>
-      </c>
       <c r="S30">
         <v>100</v>
       </c>
@@ -5443,15 +6065,24 @@
         <v>100</v>
       </c>
       <c r="U30">
+        <v>100</v>
+      </c>
+      <c r="V30">
+        <v>100</v>
+      </c>
+      <c r="W30">
         <v>93.59999999999999</v>
       </c>
-      <c r="V30">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="31" spans="1:22">
+      <c r="X30">
+        <v>100</v>
+      </c>
+      <c r="Y30">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25">
       <c r="A31" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B31">
         <v>100</v>
@@ -5481,45 +6112,54 @@
         <v>100</v>
       </c>
       <c r="K31">
+        <v>100</v>
+      </c>
+      <c r="L31">
         <v>97.5</v>
       </c>
-      <c r="L31">
+      <c r="M31">
         <v>90</v>
       </c>
-      <c r="M31">
+      <c r="N31">
         <v>95</v>
       </c>
-      <c r="N31">
+      <c r="O31">
         <v>93.8</v>
       </c>
-      <c r="O31">
+      <c r="P31">
         <v>97.5</v>
       </c>
-      <c r="P31">
-        <v>100</v>
-      </c>
       <c r="Q31">
         <v>100</v>
       </c>
       <c r="R31">
+        <v>100</v>
+      </c>
+      <c r="S31">
+        <v>100</v>
+      </c>
+      <c r="T31">
         <v>93.8</v>
       </c>
-      <c r="S31">
+      <c r="U31">
         <v>93.8</v>
       </c>
-      <c r="T31">
+      <c r="V31">
         <v>96.7</v>
       </c>
-      <c r="U31">
+      <c r="W31">
         <v>89.40000000000001</v>
       </c>
-      <c r="V31">
+      <c r="X31">
         <v>98.40000000000001</v>
       </c>
-    </row>
-    <row r="32" spans="1:22">
+      <c r="Y31">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25">
       <c r="A32" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B32">
         <v>100</v>
@@ -5543,51 +6183,60 @@
         <v>100</v>
       </c>
       <c r="I32">
+        <v>100</v>
+      </c>
+      <c r="J32">
         <v>90</v>
       </c>
-      <c r="J32">
+      <c r="K32">
         <v>93.3</v>
       </c>
-      <c r="K32">
-        <v>100</v>
-      </c>
       <c r="L32">
         <v>100</v>
       </c>
       <c r="M32">
+        <v>100</v>
+      </c>
+      <c r="N32">
         <v>95</v>
       </c>
-      <c r="N32">
+      <c r="O32">
         <v>96.90000000000001</v>
       </c>
-      <c r="O32">
-        <v>100</v>
-      </c>
       <c r="P32">
+        <v>100</v>
+      </c>
+      <c r="Q32">
+        <v>100</v>
+      </c>
+      <c r="R32">
         <v>93.8</v>
       </c>
-      <c r="Q32">
+      <c r="S32">
         <v>95.8</v>
       </c>
-      <c r="R32">
-        <v>100</v>
-      </c>
-      <c r="S32">
-        <v>100</v>
-      </c>
       <c r="T32">
+        <v>100</v>
+      </c>
+      <c r="U32">
+        <v>100</v>
+      </c>
+      <c r="V32">
         <v>96.7</v>
       </c>
-      <c r="U32">
+      <c r="W32">
         <v>93.59999999999999</v>
       </c>
-      <c r="V32">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="33" spans="1:22">
+      <c r="X32">
+        <v>100</v>
+      </c>
+      <c r="Y32">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" spans="1:25">
       <c r="A33" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B33">
         <v>100</v>
@@ -5611,53 +6260,62 @@
         <v>100</v>
       </c>
       <c r="I33">
+        <v>100</v>
+      </c>
+      <c r="J33">
         <v>90</v>
       </c>
-      <c r="J33">
-        <v>100</v>
-      </c>
       <c r="K33">
+        <v>100</v>
+      </c>
+      <c r="L33">
         <v>97.5</v>
       </c>
-      <c r="L33">
-        <v>100</v>
-      </c>
       <c r="M33">
         <v>100</v>
       </c>
       <c r="N33">
+        <v>100</v>
+      </c>
+      <c r="O33">
         <v>96.90000000000001</v>
       </c>
-      <c r="O33">
-        <v>100</v>
-      </c>
       <c r="P33">
+        <v>100</v>
+      </c>
+      <c r="Q33">
+        <v>100</v>
+      </c>
+      <c r="R33">
         <v>93.8</v>
       </c>
-      <c r="Q33">
-        <v>100</v>
-      </c>
-      <c r="R33">
+      <c r="S33">
+        <v>100</v>
+      </c>
+      <c r="T33">
         <v>98.40000000000001</v>
       </c>
-      <c r="S33">
-        <v>100</v>
-      </c>
-      <c r="T33">
-        <v>100</v>
-      </c>
       <c r="U33">
+        <v>100</v>
+      </c>
+      <c r="V33">
+        <v>100</v>
+      </c>
+      <c r="W33">
         <v>93.59999999999999</v>
       </c>
-      <c r="V33">
+      <c r="X33">
+        <v>100</v>
+      </c>
+      <c r="Y33">
         <v>100</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="I1:O1"/>
-    <mergeCell ref="P1:V1"/>
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="J1:Q1"/>
+    <mergeCell ref="R1:Y1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5678,31 +6336,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -5931,21 +6589,33 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>55</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
         <v>60</v>
       </c>
       <c r="C9">
+        <v>30</v>
+      </c>
+      <c r="D9">
+        <v>29</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9" s="2">
+        <v>96.7</v>
+      </c>
+      <c r="G9" s="2">
+        <v>3.3</v>
+      </c>
+      <c r="H9">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="I9">
         <v>0</v>
       </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="I9">
+      <c r="J9" s="2">
         <v>0</v>
       </c>
     </row>
@@ -5980,7 +6650,7 @@
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -6014,7 +6684,7 @@
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>

--- a/grupos/1FM - Estadisticos 20231.xlsx
+++ b/grupos/1FM - Estadisticos 20231.xlsx
@@ -914,25 +914,25 @@
         <v>10</v>
       </c>
       <c r="Z4">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA4">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB4">
         <v>5</v>
       </c>
       <c r="AC4">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AD4">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE4">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF4">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AG4">
         <v>10</v>
@@ -1015,16 +1015,16 @@
         <v>10</v>
       </c>
       <c r="Z5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB5">
         <v>10</v>
       </c>
       <c r="AC5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD5">
         <v>10</v>
@@ -1116,25 +1116,25 @@
         <v>10</v>
       </c>
       <c r="Z6">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD6">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG6">
         <v>10</v>
@@ -1217,25 +1217,25 @@
         <v>10</v>
       </c>
       <c r="Z7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA7">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD7">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AG7">
         <v>10</v>
@@ -1318,25 +1318,25 @@
         <v>10</v>
       </c>
       <c r="Z8">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA8">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB8">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC8">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD8">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE8">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG8">
         <v>10</v>
@@ -1437,7 +1437,7 @@
         <v>5</v>
       </c>
       <c r="AF9">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG9">
         <v>5</v>
@@ -1520,25 +1520,25 @@
         <v>10</v>
       </c>
       <c r="Z10">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC10">
         <v>10</v>
       </c>
       <c r="AD10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AG10">
         <v>10</v>
@@ -1621,16 +1621,16 @@
         <v>10</v>
       </c>
       <c r="Z11">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA11">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB11">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD11">
         <v>5</v>
@@ -1639,7 +1639,7 @@
         <v>10</v>
       </c>
       <c r="AF11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG11">
         <v>10</v>
@@ -1722,25 +1722,25 @@
         <v>10</v>
       </c>
       <c r="Z12">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA12">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB12">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC12">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AD12">
         <v>5</v>
       </c>
       <c r="AE12">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AF12">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AG12">
         <v>10</v>
@@ -1823,25 +1823,25 @@
         <v>10</v>
       </c>
       <c r="Z13">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA13">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB13">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC13">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD13">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AE13">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF13">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AG13">
         <v>10</v>
@@ -1924,25 +1924,25 @@
         <v>10</v>
       </c>
       <c r="Z14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB14">
         <v>5</v>
       </c>
       <c r="AC14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AG14">
         <v>10</v>
@@ -2025,25 +2025,25 @@
         <v>10</v>
       </c>
       <c r="Z15">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA15">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB15">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC15">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AD15">
         <v>5</v>
       </c>
       <c r="AE15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF15">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG15">
         <v>10</v>
@@ -2126,25 +2126,25 @@
         <v>10</v>
       </c>
       <c r="Z16">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA16">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB16">
         <v>5</v>
       </c>
       <c r="AC16">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AD16">
         <v>5</v>
       </c>
       <c r="AE16">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AF16">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG16">
         <v>10</v>
@@ -2227,25 +2227,25 @@
         <v>10</v>
       </c>
       <c r="Z17">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC17">
         <v>10</v>
       </c>
       <c r="AD17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG17">
         <v>10</v>
@@ -2328,25 +2328,25 @@
         <v>10</v>
       </c>
       <c r="Z18">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA18">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB18">
         <v>5</v>
       </c>
       <c r="AC18">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AD18">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE18">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF18">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG18">
         <v>10</v>
@@ -2429,25 +2429,25 @@
         <v>10</v>
       </c>
       <c r="Z19">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA19">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB19">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD19">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF19">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AG19">
         <v>10</v>
@@ -2530,25 +2530,25 @@
         <v>10</v>
       </c>
       <c r="Z20">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA20">
         <v>5</v>
       </c>
       <c r="AB20">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC20">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD20">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AE20">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF20">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AG20">
         <v>10</v>
@@ -2631,25 +2631,25 @@
         <v>10</v>
       </c>
       <c r="Z21">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA21">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB21">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC21">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD21">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE21">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF21">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AG21">
         <v>10</v>
@@ -2732,25 +2732,25 @@
         <v>10</v>
       </c>
       <c r="Z22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA22">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB22">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC22">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD22">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG22">
         <v>10</v>
@@ -2833,7 +2833,7 @@
         <v>10</v>
       </c>
       <c r="Z23">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA23">
         <v>5</v>
@@ -2842,13 +2842,13 @@
         <v>5</v>
       </c>
       <c r="AC23">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AD23">
         <v>5</v>
       </c>
       <c r="AE23">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF23">
         <v>5</v>
@@ -2934,25 +2934,25 @@
         <v>10</v>
       </c>
       <c r="Z24">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA24">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB24">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC24">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD24">
         <v>5</v>
       </c>
       <c r="AE24">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG24">
         <v>10</v>
@@ -3035,25 +3035,25 @@
         <v>10</v>
       </c>
       <c r="Z25">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA25">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB25">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD25">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE25">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF25">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AG25">
         <v>10</v>
@@ -3136,25 +3136,25 @@
         <v>10</v>
       </c>
       <c r="Z26">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA26">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB26">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC26">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD26">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE26">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF26">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AG26">
         <v>10</v>
@@ -3237,25 +3237,25 @@
         <v>10</v>
       </c>
       <c r="Z27">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA27">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB27">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD27">
         <v>5</v>
       </c>
       <c r="AE27">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF27">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AG27">
         <v>10</v>
@@ -3338,19 +3338,19 @@
         <v>10</v>
       </c>
       <c r="Z28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC28">
         <v>10</v>
       </c>
       <c r="AD28">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE28">
         <v>10</v>
@@ -3439,16 +3439,16 @@
         <v>10</v>
       </c>
       <c r="Z29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA29">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD29">
         <v>10</v>
@@ -3457,7 +3457,7 @@
         <v>10</v>
       </c>
       <c r="AF29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG29">
         <v>10</v>
@@ -3540,25 +3540,25 @@
         <v>10</v>
       </c>
       <c r="Z30">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA30">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB30">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC30">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AD30">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE30">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF30">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AG30">
         <v>10</v>
@@ -3641,25 +3641,25 @@
         <v>10</v>
       </c>
       <c r="Z31">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA31">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB31">
         <v>5</v>
       </c>
       <c r="AC31">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AD31">
         <v>5</v>
       </c>
       <c r="AE31">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AF31">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AG31">
         <v>10</v>
@@ -3742,25 +3742,25 @@
         <v>10</v>
       </c>
       <c r="Z32">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA32">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB32">
         <v>5</v>
       </c>
       <c r="AC32">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AD32">
         <v>5</v>
       </c>
       <c r="AE32">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF32">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG32">
         <v>10</v>
@@ -3843,25 +3843,25 @@
         <v>10</v>
       </c>
       <c r="Z33">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA33">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB33">
         <v>5</v>
       </c>
       <c r="AC33">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AD33">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE33">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF33">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AG33">
         <v>10</v>
@@ -6386,7 +6386,7 @@
         <v>33.3</v>
       </c>
       <c r="H2">
-        <v>6.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -6418,7 +6418,7 @@
         <v>30</v>
       </c>
       <c r="H3">
-        <v>6.6</v>
+        <v>8.5</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -6450,7 +6450,7 @@
         <v>10</v>
       </c>
       <c r="H4">
-        <v>6.7</v>
+        <v>9.5</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6482,7 +6482,7 @@
         <v>3.3</v>
       </c>
       <c r="H5">
-        <v>6.7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6514,7 +6514,7 @@
         <v>3.3</v>
       </c>
       <c r="H6">
-        <v>7.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6546,7 +6546,7 @@
         <v>3.3</v>
       </c>
       <c r="H7">
-        <v>7.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6578,7 +6578,7 @@
         <v>3.3</v>
       </c>
       <c r="H8">
-        <v>7.7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I8">
         <v>0</v>

--- a/grupos/1FM - Estadisticos 20231.xlsx
+++ b/grupos/1FM - Estadisticos 20231.xlsx
@@ -914,25 +914,25 @@
         <v>10</v>
       </c>
       <c r="Z4">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA4">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB4">
         <v>5</v>
       </c>
       <c r="AC4">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AD4">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE4">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AF4">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AG4">
         <v>10</v>
@@ -1015,16 +1015,16 @@
         <v>10</v>
       </c>
       <c r="Z5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB5">
         <v>10</v>
       </c>
       <c r="AC5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD5">
         <v>10</v>
@@ -1116,25 +1116,25 @@
         <v>10</v>
       </c>
       <c r="Z6">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD6">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG6">
         <v>10</v>
@@ -1217,25 +1217,25 @@
         <v>10</v>
       </c>
       <c r="Z7">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA7">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB7">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD7">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AG7">
         <v>10</v>
@@ -1318,25 +1318,25 @@
         <v>10</v>
       </c>
       <c r="Z8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA8">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD8">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AF8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG8">
         <v>10</v>
@@ -1437,7 +1437,7 @@
         <v>5</v>
       </c>
       <c r="AF9">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG9">
         <v>5</v>
@@ -1520,25 +1520,25 @@
         <v>10</v>
       </c>
       <c r="Z10">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB10">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC10">
         <v>10</v>
       </c>
       <c r="AD10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AF10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AG10">
         <v>10</v>
@@ -1621,16 +1621,16 @@
         <v>10</v>
       </c>
       <c r="Z11">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA11">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB11">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD11">
         <v>5</v>
@@ -1639,7 +1639,7 @@
         <v>10</v>
       </c>
       <c r="AF11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG11">
         <v>10</v>
@@ -1722,25 +1722,25 @@
         <v>10</v>
       </c>
       <c r="Z12">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA12">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC12">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AD12">
         <v>5</v>
       </c>
       <c r="AE12">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AF12">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AG12">
         <v>10</v>
@@ -1823,25 +1823,25 @@
         <v>10</v>
       </c>
       <c r="Z13">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA13">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB13">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AF13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AG13">
         <v>10</v>
@@ -1924,25 +1924,25 @@
         <v>10</v>
       </c>
       <c r="Z14">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB14">
         <v>5</v>
       </c>
       <c r="AC14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD14">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AF14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AG14">
         <v>10</v>
@@ -2025,25 +2025,25 @@
         <v>10</v>
       </c>
       <c r="Z15">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA15">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB15">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC15">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AD15">
         <v>5</v>
       </c>
       <c r="AE15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AF15">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG15">
         <v>10</v>
@@ -2126,25 +2126,25 @@
         <v>10</v>
       </c>
       <c r="Z16">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA16">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB16">
         <v>5</v>
       </c>
       <c r="AC16">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AD16">
         <v>5</v>
       </c>
       <c r="AE16">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AF16">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG16">
         <v>10</v>
@@ -2227,25 +2227,25 @@
         <v>10</v>
       </c>
       <c r="Z17">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC17">
         <v>10</v>
       </c>
       <c r="AD17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG17">
         <v>10</v>
@@ -2328,25 +2328,25 @@
         <v>10</v>
       </c>
       <c r="Z18">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA18">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB18">
         <v>5</v>
       </c>
       <c r="AC18">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AD18">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE18">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AF18">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG18">
         <v>10</v>
@@ -2429,25 +2429,25 @@
         <v>10</v>
       </c>
       <c r="Z19">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA19">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB19">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD19">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AF19">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AG19">
         <v>10</v>
@@ -2530,25 +2530,25 @@
         <v>10</v>
       </c>
       <c r="Z20">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA20">
         <v>5</v>
       </c>
       <c r="AB20">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC20">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD20">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE20">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AF20">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AG20">
         <v>10</v>
@@ -2631,25 +2631,25 @@
         <v>10</v>
       </c>
       <c r="Z21">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA21">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB21">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC21">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD21">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE21">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AF21">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AG21">
         <v>10</v>
@@ -2732,25 +2732,25 @@
         <v>10</v>
       </c>
       <c r="Z22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA22">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB22">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC22">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD22">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG22">
         <v>10</v>
@@ -2833,7 +2833,7 @@
         <v>10</v>
       </c>
       <c r="Z23">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA23">
         <v>5</v>
@@ -2842,13 +2842,13 @@
         <v>5</v>
       </c>
       <c r="AC23">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AD23">
         <v>5</v>
       </c>
       <c r="AE23">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AF23">
         <v>5</v>
@@ -2934,25 +2934,25 @@
         <v>10</v>
       </c>
       <c r="Z24">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA24">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB24">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC24">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD24">
         <v>5</v>
       </c>
       <c r="AE24">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AF24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG24">
         <v>10</v>
@@ -3035,25 +3035,25 @@
         <v>10</v>
       </c>
       <c r="Z25">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA25">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB25">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD25">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE25">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AF25">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AG25">
         <v>10</v>
@@ -3136,25 +3136,25 @@
         <v>10</v>
       </c>
       <c r="Z26">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA26">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB26">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC26">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD26">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE26">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AF26">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AG26">
         <v>10</v>
@@ -3237,25 +3237,25 @@
         <v>10</v>
       </c>
       <c r="Z27">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA27">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB27">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD27">
         <v>5</v>
       </c>
       <c r="AE27">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AF27">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AG27">
         <v>10</v>
@@ -3338,19 +3338,19 @@
         <v>10</v>
       </c>
       <c r="Z28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC28">
         <v>10</v>
       </c>
       <c r="AD28">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AE28">
         <v>10</v>
@@ -3439,16 +3439,16 @@
         <v>10</v>
       </c>
       <c r="Z29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA29">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD29">
         <v>10</v>
@@ -3457,7 +3457,7 @@
         <v>10</v>
       </c>
       <c r="AF29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG29">
         <v>10</v>
@@ -3540,25 +3540,25 @@
         <v>10</v>
       </c>
       <c r="Z30">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA30">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB30">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC30">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD30">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE30">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AF30">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AG30">
         <v>10</v>
@@ -3641,25 +3641,25 @@
         <v>10</v>
       </c>
       <c r="Z31">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA31">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB31">
         <v>5</v>
       </c>
       <c r="AC31">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AD31">
         <v>5</v>
       </c>
       <c r="AE31">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AF31">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AG31">
         <v>10</v>
@@ -3742,25 +3742,25 @@
         <v>10</v>
       </c>
       <c r="Z32">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA32">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB32">
         <v>5</v>
       </c>
       <c r="AC32">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AD32">
         <v>5</v>
       </c>
       <c r="AE32">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AF32">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG32">
         <v>10</v>
@@ -3843,25 +3843,25 @@
         <v>10</v>
       </c>
       <c r="Z33">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA33">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB33">
         <v>5</v>
       </c>
       <c r="AC33">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AD33">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AE33">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AF33">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AG33">
         <v>10</v>
@@ -6386,7 +6386,7 @@
         <v>33.3</v>
       </c>
       <c r="H2">
-        <v>8.300000000000001</v>
+        <v>6.3</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -6418,7 +6418,7 @@
         <v>30</v>
       </c>
       <c r="H3">
-        <v>8.5</v>
+        <v>6.6</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -6450,7 +6450,7 @@
         <v>10</v>
       </c>
       <c r="H4">
-        <v>9.5</v>
+        <v>6.7</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6482,7 +6482,7 @@
         <v>3.3</v>
       </c>
       <c r="H5">
-        <v>9.800000000000001</v>
+        <v>6.7</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6514,7 +6514,7 @@
         <v>3.3</v>
       </c>
       <c r="H6">
-        <v>9.800000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6546,7 +6546,7 @@
         <v>3.3</v>
       </c>
       <c r="H7">
-        <v>9.800000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6578,7 +6578,7 @@
         <v>3.3</v>
       </c>
       <c r="H8">
-        <v>9.800000000000001</v>
+        <v>7.7</v>
       </c>
       <c r="I8">
         <v>0</v>
